--- a/internacional/2_8/Contraste_quimica.xlsx
+++ b/internacional/2_8/Contraste_quimica.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE118"/>
+  <dimension ref="A1:AH122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -587,6 +587,21 @@
           <t>TW esp</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Grado SV solido</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Lectura amplia</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Lectura estricta</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -659,6 +674,22 @@
       <c r="V2" t="n">
         <v>1</v>
       </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -731,6 +762,19 @@
       <c r="V3" t="n">
         <v>1</v>
       </c>
+      <c r="AF3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -750,7 +794,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
         <v>6</v>
@@ -797,6 +841,19 @@
       <c r="V4" t="n">
         <v>1</v>
       </c>
+      <c r="AF4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -863,6 +920,22 @@
       <c r="V5" t="n">
         <v>1</v>
       </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -905,11 +978,24 @@
       <c r="V6" t="n">
         <v>1</v>
       </c>
+      <c r="AF6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Distribución electrónica por niveles (modelo de capas)</t>
+          <t>Fuerzas intermoleculares y propiedades físicas</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -918,10 +1004,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>8</v>
@@ -929,8 +1015,8 @@
       <c r="G7" t="n">
         <v>8.5</v>
       </c>
-      <c r="K7" t="n">
-        <v>8</v>
+      <c r="H7" t="n">
+        <v>7</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -938,14 +1024,30 @@
       <c r="P7" t="n">
         <v>1</v>
       </c>
-      <c r="T7" t="n">
-        <v>1</v>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Electrones de valencia y regla del octeto</t>
+          <t>Iones</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -954,22 +1056,65 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
       </c>
       <c r="G8" t="n">
         <v>8.5</v>
       </c>
+      <c r="I8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
       <c r="P8" t="n">
         <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Enlace covalente</t>
+          <t>Reutilización y reciclaje de materiales</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -978,28 +1123,74 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
         <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>7</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Enlace iónico</t>
+          <t>Mezclas homogéneas y heterogéneas</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1008,28 +1199,86 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" t="n">
         <v>5</v>
       </c>
-      <c r="D10" t="n">
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6</v>
+      </c>
+      <c r="L10" t="n">
         <v>5</v>
       </c>
-      <c r="F10" t="n">
-        <v>8</v>
-      </c>
-      <c r="G10" t="n">
-        <v>8.5</v>
+      <c r="M10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Enlace metálico</t>
+          <t>Evolución de los modelos atómicos</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1038,34 +1287,59 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" t="n">
         <v>6</v>
       </c>
-      <c r="D11" t="n">
-        <v>6</v>
-      </c>
-      <c r="F11" t="n">
+      <c r="K11" t="n">
         <v>8</v>
       </c>
-      <c r="G11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>7</v>
-      </c>
-      <c r="O11" t="n">
+      <c r="L11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7</v>
+      </c>
+      <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1</v>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Notación y estructuras de Lewis</t>
+          <t>Moléculas y fórmulas químicas</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1074,22 +1348,86 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" t="n">
         <v>6</v>
       </c>
-      <c r="D12" t="n">
+      <c r="H12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" t="n">
         <v>6</v>
       </c>
-      <c r="G12" t="n">
-        <v>8.5</v>
+      <c r="L12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>7</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
       </c>
       <c r="P12" t="n">
         <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fuerzas intermoleculares y propiedades físicas</t>
+          <t>Propiedades periódicas</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1098,34 +1436,50 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
         <v>6</v>
       </c>
-      <c r="D13" t="n">
-        <v>6</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="K13" t="n">
         <v>8</v>
       </c>
-      <c r="G13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H13" t="n">
-        <v>7</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
+      <c r="M13" t="n">
+        <v>7</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1</v>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Geometría molecular (RPECV)</t>
+          <t>Propiedades singulares del agua</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1134,22 +1488,59 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
         <v>6</v>
       </c>
-      <c r="D14" t="n">
+      <c r="H14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
         <v>6</v>
       </c>
-      <c r="G14" t="n">
-        <v>8.5</v>
+      <c r="O14" t="n">
+        <v>1</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Iones</t>
+          <t>Química descriptiva de los elementos</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1169,14 +1560,8 @@
       <c r="G15" t="n">
         <v>8.5</v>
       </c>
-      <c r="I15" t="n">
-        <v>8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>7</v>
-      </c>
-      <c r="L15" t="n">
-        <v>7.5</v>
+      <c r="H15" t="n">
+        <v>7</v>
       </c>
       <c r="M15" t="n">
         <v>7</v>
@@ -1187,23 +1572,33 @@
       <c r="P15" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
+      <c r="Q15" t="n">
         <v>1</v>
       </c>
       <c r="V15" t="n">
         <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Isótopos</t>
+          <t>Reacción química y sus evidencias</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1212,28 +1607,83 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
         <v>5</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
         <v>5</v>
       </c>
-      <c r="G16" t="n">
-        <v>8.5</v>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>7.5</v>
       </c>
+      <c r="M16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
       <c r="U16" t="n">
         <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Masa atómica relativa</t>
+          <t>Métodos físicos de separación de mezclas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1242,22 +1692,43 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="n">
         <v>5</v>
       </c>
-      <c r="D17" t="n">
-        <v>5</v>
-      </c>
       <c r="G17" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6</v>
       </c>
       <c r="L17" t="n">
         <v>7.5</v>
       </c>
       <c r="M17" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -1265,17 +1736,42 @@
       <c r="Q17" t="n">
         <v>1</v>
       </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
       <c r="U17" t="n">
         <v>1</v>
       </c>
       <c r="V17" t="n">
         <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Reutilización y reciclaje de materiales</t>
+          <t>Organización de la tabla periódica</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1284,10 +1780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
         <v>8</v>
@@ -1296,13 +1792,13 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
         <v>7.5</v>
@@ -1331,11 +1827,27 @@
       <c r="V18" t="n">
         <v>1</v>
       </c>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mezclas homogéneas y heterogéneas</t>
+          <t>Calidad y tratamiento del agua</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1344,40 +1856,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="H19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
-        <v>6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4.5</v>
-      </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L19" t="n">
         <v>5</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
@@ -1388,12 +1888,6 @@
       <c r="Q19" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
@@ -1402,47 +1896,72 @@
       </c>
       <c r="V19" t="n">
         <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Evolución de los modelos atómicos</t>
+          <t>Ácidos y bases: propiedades</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
-      </c>
-      <c r="E20" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" t="n">
         <v>8</v>
       </c>
       <c r="G20" t="n">
         <v>6</v>
       </c>
-      <c r="K20" t="n">
-        <v>8</v>
+      <c r="H20" t="n">
+        <v>7</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
         <v>7.5</v>
       </c>
       <c r="M20" t="n">
-        <v>7</v>
-      </c>
-      <c r="N20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O20" t="n">
         <v>1</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
       </c>
-      <c r="T20" t="n">
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
@@ -1450,51 +1969,64 @@
       </c>
       <c r="V20" t="n">
         <v>1</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Moléculas y fórmulas químicas</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M21" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N21" t="n">
         <v>1</v>
@@ -1522,69 +2054,122 @@
       </c>
       <c r="V21" t="n">
         <v>1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Número de oxidación</t>
+          <t>Combustibles fósiles y biocombustibles</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
         <v>8</v>
       </c>
+      <c r="G22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>7</v>
+      </c>
       <c r="O22" t="n">
         <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Propiedades físicas y químicas</t>
+          <t>Conservación de la masa</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7</v>
+      </c>
+      <c r="I23" t="n">
         <v>4</v>
       </c>
-      <c r="G23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" t="n">
-        <v>6</v>
-      </c>
       <c r="J23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L23" t="n">
         <v>7.5</v>
@@ -1610,44 +2195,63 @@
       <c r="S23" t="n">
         <v>1</v>
       </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="n">
         <v>1</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Propiedades periódicas</t>
+          <t>Disolución y rapidez de disolución</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K24" t="n">
         <v>6</v>
       </c>
-      <c r="H24" t="n">
-        <v>7</v>
-      </c>
-      <c r="K24" t="n">
-        <v>8</v>
+      <c r="L24" t="n">
+        <v>7.5</v>
       </c>
       <c r="M24" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
@@ -1655,32 +2259,57 @@
       <c r="Q24" t="n">
         <v>1</v>
       </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
       <c r="T24" t="n">
         <v>1</v>
       </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
       <c r="V24" t="n">
         <v>1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Propiedades singulares del agua</t>
+          <t>Ecuación química y su balanceo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G25" t="n">
         <v>6</v>
@@ -1689,10 +2318,19 @@
         <v>7</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>7</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -1706,38 +2344,69 @@
       <c r="R25" t="n">
         <v>1</v>
       </c>
-      <c r="T25" t="n">
-        <v>1</v>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Química descriptiva de los elementos</t>
+          <t>Escala de pH</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F26" t="n">
         <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
         <v>7</v>
       </c>
+      <c r="I26" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M26" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
@@ -1748,80 +2417,148 @@
       <c r="Q26" t="n">
         <v>1</v>
       </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
       <c r="V26" t="n">
         <v>1</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Radiactividad y emisiones nucleares</t>
+          <t>Estados de la materia</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
         <v>8</v>
       </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>4</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.5</v>
+      </c>
       <c r="N27" t="n">
         <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Reacción química y sus evidencias</t>
+          <t>Estequiometría</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
-      </c>
-      <c r="H28" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K28" t="n">
-        <v>4</v>
-      </c>
-      <c r="L28" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
@@ -1829,72 +2566,58 @@
       <c r="P28" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
       <c r="R28" t="n">
         <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
-      <c r="T28" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1</v>
+      <c r="AF28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Métodos físicos de separación de mezclas</t>
+          <t>Indicadores ácido-base</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" t="n">
+        <v>9</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" t="n">
         <v>6</v>
       </c>
-      <c r="F29" t="n">
-        <v>4</v>
-      </c>
-      <c r="G29" t="n">
-        <v>3</v>
-      </c>
       <c r="H29" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J29" t="n">
         <v>4.5</v>
       </c>
-      <c r="K29" t="n">
-        <v>6</v>
-      </c>
       <c r="L29" t="n">
         <v>7.5</v>
       </c>
       <c r="M29" t="n">
         <v>2.5</v>
       </c>
-      <c r="N29" t="n">
-        <v>1</v>
-      </c>
       <c r="O29" t="n">
         <v>1</v>
       </c>
@@ -1904,59 +2627,75 @@
       <c r="Q29" t="n">
         <v>1</v>
       </c>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
-      <c r="T29" t="n">
-        <v>1</v>
-      </c>
       <c r="U29" t="n">
         <v>1</v>
       </c>
       <c r="V29" t="n">
         <v>1</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Organización de la tabla periódica</t>
+          <t>Materia y materiales</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
       </c>
       <c r="F30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
         <v>8</v>
       </c>
-      <c r="G30" t="n">
-        <v>6</v>
-      </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4</v>
+      </c>
+      <c r="L30" t="n">
         <v>3</v>
       </c>
-      <c r="J30" t="n">
-        <v>7</v>
-      </c>
-      <c r="K30" t="n">
-        <v>8</v>
-      </c>
-      <c r="L30" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M30" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
@@ -1967,6 +2706,9 @@
       <c r="Q30" t="n">
         <v>1</v>
       </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
@@ -1978,43 +2720,68 @@
       </c>
       <c r="V30" t="n">
         <v>1</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Calidad y tratamiento del agua</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" t="n">
+        <v>7</v>
+      </c>
+      <c r="I31" t="n">
         <v>3</v>
       </c>
-      <c r="D31" t="n">
-        <v>3</v>
-      </c>
-      <c r="F31" t="n">
+      <c r="J31" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" t="n">
         <v>4</v>
       </c>
-      <c r="G31" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" t="n">
-        <v>7</v>
-      </c>
       <c r="L31" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="M31" t="n">
         <v>7</v>
       </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
       <c r="O31" t="n">
         <v>1</v>
       </c>
@@ -2024,6 +2791,12 @@
       <c r="Q31" t="n">
         <v>1</v>
       </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
@@ -2032,12 +2805,28 @@
       </c>
       <c r="V31" t="n">
         <v>1</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ácidos y bases: propiedades</t>
+          <t>Neutralización y reacciones de los ácidos</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2046,16 +2835,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
-      </c>
-      <c r="D32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F32" t="n">
         <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H32" t="n">
         <v>7</v>
@@ -2070,7 +2856,7 @@
         <v>7.5</v>
       </c>
       <c r="M32" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
@@ -2092,12 +2878,28 @@
       </c>
       <c r="V32" t="n">
         <v>1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Propiedades físicas de los materiales</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2115,7 +2917,7 @@
         <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
         <v>2</v>
@@ -2124,7 +2926,7 @@
         <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
         <v>2.5</v>
@@ -2133,7 +2935,7 @@
         <v>4</v>
       </c>
       <c r="L33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
         <v>2.5</v>
@@ -2165,11 +2967,27 @@
       <c r="V33" t="n">
         <v>1</v>
       </c>
+      <c r="Z33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Combustibles fósiles y biocombustibles</t>
+          <t>Sustancias puras: elementos y compuestos</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2178,10 +2996,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>6</v>
       </c>
       <c r="F34" t="n">
         <v>8</v>
@@ -2190,13 +3011,25 @@
         <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="L34" t="n">
+        <v>7.5</v>
       </c>
       <c r="M34" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
       </c>
       <c r="O34" t="n">
         <v>1</v>
@@ -2207,17 +3040,42 @@
       <c r="Q34" t="n">
         <v>1</v>
       </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
       <c r="T34" t="n">
         <v>1</v>
       </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
       <c r="V34" t="n">
         <v>1</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Composición del aire y contaminantes atmosféricos</t>
+          <t>Clasificación de las reacciones químicas</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2226,25 +3084,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F35" t="n">
         <v>8</v>
       </c>
       <c r="G35" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2.5</v>
+        <v>6</v>
+      </c>
+      <c r="L35" t="n">
+        <v>7.5</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
@@ -2258,89 +3116,70 @@
       <c r="R35" t="n">
         <v>1</v>
       </c>
-      <c r="S35" t="n">
-        <v>1</v>
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Disolución y rapidez de disolución</t>
+          <t>Aminoácidos y estructura de las proteínas</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
-      </c>
-      <c r="G36" t="n">
-        <v>3</v>
-      </c>
-      <c r="H36" t="n">
-        <v>2</v>
-      </c>
-      <c r="I36" t="n">
-        <v>4</v>
-      </c>
-      <c r="J36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K36" t="n">
         <v>6</v>
       </c>
-      <c r="L36" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1</v>
+      <c r="AF36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ecuación química y su balanceo</t>
+          <t>Metales, cerámicas y materiales compuestos</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
-      </c>
-      <c r="D37" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E37" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F37" t="n">
         <v>8</v>
@@ -2351,15 +3190,6 @@
       <c r="H37" t="n">
         <v>7</v>
       </c>
-      <c r="I37" t="n">
-        <v>7</v>
-      </c>
-      <c r="J37" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L37" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M37" t="n">
         <v>7</v>
       </c>
@@ -2375,28 +3205,35 @@
       <c r="Q37" t="n">
         <v>1</v>
       </c>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
       <c r="V37" t="n">
         <v>1</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Escala de pH</t>
+          <t>Combustión</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2404,15 +3241,18 @@
       </c>
       <c r="D38" t="n">
         <v>7</v>
+      </c>
+      <c r="E38" t="n">
+        <v>8</v>
       </c>
       <c r="F38" t="n">
         <v>8</v>
       </c>
       <c r="G38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H38" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
         <v>5</v>
@@ -2424,7 +3264,10 @@
         <v>7.5</v>
       </c>
       <c r="M38" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
       </c>
       <c r="O38" t="n">
         <v>1</v>
@@ -2446,55 +3289,56 @@
       </c>
       <c r="V38" t="n">
         <v>1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Estados de la materia</t>
+          <t>Composición del aire y contaminantes atmosféricos</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H39" t="n">
         <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J39" t="n">
         <v>2.5</v>
       </c>
-      <c r="K39" t="n">
-        <v>4</v>
-      </c>
-      <c r="L39" t="n">
-        <v>4</v>
-      </c>
-      <c r="M39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
       <c r="O39" t="n">
         <v>1</v>
       </c>
@@ -2510,320 +3354,264 @@
       <c r="S39" t="n">
         <v>1</v>
       </c>
-      <c r="T39" t="n">
-        <v>1</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1</v>
+      <c r="AF39" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Estequiometría</t>
+          <t>Composición porcentual y fórmulas empírica y molecular</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>8</v>
-      </c>
-      <c r="F40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G40" t="n">
         <v>8.5</v>
       </c>
-      <c r="I40" t="n">
-        <v>7</v>
-      </c>
-      <c r="J40" t="n">
-        <v>7</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1</v>
-      </c>
       <c r="P40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" t="n">
-        <v>1</v>
-      </c>
-      <c r="S40" t="n">
-        <v>1</v>
+      <c r="AF40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fuerzas intermoleculares</t>
+          <t>Configuración electrónica por orbitales</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
-      </c>
-      <c r="E41" t="n">
-        <v>6</v>
-      </c>
-      <c r="G41" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J41" t="n">
-        <v>7</v>
-      </c>
-      <c r="N41" t="n">
-        <v>1</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1</v>
-      </c>
-      <c r="S41" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Masa molar</t>
+          <t>Diagramas de fases</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D42" t="n">
-        <v>8</v>
-      </c>
-      <c r="F42" t="n">
-        <v>8</v>
-      </c>
-      <c r="G42" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Materia y materiales</t>
+          <t>Mezclas de gases, difusión y gases reales</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" t="n">
-        <v>2</v>
-      </c>
-      <c r="F43" t="n">
-        <v>4</v>
-      </c>
-      <c r="G43" t="n">
-        <v>2</v>
-      </c>
-      <c r="H43" t="n">
-        <v>2</v>
-      </c>
-      <c r="I43" t="n">
         <v>8</v>
       </c>
       <c r="J43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L43" t="n">
-        <v>3</v>
-      </c>
-      <c r="M43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N43" t="n">
-        <v>1</v>
-      </c>
-      <c r="O43" t="n">
-        <v>1</v>
-      </c>
-      <c r="P43" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>1</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
       </c>
-      <c r="T43" t="n">
-        <v>1</v>
-      </c>
       <c r="U43" t="n">
         <v>1</v>
       </c>
-      <c r="V43" t="n">
-        <v>1</v>
+      <c r="AF43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Minerales: composición y estructura cristalina</t>
+          <t>Distribución electrónica por niveles (modelo de capas)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>8</v>
-      </c>
-      <c r="E44" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
       </c>
-      <c r="H44" t="n">
-        <v>7</v>
-      </c>
-      <c r="N44" t="n">
-        <v>1</v>
+      <c r="G44" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K44" t="n">
+        <v>8</v>
       </c>
       <c r="O44" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" t="n">
-        <v>1</v>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>Energía de activación y perfil energético</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
-      </c>
-      <c r="E45" t="n">
-        <v>4</v>
-      </c>
-      <c r="F45" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G45" t="n">
         <v>6</v>
       </c>
-      <c r="H45" t="n">
-        <v>7</v>
-      </c>
-      <c r="I45" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" t="n">
-        <v>7</v>
-      </c>
-      <c r="K45" t="n">
-        <v>4</v>
-      </c>
-      <c r="L45" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M45" t="n">
-        <v>7</v>
-      </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1</v>
-      </c>
       <c r="P45" t="n">
         <v>1</v>
       </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1</v>
-      </c>
-      <c r="S45" t="n">
-        <v>1</v>
-      </c>
-      <c r="T45" t="n">
-        <v>1</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1</v>
+      <c r="AF45" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mol y número de Avogadro</t>
+          <t>Enlace metálico</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F46" t="n">
         <v>8</v>
@@ -2831,38 +3619,60 @@
       <c r="G46" t="n">
         <v>8.5</v>
       </c>
+      <c r="H46" t="n">
+        <v>7</v>
+      </c>
       <c r="O46" t="n">
         <v>1</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Compuestos inorgánicos: funciones y nomenclatura</t>
+          <t>Enlace químico</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F47" t="n">
         <v>8</v>
       </c>
       <c r="G47" t="n">
-        <v>6</v>
-      </c>
-      <c r="M47" t="n">
-        <v>7</v>
+        <v>8.5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>7</v>
+      </c>
+      <c r="L47" t="n">
+        <v>7.5</v>
       </c>
       <c r="O47" t="n">
         <v>1</v>
@@ -2870,55 +3680,78 @@
       <c r="P47" t="n">
         <v>1</v>
       </c>
-      <c r="V47" t="n">
-        <v>1</v>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Oxidación y corrosión de los metales</t>
+          <t>Equilibrio químico dinámico</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>7</v>
-      </c>
-      <c r="H48" t="n">
-        <v>3</v>
-      </c>
-      <c r="I48" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="G48" t="n">
+        <v>8.5</v>
       </c>
       <c r="M48" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1</v>
-      </c>
-      <c r="R48" t="n">
+        <v>7</v>
+      </c>
+      <c r="P48" t="n">
         <v>1</v>
       </c>
       <c r="V48" t="n">
         <v>1</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Polaridad molecular</t>
+          <t>Fuerzas intermoleculares</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -2927,77 +3760,91 @@
       <c r="D49" t="n">
         <v>6</v>
       </c>
-      <c r="F49" t="n">
-        <v>8</v>
-      </c>
-      <c r="K49" t="n">
+      <c r="E49" t="n">
         <v>6</v>
       </c>
-      <c r="O49" t="n">
-        <v>1</v>
-      </c>
-      <c r="T49" t="n">
-        <v>1</v>
+      <c r="G49" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J49" t="n">
+        <v>7</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Proceso de disolución y solvatación</t>
+          <t>Fundamentos de la reactividad orgánica</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>7</v>
-      </c>
-      <c r="H50" t="n">
-        <v>7</v>
-      </c>
-      <c r="K50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M50" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>1</v>
-      </c>
-      <c r="T50" t="n">
-        <v>1</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Procesos de la industria química</t>
+          <t>Masa atómica relativa</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G51" t="n">
         <v>8.5</v>
       </c>
-      <c r="K51" t="n">
-        <v>6</v>
+      <c r="L51" t="n">
+        <v>7.5</v>
       </c>
       <c r="M51" t="n">
         <v>7</v>
@@ -3005,101 +3852,94 @@
       <c r="P51" t="n">
         <v>1</v>
       </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
         <v>1</v>
       </c>
       <c r="V51" t="n">
         <v>1</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Propiedades físicas de los materiales</t>
+          <t>Minerales: composición y estructura cristalina</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>8</v>
+      </c>
+      <c r="D52" t="n">
+        <v>8</v>
+      </c>
+      <c r="E52" t="n">
+        <v>7</v>
+      </c>
+      <c r="F52" t="n">
+        <v>8</v>
+      </c>
+      <c r="H52" t="n">
+        <v>7</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
           <t>alineado</t>
         </is>
-      </c>
-      <c r="C52" t="n">
-        <v>2</v>
-      </c>
-      <c r="D52" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2</v>
-      </c>
-      <c r="F52" t="n">
-        <v>4</v>
-      </c>
-      <c r="G52" t="n">
-        <v>2</v>
-      </c>
-      <c r="H52" t="n">
-        <v>2</v>
-      </c>
-      <c r="I52" t="n">
-        <v>6</v>
-      </c>
-      <c r="J52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K52" t="n">
-        <v>4</v>
-      </c>
-      <c r="L52" t="n">
-        <v>3</v>
-      </c>
-      <c r="M52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N52" t="n">
-        <v>1</v>
-      </c>
-      <c r="O52" t="n">
-        <v>1</v>
-      </c>
-      <c r="P52" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>1</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1</v>
-      </c>
-      <c r="S52" t="n">
-        <v>1</v>
-      </c>
-      <c r="T52" t="n">
-        <v>1</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Factores que afectan la rapidez de reacción</t>
+          <t>Compuestos inorgánicos: funciones y nomenclatura</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F53" t="n">
         <v>8</v>
@@ -3107,11 +3947,8 @@
       <c r="G53" t="n">
         <v>6</v>
       </c>
-      <c r="H53" t="n">
-        <v>7</v>
-      </c>
       <c r="M53" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O53" t="n">
         <v>1</v>
@@ -3119,455 +3956,648 @@
       <c r="P53" t="n">
         <v>1</v>
       </c>
-      <c r="Q53" t="n">
-        <v>1</v>
-      </c>
       <c r="V53" t="n">
         <v>1</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Solubilidad y disoluciones saturadas</t>
+          <t>Nomenclatura orgánica IUPAC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
-      </c>
-      <c r="F54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
-      </c>
-      <c r="H54" t="n">
-        <v>2</v>
-      </c>
-      <c r="I54" t="n">
-        <v>4</v>
-      </c>
-      <c r="J54" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K54" t="n">
         <v>6</v>
       </c>
-      <c r="L54" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M54" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O54" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
       </c>
-      <c r="Q54" t="n">
-        <v>1</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1</v>
-      </c>
-      <c r="S54" t="n">
-        <v>1</v>
-      </c>
-      <c r="T54" t="n">
-        <v>1</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1</v>
-      </c>
       <c r="V54" t="n">
         <v>1</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sustancias puras: elementos y compuestos</t>
+          <t>Oxidación y corrosión de los metales</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
-      </c>
-      <c r="E55" t="n">
-        <v>6</v>
-      </c>
-      <c r="F55" t="n">
-        <v>8</v>
-      </c>
-      <c r="G55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H55" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>6</v>
-      </c>
-      <c r="J55" t="n">
-        <v>7</v>
-      </c>
-      <c r="K55" t="n">
-        <v>6</v>
-      </c>
-      <c r="L55" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="M55" t="n">
         <v>2.5</v>
       </c>
-      <c r="N55" t="n">
-        <v>1</v>
-      </c>
-      <c r="O55" t="n">
-        <v>1</v>
-      </c>
-      <c r="P55" t="n">
-        <v>1</v>
-      </c>
       <c r="Q55" t="n">
         <v>1</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
       </c>
-      <c r="S55" t="n">
-        <v>1</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1</v>
-      </c>
       <c r="V55" t="n">
         <v>1</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tipo de enlace y propiedades de las sustancias</t>
+          <t>Proceso de disolución y solvatación</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>7</v>
+      </c>
+      <c r="D56" t="n">
+        <v>7</v>
+      </c>
+      <c r="H56" t="n">
+        <v>7</v>
+      </c>
+      <c r="K56" t="n">
+        <v>6</v>
+      </c>
+      <c r="M56" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
           <t>alineado</t>
         </is>
-      </c>
-      <c r="C56" t="n">
-        <v>6</v>
-      </c>
-      <c r="D56" t="n">
-        <v>6</v>
-      </c>
-      <c r="F56" t="n">
-        <v>8</v>
-      </c>
-      <c r="G56" t="n">
-        <v>6</v>
-      </c>
-      <c r="H56" t="n">
-        <v>7</v>
-      </c>
-      <c r="M56" t="n">
-        <v>7</v>
-      </c>
-      <c r="O56" t="n">
-        <v>1</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>1</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Clasificación de las reacciones químicas</t>
+          <t>Procesos de la industria química</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" t="n">
+        <v>8</v>
+      </c>
+      <c r="G57" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K57" t="n">
+        <v>6</v>
+      </c>
+      <c r="M57" t="n">
+        <v>7</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
           <t>alineado</t>
         </is>
-      </c>
-      <c r="C57" t="n">
-        <v>6</v>
-      </c>
-      <c r="D57" t="n">
-        <v>6</v>
-      </c>
-      <c r="F57" t="n">
-        <v>8</v>
-      </c>
-      <c r="G57" t="n">
-        <v>6</v>
-      </c>
-      <c r="H57" t="n">
-        <v>7</v>
-      </c>
-      <c r="I57" t="n">
-        <v>6</v>
-      </c>
-      <c r="L57" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O57" t="n">
-        <v>1</v>
-      </c>
-      <c r="P57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>1</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Autoionización del agua, Kw y cálculo de pH</t>
+          <t>Propiedades físicas y químicas</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.5</v>
       </c>
       <c r="G58" t="n">
-        <v>8.5</v>
+        <v>2</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" t="n">
+        <v>6</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K58" t="n">
+        <v>8</v>
+      </c>
+      <c r="L58" t="n">
+        <v>7.5</v>
       </c>
       <c r="M58" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
       </c>
       <c r="P58" t="n">
         <v>1</v>
       </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
+      </c>
       <c r="V58" t="n">
         <v>1</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Catalizadores</t>
+          <t>Química de los carbohidratos</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C59" t="n">
+        <v>6</v>
+      </c>
+      <c r="D59" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF59" t="n">
         <v>10</v>
       </c>
-      <c r="G59" t="n">
-        <v>6</v>
-      </c>
-      <c r="M59" t="n">
-        <v>7</v>
-      </c>
-      <c r="P59" t="n">
-        <v>1</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1</v>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Celdas galvánicas</t>
+          <t>Radiactividad y emisiones nucleares</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>11</v>
-      </c>
-      <c r="I60" t="n">
         <v>5</v>
       </c>
-      <c r="M60" t="n">
-        <v>7</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1</v>
-      </c>
-      <c r="V60" t="n">
-        <v>1</v>
+      <c r="D60" t="n">
+        <v>5</v>
+      </c>
+      <c r="E60" t="n">
+        <v>8</v>
+      </c>
+      <c r="N60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Composición porcentual y fórmulas empírica y molecular</t>
+          <t>Factores que afectan la rapidez de reacción</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="D61" t="n">
+        <v>6</v>
+      </c>
+      <c r="F61" t="n">
+        <v>8</v>
       </c>
       <c r="G61" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H61" t="n">
+        <v>7</v>
+      </c>
+      <c r="M61" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1</v>
       </c>
       <c r="P61" t="n">
         <v>1</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cromatografía</t>
+          <t>Rendimiento de una reacción</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C62" t="n">
+        <v>8</v>
+      </c>
+      <c r="D62" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF62" t="n">
         <v>10</v>
       </c>
-      <c r="G62" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H62" t="n">
-        <v>7</v>
-      </c>
-      <c r="L62" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M62" t="n">
-        <v>7</v>
-      </c>
-      <c r="P62" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>1</v>
-      </c>
-      <c r="U62" t="n">
-        <v>1</v>
-      </c>
-      <c r="V62" t="n">
-        <v>1</v>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mezclas de gases, difusión y gases reales</t>
+          <t>Solubilidad y disoluciones saturadas</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="D63" t="n">
+        <v>3</v>
+      </c>
+      <c r="F63" t="n">
+        <v>8</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2</v>
+      </c>
+      <c r="I63" t="n">
+        <v>4</v>
       </c>
       <c r="J63" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K63" t="n">
+        <v>6</v>
       </c>
       <c r="L63" t="n">
         <v>7.5</v>
       </c>
+      <c r="M63" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1</v>
+      </c>
       <c r="S63" t="n">
         <v>1</v>
       </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
       <c r="U63" t="n">
         <v>1</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ecuación de los gases ideales y volumen molar</t>
+          <t>Teoría cinética de los gases</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C64" t="n">
+        <v>8</v>
+      </c>
+      <c r="D64" t="n">
+        <v>8</v>
+      </c>
+      <c r="G64" t="n">
+        <v>6</v>
+      </c>
+      <c r="H64" t="n">
+        <v>7</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M64" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" t="n">
         <v>10</v>
       </c>
-      <c r="F64" t="n">
-        <v>8</v>
-      </c>
-      <c r="O64" t="n">
-        <v>1</v>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ecuaciones y reacciones nucleares</t>
+          <t>Tipo de enlace y propiedades de las sustancias</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>10</v>
-      </c>
-      <c r="L65" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="D65" t="n">
+        <v>6</v>
+      </c>
+      <c r="F65" t="n">
+        <v>8</v>
+      </c>
+      <c r="G65" t="n">
+        <v>6</v>
+      </c>
+      <c r="H65" t="n">
+        <v>7</v>
+      </c>
+      <c r="M65" t="n">
+        <v>7</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>El carbono y las moléculas orgánicas</t>
+          <t>Autoionización del agua, Kw y cálculo de pH</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3576,10 +4606,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>10</v>
-      </c>
-      <c r="F66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G66" t="n">
         <v>8.5</v>
@@ -3587,20 +4614,30 @@
       <c r="M66" t="n">
         <v>7</v>
       </c>
-      <c r="O66" t="n">
-        <v>1</v>
-      </c>
       <c r="P66" t="n">
         <v>1</v>
       </c>
       <c r="V66" t="n">
         <v>1</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Electrólisis y celdas electrolíticas</t>
+          <t>Celdas galvánicas</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3609,37 +4646,41 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>10</v>
-      </c>
-      <c r="G67" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H67" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="D67" t="n">
+        <v>4</v>
       </c>
       <c r="I67" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M67" t="n">
         <v>7</v>
       </c>
-      <c r="P67" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>1</v>
-      </c>
       <c r="R67" t="n">
         <v>1</v>
       </c>
       <c r="V67" t="n">
         <v>1</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Electrolitos fuertes y débiles</t>
+          <t>Cromatografía</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3648,37 +4689,50 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>9</v>
-      </c>
-      <c r="F68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G68" t="n">
         <v>8.5</v>
       </c>
-      <c r="I68" t="n">
-        <v>8</v>
+      <c r="H68" t="n">
+        <v>7</v>
+      </c>
+      <c r="L68" t="n">
+        <v>7.5</v>
       </c>
       <c r="M68" t="n">
         <v>7</v>
       </c>
-      <c r="O68" t="n">
-        <v>1</v>
-      </c>
       <c r="P68" t="n">
         <v>1</v>
       </c>
-      <c r="R68" t="n">
+      <c r="Q68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
         <v>1</v>
       </c>
       <c r="V68" t="n">
         <v>1</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Energía de activación y perfil energético</t>
+          <t>Ecuación de los gases ideales y volumen molar</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3689,17 +4743,30 @@
       <c r="C69" t="n">
         <v>10</v>
       </c>
-      <c r="G69" t="n">
-        <v>6</v>
-      </c>
-      <c r="P69" t="n">
-        <v>1</v>
+      <c r="F69" t="n">
+        <v>8</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Energía de enlace</t>
+          <t>Ecuaciones y reacciones nucleares</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3710,17 +4777,30 @@
       <c r="C70" t="n">
         <v>10</v>
       </c>
-      <c r="G70" t="n">
-        <v>6</v>
-      </c>
-      <c r="P70" t="n">
-        <v>1</v>
+      <c r="L70" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Enlace químico</t>
+          <t>El carbono y las moléculas orgánicas</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3737,11 +4817,8 @@
       <c r="G71" t="n">
         <v>8.5</v>
       </c>
-      <c r="H71" t="n">
-        <v>7</v>
-      </c>
-      <c r="L71" t="n">
-        <v>7.5</v>
+      <c r="M71" t="n">
+        <v>7</v>
       </c>
       <c r="O71" t="n">
         <v>1</v>
@@ -3749,17 +4826,27 @@
       <c r="P71" t="n">
         <v>1</v>
       </c>
-      <c r="Q71" t="n">
-        <v>1</v>
-      </c>
-      <c r="U71" t="n">
-        <v>1</v>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Entalpía de reacción y ecuaciones termoquímicas</t>
+          <t>Electrólisis y celdas electrolíticas</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3773,8 +4860,11 @@
       <c r="G72" t="n">
         <v>8.5</v>
       </c>
+      <c r="H72" t="n">
+        <v>7</v>
+      </c>
       <c r="I72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M72" t="n">
         <v>7</v>
@@ -3782,17 +4872,33 @@
       <c r="P72" t="n">
         <v>1</v>
       </c>
+      <c r="Q72" t="n">
+        <v>1</v>
+      </c>
       <c r="R72" t="n">
         <v>1</v>
       </c>
       <c r="V72" t="n">
         <v>1</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Equilibrio químico dinámico</t>
+          <t>Electrolitos fuertes y débiles</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3803,23 +4909,48 @@
       <c r="C73" t="n">
         <v>9</v>
       </c>
+      <c r="F73" t="n">
+        <v>8</v>
+      </c>
       <c r="G73" t="n">
         <v>8.5</v>
       </c>
+      <c r="I73" t="n">
+        <v>8</v>
+      </c>
       <c r="M73" t="n">
         <v>7</v>
       </c>
+      <c r="O73" t="n">
+        <v>1</v>
+      </c>
       <c r="P73" t="n">
         <v>1</v>
       </c>
+      <c r="R73" t="n">
+        <v>1</v>
+      </c>
       <c r="V73" t="n">
         <v>1</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Equilibrio y rapidez en procesos industriales</t>
+          <t>Energía de enlace</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3831,16 +4962,29 @@
         <v>10</v>
       </c>
       <c r="G74" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Espectros atómicos y modelo de Bohr</t>
+          <t>Entalpía de reacción y ecuaciones termoquímicas</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3851,17 +4995,42 @@
       <c r="C75" t="n">
         <v>10</v>
       </c>
-      <c r="H75" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>1</v>
+      <c r="G75" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="M75" t="n">
+        <v>7</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Estereoquímica y quiralidad</t>
+          <t>Equilibrio y rapidez en procesos industriales</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3870,19 +5039,32 @@
         </is>
       </c>
       <c r="C76" t="n">
+        <v>9</v>
+      </c>
+      <c r="G76" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF76" t="n">
         <v>10</v>
       </c>
-      <c r="M76" t="n">
-        <v>7</v>
-      </c>
-      <c r="V76" t="n">
-        <v>1</v>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Esterificación e hidrólisis</t>
+          <t>Espectros atómicos y modelo de Bohr</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3891,19 +5073,32 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>11</v>
-      </c>
-      <c r="M77" t="n">
-        <v>7</v>
-      </c>
-      <c r="V77" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="H77" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Estructura y propiedades de los polímeros</t>
+          <t>Estereoquímica y quiralidad</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3912,37 +5107,32 @@
         </is>
       </c>
       <c r="C78" t="n">
+        <v>10</v>
+      </c>
+      <c r="M78" t="n">
+        <v>7</v>
+      </c>
+      <c r="V78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF78" t="n">
         <v>11</v>
       </c>
-      <c r="F78" t="n">
-        <v>8</v>
-      </c>
-      <c r="G78" t="n">
-        <v>6</v>
-      </c>
-      <c r="H78" t="n">
-        <v>7</v>
-      </c>
-      <c r="M78" t="n">
-        <v>7</v>
-      </c>
-      <c r="O78" t="n">
-        <v>1</v>
-      </c>
-      <c r="P78" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>1</v>
-      </c>
-      <c r="V78" t="n">
-        <v>1</v>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Fuerza de ácidos y bases: Ka y Kb</t>
+          <t>Esterificación e hidrólisis</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3951,31 +5141,32 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>9</v>
-      </c>
-      <c r="F79" t="n">
-        <v>8</v>
-      </c>
-      <c r="G79" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="M79" t="n">
         <v>7</v>
       </c>
-      <c r="O79" t="n">
-        <v>1</v>
-      </c>
-      <c r="P79" t="n">
-        <v>1</v>
-      </c>
       <c r="V79" t="n">
         <v>1</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Grupos funcionales</t>
+          <t>Estructura y propiedades de los polímeros</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3990,7 +5181,10 @@
         <v>8</v>
       </c>
       <c r="G80" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H80" t="n">
+        <v>7</v>
       </c>
       <c r="M80" t="n">
         <v>7</v>
@@ -4001,14 +5195,33 @@
       <c r="P80" t="n">
         <v>1</v>
       </c>
+      <c r="Q80" t="n">
+        <v>1</v>
+      </c>
       <c r="V80" t="n">
         <v>1</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Hidrocarburos: alcanos, alquenos y alquinos</t>
+          <t>Fuerza de ácidos y bases: Ka y Kb</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4017,7 +5230,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F81" t="n">
         <v>8</v>
@@ -4025,9 +5238,6 @@
       <c r="G81" t="n">
         <v>8.5</v>
       </c>
-      <c r="H81" t="n">
-        <v>7</v>
-      </c>
       <c r="M81" t="n">
         <v>7</v>
       </c>
@@ -4037,17 +5247,27 @@
       <c r="P81" t="n">
         <v>1</v>
       </c>
-      <c r="Q81" t="n">
-        <v>1</v>
-      </c>
       <c r="V81" t="n">
         <v>1</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Hidrocarburos aromáticos</t>
+          <t>Grupos funcionales</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4056,19 +5276,44 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="F82" t="n">
+        <v>8</v>
       </c>
       <c r="G82" t="n">
         <v>8.5</v>
       </c>
+      <c r="M82" t="n">
+        <v>7</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1</v>
+      </c>
       <c r="P82" t="n">
         <v>1</v>
+      </c>
+      <c r="V82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Isomería estructural</t>
+          <t>Hidrocarburos: alcanos, alquenos y alquinos</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4077,25 +5322,47 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F83" t="n">
         <v>8</v>
       </c>
+      <c r="G83" t="n">
+        <v>8.5</v>
+      </c>
       <c r="M83" t="n">
         <v>7</v>
       </c>
       <c r="O83" t="n">
         <v>1</v>
       </c>
+      <c r="P83" t="n">
+        <v>1</v>
+      </c>
       <c r="V83" t="n">
         <v>1</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ley de Hess y entalpías de formación</t>
+          <t>Hidrocarburos aromáticos</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4104,7 +5371,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G84" t="n">
         <v>8.5</v>
@@ -4112,11 +5379,24 @@
       <c r="P84" t="n">
         <v>1</v>
       </c>
+      <c r="AF84" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Leyes de los gases</t>
+          <t>Isomería estructural</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4127,23 +5407,36 @@
       <c r="C85" t="n">
         <v>10</v>
       </c>
-      <c r="I85" t="n">
-        <v>6</v>
-      </c>
-      <c r="J85" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R85" t="n">
-        <v>1</v>
-      </c>
-      <c r="S85" t="n">
-        <v>1</v>
+      <c r="F85" t="n">
+        <v>8</v>
+      </c>
+      <c r="M85" t="n">
+        <v>7</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1</v>
+      </c>
+      <c r="V85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Leyes ponderales y volumétricas</t>
+          <t>Ley de Hess y entalpías de formación</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4154,23 +5447,30 @@
       <c r="C86" t="n">
         <v>10</v>
       </c>
-      <c r="I86" t="n">
-        <v>7</v>
-      </c>
-      <c r="J86" t="n">
-        <v>7</v>
-      </c>
-      <c r="R86" t="n">
-        <v>1</v>
-      </c>
-      <c r="S86" t="n">
-        <v>1</v>
+      <c r="G86" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Nomenclatura orgánica IUPAC</t>
+          <t>Leyes de los gases</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4179,25 +5479,38 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>11</v>
-      </c>
-      <c r="G87" t="n">
+        <v>10</v>
+      </c>
+      <c r="I87" t="n">
         <v>6</v>
       </c>
-      <c r="M87" t="n">
-        <v>7</v>
-      </c>
-      <c r="P87" t="n">
-        <v>1</v>
-      </c>
-      <c r="V87" t="n">
-        <v>1</v>
+      <c r="J87" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R87" t="n">
+        <v>1</v>
+      </c>
+      <c r="S87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Polimerización por adición y por condensación</t>
+          <t>Leyes ponderales y volumétricas</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4206,25 +5519,38 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>11</v>
-      </c>
-      <c r="H88" t="n">
-        <v>7</v>
-      </c>
-      <c r="M88" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>1</v>
-      </c>
-      <c r="V88" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="I88" t="n">
+        <v>7</v>
+      </c>
+      <c r="J88" t="n">
+        <v>7</v>
+      </c>
+      <c r="R88" t="n">
+        <v>1</v>
+      </c>
+      <c r="S88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Polímeros y ambiente</t>
+          <t>Polimerización por adición y por condensación</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4235,23 +5561,33 @@
       <c r="C89" t="n">
         <v>11</v>
       </c>
-      <c r="F89" t="n">
-        <v>8</v>
-      </c>
-      <c r="H89" t="n">
-        <v>7</v>
-      </c>
-      <c r="O89" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>1</v>
+      <c r="M89" t="n">
+        <v>7</v>
+      </c>
+      <c r="V89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Potenciales estándar de electrodo y de celda</t>
+          <t>Polímeros y ambiente</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4265,20 +5601,36 @@
       <c r="F90" t="n">
         <v>8</v>
       </c>
-      <c r="G90" t="n">
-        <v>8.5</v>
+      <c r="H90" t="n">
+        <v>7</v>
       </c>
       <c r="O90" t="n">
         <v>1</v>
       </c>
-      <c r="P90" t="n">
-        <v>1</v>
+      <c r="Q90" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Principio de Le Chatelier</t>
+          <t>Potenciales estándar de electrodo y de celda</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4287,25 +5639,38 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F91" t="n">
+        <v>8</v>
       </c>
       <c r="G91" t="n">
         <v>8.5</v>
       </c>
-      <c r="M91" t="n">
-        <v>7</v>
+      <c r="O91" t="n">
+        <v>1</v>
       </c>
       <c r="P91" t="n">
         <v>1</v>
       </c>
-      <c r="V91" t="n">
-        <v>1</v>
+      <c r="AF91" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Química de los lípidos</t>
+          <t>Principio de Le Chatelier</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4314,16 +5679,38 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>6</v>
-      </c>
-      <c r="D92" t="n">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="G92" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M92" t="n">
+        <v>7</v>
+      </c>
+      <c r="P92" t="n">
+        <v>1</v>
+      </c>
+      <c r="V92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Química verde y economía atómica</t>
+          <t>Química de los lípidos</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4332,25 +5719,29 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>11</v>
-      </c>
-      <c r="G93" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H93" t="n">
-        <v>7</v>
-      </c>
-      <c r="P93" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="D93" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Reacciones de precipitación e identificación de iones</t>
+          <t>Química verde y economía atómica</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4359,31 +5750,38 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="G94" t="n">
+        <v>8.5</v>
       </c>
       <c r="H94" t="n">
         <v>7</v>
       </c>
-      <c r="I94" t="n">
-        <v>8</v>
-      </c>
-      <c r="M94" t="n">
-        <v>7</v>
+      <c r="P94" t="n">
+        <v>1</v>
       </c>
       <c r="Q94" t="n">
         <v>1</v>
       </c>
-      <c r="R94" t="n">
-        <v>1</v>
-      </c>
-      <c r="V94" t="n">
-        <v>1</v>
+      <c r="AF94" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Reacciones orgánicas características</t>
+          <t>Reacciones de precipitación e identificación de iones</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4392,19 +5790,44 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="H95" t="n">
+        <v>7</v>
+      </c>
+      <c r="I95" t="n">
+        <v>8</v>
       </c>
       <c r="M95" t="n">
         <v>7</v>
       </c>
+      <c r="Q95" t="n">
+        <v>1</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1</v>
+      </c>
       <c r="V95" t="n">
         <v>1</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Reactivo limitante y en exceso</t>
+          <t>Reacciones orgánicas características</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4413,19 +5836,32 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>10</v>
-      </c>
-      <c r="G96" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P96" t="n">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="M96" t="n">
+        <v>7</v>
+      </c>
+      <c r="V96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Redes covalentes y alótropos del carbono</t>
+          <t>Reactivo limitante y en exceso</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4436,29 +5872,30 @@
       <c r="C97" t="n">
         <v>10</v>
       </c>
-      <c r="F97" t="n">
-        <v>8</v>
-      </c>
       <c r="G97" t="n">
         <v>8.5</v>
       </c>
-      <c r="M97" t="n">
-        <v>7</v>
-      </c>
-      <c r="O97" t="n">
-        <v>1</v>
-      </c>
       <c r="P97" t="n">
         <v>1</v>
       </c>
-      <c r="V97" t="n">
-        <v>1</v>
+      <c r="AF97" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Semivida, series de desintegración y residuos radiactivos</t>
+          <t>Redes covalentes y alótropos del carbono</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4469,29 +5906,42 @@
       <c r="C98" t="n">
         <v>10</v>
       </c>
-      <c r="E98" t="n">
-        <v>8</v>
-      </c>
       <c r="F98" t="n">
         <v>8</v>
       </c>
       <c r="G98" t="n">
         <v>8.5</v>
       </c>
-      <c r="N98" t="n">
-        <v>1</v>
+      <c r="M98" t="n">
+        <v>7</v>
       </c>
       <c r="O98" t="n">
         <v>1</v>
       </c>
       <c r="P98" t="n">
         <v>1</v>
+      </c>
+      <c r="V98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Teoría cinética de los gases</t>
+          <t>Semivida, series de desintegración y residuos radiactivos</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4500,31 +5950,38 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E99" t="n">
+        <v>8</v>
+      </c>
+      <c r="F99" t="n">
+        <v>8</v>
       </c>
       <c r="G99" t="n">
-        <v>6</v>
-      </c>
-      <c r="H99" t="n">
-        <v>7</v>
-      </c>
-      <c r="J99" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M99" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="N99" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" t="n">
+        <v>1</v>
       </c>
       <c r="P99" t="n">
         <v>1</v>
       </c>
-      <c r="Q99" t="n">
-        <v>1</v>
-      </c>
-      <c r="S99" t="n">
-        <v>1</v>
-      </c>
-      <c r="V99" t="n">
-        <v>1</v>
+      <c r="AF99" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -4547,9 +6004,6 @@
       <c r="G100" t="n">
         <v>8.5</v>
       </c>
-      <c r="H100" t="n">
-        <v>7</v>
-      </c>
       <c r="M100" t="n">
         <v>7</v>
       </c>
@@ -4559,11 +6013,24 @@
       <c r="P100" t="n">
         <v>1</v>
       </c>
-      <c r="Q100" t="n">
-        <v>1</v>
-      </c>
       <c r="V100" t="n">
         <v>1</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -4604,6 +6071,19 @@
       <c r="V101" t="n">
         <v>1</v>
       </c>
+      <c r="AF101" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4625,11 +6105,24 @@
       <c r="P102" t="n">
         <v>1</v>
       </c>
+      <c r="AF102" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Aminoácidos y estructura de las proteínas</t>
+          <t>Catalizadores</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4643,6 +6136,31 @@
       <c r="D103" t="n">
         <v>6</v>
       </c>
+      <c r="G103" t="n">
+        <v>6</v>
+      </c>
+      <c r="M103" t="n">
+        <v>7</v>
+      </c>
+      <c r="P103" t="n">
+        <v>1</v>
+      </c>
+      <c r="V103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4661,11 +6179,24 @@
       <c r="D104" t="n">
         <v>6</v>
       </c>
+      <c r="AF104" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Modelo mecanocuántico y orbitales atómicos</t>
+          <t>Electrones de valencia y regla del octeto</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4679,11 +6210,30 @@
       <c r="D105" t="n">
         <v>5</v>
       </c>
+      <c r="G105" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Molaridad y unidades químicas de concentración</t>
+          <t>Enlace covalente</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4692,16 +6242,41 @@
         </is>
       </c>
       <c r="C106" t="n">
+        <v>6</v>
+      </c>
+      <c r="D106" t="n">
+        <v>6</v>
+      </c>
+      <c r="F106" t="n">
         <v>8</v>
       </c>
-      <c r="D106" t="n">
-        <v>8</v>
+      <c r="G106" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O106" t="n">
+        <v>1</v>
+      </c>
+      <c r="P106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Números cuánticos</t>
+          <t>Enlace iónico</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4715,11 +6290,36 @@
       <c r="D107" t="n">
         <v>5</v>
       </c>
+      <c r="F107" t="n">
+        <v>8</v>
+      </c>
+      <c r="G107" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O107" t="n">
+        <v>1</v>
+      </c>
+      <c r="P107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Propiedades coligativas</t>
+          <t>Notación y estructuras de Lewis</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4728,16 +6328,35 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D108" t="n">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="G108" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Química de los carbohidratos</t>
+          <t>Geometría molecular (RPECV)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4751,11 +6370,30 @@
       <c r="D109" t="n">
         <v>6</v>
       </c>
+      <c r="G109" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sólidos cristalinos y amorfos</t>
+          <t>Isótopos</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4764,145 +6402,133 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D110" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="G110" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L110" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P110" t="n">
+        <v>1</v>
+      </c>
+      <c r="U110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Agentes oxidantes y reductores</t>
+          <t>Masa molar</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="D111" t="n">
+        <v>8</v>
       </c>
       <c r="F111" t="n">
         <v>8</v>
       </c>
       <c r="G111" t="n">
-        <v>6</v>
-      </c>
-      <c r="H111" t="n">
-        <v>7</v>
-      </c>
-      <c r="I111" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O111" t="n">
+        <v>1</v>
+      </c>
+      <c r="P111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF111" t="n">
         <v>8</v>
       </c>
-      <c r="M111" t="n">
-        <v>7</v>
-      </c>
-      <c r="O111" t="n">
-        <v>1</v>
-      </c>
-      <c r="P111" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>1</v>
-      </c>
-      <c r="R111" t="n">
-        <v>1</v>
-      </c>
-      <c r="V111" t="n">
-        <v>1</v>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Metales, cerámicas y materiales compuestos</t>
+          <t>Modelo mecanocuántico y orbitales atómicos</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>10</v>
-      </c>
-      <c r="E112" t="n">
-        <v>3</v>
-      </c>
-      <c r="F112" t="n">
-        <v>8</v>
-      </c>
-      <c r="G112" t="n">
-        <v>6</v>
-      </c>
-      <c r="H112" t="n">
-        <v>7</v>
-      </c>
-      <c r="M112" t="n">
-        <v>7</v>
-      </c>
-      <c r="N112" t="n">
-        <v>1</v>
-      </c>
-      <c r="O112" t="n">
-        <v>1</v>
-      </c>
-      <c r="P112" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>1</v>
-      </c>
-      <c r="V112" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D112" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Combustión</t>
+          <t>Mol y número de Avogadro</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D113" t="n">
-        <v>7</v>
-      </c>
-      <c r="E113" t="n">
         <v>8</v>
       </c>
       <c r="F113" t="n">
         <v>8</v>
       </c>
       <c r="G113" t="n">
-        <v>3</v>
-      </c>
-      <c r="H113" t="n">
-        <v>3</v>
-      </c>
-      <c r="I113" t="n">
-        <v>5</v>
-      </c>
-      <c r="J113" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L113" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M113" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N113" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="O113" t="n">
         <v>1</v>
@@ -4910,299 +6536,417 @@
       <c r="P113" t="n">
         <v>1</v>
       </c>
-      <c r="Q113" t="n">
-        <v>1</v>
-      </c>
-      <c r="R113" t="n">
-        <v>1</v>
-      </c>
-      <c r="S113" t="n">
-        <v>1</v>
-      </c>
-      <c r="U113" t="n">
-        <v>1</v>
-      </c>
-      <c r="V113" t="n">
-        <v>1</v>
+      <c r="AF113" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Conservación de la masa</t>
+          <t>Molaridad y unidades químicas de concentración</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>10</v>
-      </c>
-      <c r="E114" t="n">
         <v>8</v>
       </c>
-      <c r="F114" t="n">
+      <c r="D114" t="n">
         <v>8</v>
       </c>
-      <c r="G114" t="n">
-        <v>6</v>
-      </c>
-      <c r="H114" t="n">
-        <v>7</v>
-      </c>
-      <c r="I114" t="n">
-        <v>4</v>
-      </c>
-      <c r="J114" t="n">
-        <v>7</v>
-      </c>
-      <c r="L114" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M114" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N114" t="n">
-        <v>1</v>
-      </c>
-      <c r="O114" t="n">
-        <v>1</v>
-      </c>
-      <c r="P114" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q114" t="n">
-        <v>1</v>
-      </c>
-      <c r="R114" t="n">
-        <v>1</v>
-      </c>
-      <c r="S114" t="n">
-        <v>1</v>
-      </c>
-      <c r="U114" t="n">
-        <v>1</v>
-      </c>
-      <c r="V114" t="n">
-        <v>1</v>
+      <c r="AF114" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Indicadores ácido-base</t>
+          <t>Número de oxidación</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="D115" t="n">
+        <v>5</v>
       </c>
       <c r="F115" t="n">
         <v>8</v>
       </c>
-      <c r="G115" t="n">
-        <v>6</v>
-      </c>
-      <c r="H115" t="n">
-        <v>7</v>
-      </c>
-      <c r="J115" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L115" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M115" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O115" t="n">
         <v>1</v>
       </c>
-      <c r="P115" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>1</v>
-      </c>
-      <c r="S115" t="n">
-        <v>1</v>
-      </c>
-      <c r="U115" t="n">
-        <v>1</v>
-      </c>
-      <c r="V115" t="n">
-        <v>1</v>
+      <c r="AF115" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Neutralización y reacciones de los ácidos</t>
+          <t>Números cuánticos</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>9</v>
-      </c>
-      <c r="F116" t="n">
-        <v>8</v>
-      </c>
-      <c r="G116" t="n">
-        <v>3</v>
-      </c>
-      <c r="H116" t="n">
-        <v>7</v>
-      </c>
-      <c r="I116" t="n">
         <v>5</v>
       </c>
-      <c r="J116" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L116" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M116" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O116" t="n">
-        <v>1</v>
-      </c>
-      <c r="P116" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>1</v>
-      </c>
-      <c r="R116" t="n">
-        <v>1</v>
-      </c>
-      <c r="S116" t="n">
-        <v>1</v>
-      </c>
-      <c r="U116" t="n">
-        <v>1</v>
-      </c>
-      <c r="V116" t="n">
-        <v>1</v>
+      <c r="D116" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Oxidación y reducción</t>
+          <t>Polaridad molecular</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="D117" t="n">
+        <v>6</v>
       </c>
       <c r="F117" t="n">
         <v>8</v>
       </c>
-      <c r="G117" t="n">
+      <c r="K117" t="n">
         <v>6</v>
       </c>
-      <c r="H117" t="n">
-        <v>7</v>
-      </c>
-      <c r="I117" t="n">
-        <v>7</v>
-      </c>
-      <c r="L117" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M117" t="n">
-        <v>7</v>
-      </c>
       <c r="O117" t="n">
         <v>1</v>
       </c>
-      <c r="P117" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>1</v>
-      </c>
-      <c r="R117" t="n">
-        <v>1</v>
-      </c>
-      <c r="U117" t="n">
-        <v>1</v>
-      </c>
-      <c r="V117" t="n">
-        <v>1</v>
+      <c r="T117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
+          <t>Propiedades coligativas</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>8</v>
+      </c>
+      <c r="D118" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Sólidos cristalinos y amorfos</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>8</v>
+      </c>
+      <c r="D119" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Agentes oxidantes y reductores</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>10</v>
+      </c>
+      <c r="F120" t="n">
+        <v>8</v>
+      </c>
+      <c r="G120" t="n">
+        <v>6</v>
+      </c>
+      <c r="H120" t="n">
+        <v>7</v>
+      </c>
+      <c r="I120" t="n">
+        <v>8</v>
+      </c>
+      <c r="M120" t="n">
+        <v>7</v>
+      </c>
+      <c r="O120" t="n">
+        <v>1</v>
+      </c>
+      <c r="P120" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>1</v>
+      </c>
+      <c r="R120" t="n">
+        <v>1</v>
+      </c>
+      <c r="V120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Oxidación y reducción</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>10</v>
+      </c>
+      <c r="F121" t="n">
+        <v>8</v>
+      </c>
+      <c r="G121" t="n">
+        <v>6</v>
+      </c>
+      <c r="H121" t="n">
+        <v>7</v>
+      </c>
+      <c r="I121" t="n">
+        <v>7</v>
+      </c>
+      <c r="L121" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M121" t="n">
+        <v>7</v>
+      </c>
+      <c r="O121" t="n">
+        <v>1</v>
+      </c>
+      <c r="P121" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>1</v>
+      </c>
+      <c r="R121" t="n">
+        <v>1</v>
+      </c>
+      <c r="U121" t="n">
+        <v>1</v>
+      </c>
+      <c r="V121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
           <t>Reacciones exotérmicas y endotérmicas</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>tardio</t>
         </is>
       </c>
-      <c r="C118" t="n">
+      <c r="C122" t="n">
         <v>10</v>
       </c>
-      <c r="E118" t="n">
-        <v>7</v>
-      </c>
-      <c r="F118" t="n">
+      <c r="E122" t="n">
+        <v>7</v>
+      </c>
+      <c r="F122" t="n">
         <v>8</v>
       </c>
-      <c r="G118" t="n">
+      <c r="G122" t="n">
         <v>6</v>
       </c>
-      <c r="H118" t="n">
-        <v>7</v>
-      </c>
-      <c r="I118" t="n">
-        <v>7</v>
-      </c>
-      <c r="J118" t="n">
-        <v>7</v>
-      </c>
-      <c r="M118" t="n">
-        <v>7</v>
-      </c>
-      <c r="N118" t="n">
-        <v>1</v>
-      </c>
-      <c r="O118" t="n">
-        <v>1</v>
-      </c>
-      <c r="P118" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>1</v>
-      </c>
-      <c r="R118" t="n">
-        <v>1</v>
-      </c>
-      <c r="S118" t="n">
-        <v>1</v>
-      </c>
-      <c r="V118" t="n">
-        <v>1</v>
+      <c r="H122" t="n">
+        <v>7</v>
+      </c>
+      <c r="I122" t="n">
+        <v>7</v>
+      </c>
+      <c r="J122" t="n">
+        <v>7</v>
+      </c>
+      <c r="M122" t="n">
+        <v>7</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" t="n">
+        <v>1</v>
+      </c>
+      <c r="P122" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>1</v>
+      </c>
+      <c r="R122" t="n">
+        <v>1</v>
+      </c>
+      <c r="S122" t="n">
+        <v>1</v>
+      </c>
+      <c r="V122" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5216,7 +6960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -10185,6 +11929,174 @@
       </c>
       <c r="J118">
         <f>Datos!B118</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <f>Datos!A119</f>
+        <v/>
+      </c>
+      <c r="B119">
+        <f>IF(Datos!C119="","",Datos!C119)</f>
+        <v/>
+      </c>
+      <c r="C119">
+        <f>COUNT(Datos!E119:M119)</f>
+        <v/>
+      </c>
+      <c r="D119">
+        <f>IF(C119=0,"",MEDIAN(Datos!E119:M119))</f>
+        <v/>
+      </c>
+      <c r="E119">
+        <f>COUNT(Datos!W119:AE119)</f>
+        <v/>
+      </c>
+      <c r="F119">
+        <f>IF(OR(B119="",D119=""),"",B119-D119)</f>
+        <v/>
+      </c>
+      <c r="G119">
+        <f>IF(Datos!D119="","",Datos!D119)</f>
+        <v/>
+      </c>
+      <c r="H119">
+        <f>COUNT(Datos!N119:V119)</f>
+        <v/>
+      </c>
+      <c r="I119">
+        <f>IF(B119="",IF(C119&gt;=5,"falta en SV",""),IF(G119="",IF(B119&gt;8,IF(C119&gt;=5,"SV tarde","despues del tramo"),IF(H119&gt;=5,"no retomado en 2-8","previo")),IF(B119&lt;2,"retomado",IF(AND(C119&lt;=1,E119&gt;=3),"solo especializacion",IF(F119="","coherente",IF(F119&lt;=-1.5,"SV adelantado",IF(F119&gt;=2,"SV tarde","coherente")))))))</f>
+        <v/>
+      </c>
+      <c r="J119">
+        <f>Datos!B119</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <f>Datos!A120</f>
+        <v/>
+      </c>
+      <c r="B120">
+        <f>IF(Datos!C120="","",Datos!C120)</f>
+        <v/>
+      </c>
+      <c r="C120">
+        <f>COUNT(Datos!E120:M120)</f>
+        <v/>
+      </c>
+      <c r="D120">
+        <f>IF(C120=0,"",MEDIAN(Datos!E120:M120))</f>
+        <v/>
+      </c>
+      <c r="E120">
+        <f>COUNT(Datos!W120:AE120)</f>
+        <v/>
+      </c>
+      <c r="F120">
+        <f>IF(OR(B120="",D120=""),"",B120-D120)</f>
+        <v/>
+      </c>
+      <c r="G120">
+        <f>IF(Datos!D120="","",Datos!D120)</f>
+        <v/>
+      </c>
+      <c r="H120">
+        <f>COUNT(Datos!N120:V120)</f>
+        <v/>
+      </c>
+      <c r="I120">
+        <f>IF(B120="",IF(C120&gt;=5,"falta en SV",""),IF(G120="",IF(B120&gt;8,IF(C120&gt;=5,"SV tarde","despues del tramo"),IF(H120&gt;=5,"no retomado en 2-8","previo")),IF(B120&lt;2,"retomado",IF(AND(C120&lt;=1,E120&gt;=3),"solo especializacion",IF(F120="","coherente",IF(F120&lt;=-1.5,"SV adelantado",IF(F120&gt;=2,"SV tarde","coherente")))))))</f>
+        <v/>
+      </c>
+      <c r="J120">
+        <f>Datos!B120</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <f>Datos!A121</f>
+        <v/>
+      </c>
+      <c r="B121">
+        <f>IF(Datos!C121="","",Datos!C121)</f>
+        <v/>
+      </c>
+      <c r="C121">
+        <f>COUNT(Datos!E121:M121)</f>
+        <v/>
+      </c>
+      <c r="D121">
+        <f>IF(C121=0,"",MEDIAN(Datos!E121:M121))</f>
+        <v/>
+      </c>
+      <c r="E121">
+        <f>COUNT(Datos!W121:AE121)</f>
+        <v/>
+      </c>
+      <c r="F121">
+        <f>IF(OR(B121="",D121=""),"",B121-D121)</f>
+        <v/>
+      </c>
+      <c r="G121">
+        <f>IF(Datos!D121="","",Datos!D121)</f>
+        <v/>
+      </c>
+      <c r="H121">
+        <f>COUNT(Datos!N121:V121)</f>
+        <v/>
+      </c>
+      <c r="I121">
+        <f>IF(B121="",IF(C121&gt;=5,"falta en SV",""),IF(G121="",IF(B121&gt;8,IF(C121&gt;=5,"SV tarde","despues del tramo"),IF(H121&gt;=5,"no retomado en 2-8","previo")),IF(B121&lt;2,"retomado",IF(AND(C121&lt;=1,E121&gt;=3),"solo especializacion",IF(F121="","coherente",IF(F121&lt;=-1.5,"SV adelantado",IF(F121&gt;=2,"SV tarde","coherente")))))))</f>
+        <v/>
+      </c>
+      <c r="J121">
+        <f>Datos!B121</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <f>Datos!A122</f>
+        <v/>
+      </c>
+      <c r="B122">
+        <f>IF(Datos!C122="","",Datos!C122)</f>
+        <v/>
+      </c>
+      <c r="C122">
+        <f>COUNT(Datos!E122:M122)</f>
+        <v/>
+      </c>
+      <c r="D122">
+        <f>IF(C122=0,"",MEDIAN(Datos!E122:M122))</f>
+        <v/>
+      </c>
+      <c r="E122">
+        <f>COUNT(Datos!W122:AE122)</f>
+        <v/>
+      </c>
+      <c r="F122">
+        <f>IF(OR(B122="",D122=""),"",B122-D122)</f>
+        <v/>
+      </c>
+      <c r="G122">
+        <f>IF(Datos!D122="","",Datos!D122)</f>
+        <v/>
+      </c>
+      <c r="H122">
+        <f>COUNT(Datos!N122:V122)</f>
+        <v/>
+      </c>
+      <c r="I122">
+        <f>IF(B122="",IF(C122&gt;=5,"falta en SV",""),IF(G122="",IF(B122&gt;8,IF(C122&gt;=5,"SV tarde","despues del tramo"),IF(H122&gt;=5,"no retomado en 2-8","previo")),IF(B122&lt;2,"retomado",IF(AND(C122&lt;=1,E122&gt;=3),"solo especializacion",IF(F122="","coherente",IF(F122&lt;=-1.5,"SV adelantado",IF(F122&gt;=2,"SV tarde","coherente")))))))</f>
+        <v/>
+      </c>
+      <c r="J122">
+        <f>Datos!B122</f>
         <v/>
       </c>
     </row>
@@ -10199,7 +12111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -10224,7 +12136,7 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIF(Datos!B2:B118,A2)</f>
+        <f>COUNTIF(Datos!B2:B122,A2)</f>
         <v/>
       </c>
     </row>
@@ -10235,7 +12147,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(Datos!B2:B118,A3)</f>
+        <f>COUNTIF(Datos!B2:B122,A3)</f>
         <v/>
       </c>
     </row>
@@ -10246,7 +12158,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(Datos!B2:B118,A4)</f>
+        <f>COUNTIF(Datos!B2:B122,A4)</f>
         <v/>
       </c>
     </row>
@@ -10257,7 +12169,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(Datos!B2:B118,A5)</f>
+        <f>COUNTIF(Datos!B2:B122,A5)</f>
         <v/>
       </c>
     </row>
@@ -10268,7 +12180,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(Datos!B2:B118,A6)</f>
+        <f>COUNTIF(Datos!B2:B122,A6)</f>
         <v/>
       </c>
     </row>
@@ -10279,18 +12191,29 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF(Datos!B2:B118,A7)</f>
+        <f>COUNTIF(Datos!B2:B122,A7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>COUNTIF(Datos!B2:B122,A8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B8">
-        <f>SUM(B2:B7)</f>
+      <c r="B9">
+        <f>SUM(B2:B8)</f>
         <v/>
       </c>
     </row>

--- a/internacional/2_8/Contraste_quimica.xlsx
+++ b/internacional/2_8/Contraste_quimica.xlsx
@@ -995,7 +995,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fuerzas intermoleculares y propiedades físicas</t>
+          <t>Distribución electrónica por niveles (modelo de capas)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>8</v>
@@ -1015,8 +1015,8 @@
       <c r="G7" t="n">
         <v>8.5</v>
       </c>
-      <c r="H7" t="n">
-        <v>7</v>
+      <c r="K7" t="n">
+        <v>8</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1024,14 +1024,11 @@
       <c r="P7" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z7" t="n">
+      <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -1040,14 +1037,14 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Iones</t>
+          <t>Fuerzas intermoleculares y propiedades físicas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,10 +1053,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>8</v>
@@ -1067,16 +1064,7 @@
       <c r="G8" t="n">
         <v>8.5</v>
       </c>
-      <c r="I8" t="n">
-        <v>8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>7</v>
-      </c>
-      <c r="L8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="H8" t="n">
         <v>7</v>
       </c>
       <c r="O8" t="n">
@@ -1085,36 +1073,30 @@
       <c r="P8" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
         <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reutilización y reciclaje de materiales</t>
+          <t>Iones</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1123,25 +1105,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
         <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
-      </c>
-      <c r="H9" t="n">
-        <v>7</v>
+        <v>8.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
         <v>7.5</v>
@@ -1155,26 +1134,20 @@
       <c r="P9" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
       <c r="U9" t="n">
         <v>1</v>
       </c>
       <c r="V9" t="n">
         <v>1</v>
       </c>
-      <c r="Z9" t="n">
-        <v>1</v>
-      </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -1190,7 +1163,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mezclas homogéneas y heterogéneas</t>
+          <t>Masa atómica relativa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1199,74 +1172,38 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F10" t="n">
         <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="L10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>7</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
         <v>5</v>
       </c>
-      <c r="M10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2</v>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -1278,7 +1215,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Evolución de los modelos atómicos</t>
+          <t>Reutilización y reciclaje de materiales</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1287,19 +1224,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
         <v>8</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
       </c>
+      <c r="H11" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.5</v>
+      </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>7.5</v>
@@ -1307,12 +1250,18 @@
       <c r="M11" t="n">
         <v>7</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>1</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
@@ -1322,8 +1271,11 @@
       <c r="V11" t="n">
         <v>1</v>
       </c>
+      <c r="Z11" t="n">
+        <v>1</v>
+      </c>
       <c r="AF11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -1339,7 +1291,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Moléculas y fórmulas químicas</t>
+          <t>Mezclas homogéneas y heterogéneas</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1348,37 +1300,37 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="n">
         <v>5</v>
       </c>
-      <c r="D12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E12" t="n">
-        <v>7</v>
-      </c>
-      <c r="F12" t="n">
-        <v>8</v>
-      </c>
       <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
         <v>6</v>
       </c>
-      <c r="H12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" t="n">
-        <v>7</v>
-      </c>
       <c r="J12" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K12" t="n">
         <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
@@ -1411,7 +1363,7 @@
         <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -1427,7 +1379,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Propiedades periódicas</t>
+          <t>Evolución de los modelos atómicos</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1441,25 +1393,34 @@
       <c r="D13" t="n">
         <v>5</v>
       </c>
+      <c r="E13" t="n">
+        <v>8</v>
+      </c>
       <c r="G13" t="n">
         <v>6</v>
       </c>
       <c r="K13" t="n">
         <v>8</v>
       </c>
+      <c r="L13" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M13" t="n">
         <v>7</v>
       </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
       <c r="P13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
       <c r="V13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z13" t="n">
         <v>1</v>
       </c>
       <c r="AF13" t="n">
@@ -1479,7 +1440,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Propiedades singulares del agua</t>
+          <t>Moléculas y fórmulas químicas</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1488,13 +1449,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
         <v>6</v>
@@ -1503,11 +1467,23 @@
         <v>7</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
       </c>
       <c r="K14" t="n">
         <v>6</v>
       </c>
+      <c r="L14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
       <c r="O14" t="n">
         <v>1</v>
       </c>
@@ -1520,11 +1496,23 @@
       <c r="R14" t="n">
         <v>1</v>
       </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1</v>
+      </c>
       <c r="AF14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
@@ -1540,7 +1528,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Química descriptiva de los elementos</t>
+          <t>Propiedades periódicas</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1554,25 +1542,19 @@
       <c r="D15" t="n">
         <v>5</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" t="n">
         <v>8</v>
       </c>
-      <c r="G15" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>7</v>
-      </c>
       <c r="M15" t="n">
         <v>7</v>
       </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
       <c r="P15" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="V15" t="n">
@@ -1598,7 +1580,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Reacción química y sus evidencias</t>
+          <t>Propiedades singulares del agua</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1607,40 +1589,25 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
         <v>5</v>
       </c>
-      <c r="F16" t="n">
-        <v>8</v>
-      </c>
       <c r="G16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" t="n">
         <v>3</v>
       </c>
-      <c r="H16" t="n">
-        <v>5</v>
-      </c>
-      <c r="I16" t="n">
-        <v>5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.5</v>
-      </c>
       <c r="K16" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -1654,20 +1621,11 @@
       <c r="R16" t="n">
         <v>1</v>
       </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1</v>
-      </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
@@ -1683,7 +1641,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Métodos físicos de separación de mezclas</t>
+          <t>Química descriptiva de los elementos</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1692,70 +1650,40 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
         <v>5</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K17" t="n">
-        <v>6</v>
-      </c>
-      <c r="L17" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
@@ -1771,7 +1699,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Organización de la tabla periódica</t>
+          <t>Reacción química y sus evidencias</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1780,31 +1708,40 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
         <v>5</v>
       </c>
       <c r="F18" t="n">
         <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
         <v>7.5</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
@@ -1815,6 +1752,9 @@
       <c r="Q18" t="n">
         <v>1</v>
       </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
@@ -1827,11 +1767,8 @@
       <c r="V18" t="n">
         <v>1</v>
       </c>
-      <c r="Z18" t="n">
-        <v>1</v>
-      </c>
       <c r="AF18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
@@ -1847,7 +1784,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Calidad y tratamiento del agua</t>
+          <t>Métodos físicos de separación de mezclas</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1856,28 +1793,40 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
       </c>
       <c r="F19" t="n">
         <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
         <v>2</v>
       </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.5</v>
+      </c>
       <c r="K19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
@@ -1888,6 +1837,12 @@
       <c r="Q19" t="n">
         <v>1</v>
       </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
@@ -1897,8 +1852,11 @@
       <c r="V19" t="n">
         <v>1</v>
       </c>
+      <c r="Z19" t="n">
+        <v>1</v>
+      </c>
       <c r="AF19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
@@ -1914,35 +1872,38 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ácidos y bases: propiedades</t>
+          <t>Solubilidad y disoluciones saturadas</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
         <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J20" t="n">
         <v>4.5</v>
       </c>
+      <c r="K20" t="n">
+        <v>6</v>
+      </c>
       <c r="L20" t="n">
         <v>7.5</v>
       </c>
@@ -1964,6 +1925,9 @@
       <c r="S20" t="n">
         <v>1</v>
       </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
       <c r="U20" t="n">
         <v>1</v>
       </c>
@@ -1971,11 +1935,11 @@
         <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
@@ -1987,49 +1951,40 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Organización de la tabla periódica</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" t="n">
         <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L21" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="M21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
@@ -2040,9 +1995,6 @@
       <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
@@ -2059,87 +2011,90 @@
         <v>1</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Combustibles fósiles y biocombustibles</t>
+          <t>Calidad y tratamiento del agua</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>7</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5</v>
+      </c>
+      <c r="M22" t="n">
+        <v>7</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="n">
         <v>3</v>
       </c>
-      <c r="K22" t="n">
-        <v>4</v>
-      </c>
-      <c r="M22" t="n">
-        <v>7</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>7</v>
-      </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Conservación de la masa</t>
+          <t>Ácidos y bases: propiedades</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2152,9 +2107,6 @@
       </c>
       <c r="D23" t="n">
         <v>7</v>
-      </c>
-      <c r="E23" t="n">
-        <v>8</v>
       </c>
       <c r="F23" t="n">
         <v>8</v>
@@ -2166,19 +2118,16 @@
         <v>7</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="L23" t="n">
         <v>7.5</v>
       </c>
       <c r="M23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
@@ -2202,7 +2151,7 @@
         <v>1</v>
       </c>
       <c r="AF23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
@@ -2211,14 +2160,14 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Disolución y rapidez de disolución</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2227,32 +2176,44 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
         <v>2</v>
       </c>
       <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K24" t="n">
         <v>4</v>
       </c>
-      <c r="J24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K24" t="n">
-        <v>6</v>
-      </c>
       <c r="L24" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M24" t="n">
         <v>2.5</v>
       </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
       <c r="P24" t="n">
         <v>1</v>
       </c>
@@ -2274,8 +2235,11 @@
       <c r="V24" t="n">
         <v>1</v>
       </c>
+      <c r="Z24" t="n">
+        <v>1</v>
+      </c>
       <c r="AF24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
@@ -2291,7 +2255,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ecuación química y su balanceo</t>
+          <t>Combustibles fósiles y biocombustibles</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2300,13 +2264,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
-      </c>
-      <c r="E25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
         <v>8</v>
@@ -2315,23 +2276,14 @@
         <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
-      </c>
-      <c r="I25" t="n">
-        <v>7</v>
-      </c>
-      <c r="J25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L25" t="n">
-        <v>7.5</v>
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4</v>
       </c>
       <c r="M25" t="n">
         <v>7</v>
       </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
       <c r="O25" t="n">
         <v>1</v>
       </c>
@@ -2341,13 +2293,7 @@
       <c r="Q25" t="n">
         <v>1</v>
       </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="T25" t="n">
         <v>1</v>
       </c>
       <c r="V25" t="n">
@@ -2373,7 +2319,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Escala de pH</t>
+          <t>Combustión</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2386,15 +2332,18 @@
       </c>
       <c r="D26" t="n">
         <v>7</v>
+      </c>
+      <c r="E26" t="n">
+        <v>8</v>
       </c>
       <c r="F26" t="n">
         <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
         <v>5</v>
@@ -2406,7 +2355,10 @@
         <v>7.5</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
@@ -2429,6 +2381,9 @@
       <c r="V26" t="n">
         <v>1</v>
       </c>
+      <c r="Z26" t="n">
+        <v>1</v>
+      </c>
       <c r="AF26" t="n">
         <v>7</v>
       </c>
@@ -2439,14 +2394,14 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Estados de la materia</t>
+          <t>Composición del aire y contaminantes atmosféricos</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2455,41 +2410,26 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
         <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H27" t="n">
         <v>2</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
         <v>2.5</v>
       </c>
-      <c r="K27" t="n">
-        <v>4</v>
-      </c>
-      <c r="L27" t="n">
-        <v>4</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
       <c r="O27" t="n">
         <v>1</v>
       </c>
@@ -2505,24 +2445,12 @@
       <c r="S27" t="n">
         <v>1</v>
       </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1</v>
-      </c>
       <c r="AF27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -2534,7 +2462,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Estequiometría</t>
+          <t>Conservación de la masa</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2543,37 +2471,61 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="n">
         <v>8</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H28" t="n">
+        <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
         <v>7</v>
       </c>
+      <c r="L28" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
       <c r="P28" t="n">
         <v>1</v>
       </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
       <c r="R28" t="n">
         <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
       <c r="AF28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
@@ -2582,14 +2534,14 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Indicadores ácido-base</t>
+          <t>Disolución y rapidez de disolución</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2598,38 +2550,47 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
-      </c>
-      <c r="F29" t="n">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
       </c>
       <c r="J29" t="n">
         <v>4.5</v>
       </c>
+      <c r="K29" t="n">
+        <v>6</v>
+      </c>
       <c r="L29" t="n">
         <v>7.5</v>
       </c>
       <c r="M29" t="n">
         <v>2.5</v>
       </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
       <c r="P29" t="n">
         <v>1</v>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
       <c r="U29" t="n">
         <v>1</v>
       </c>
@@ -2637,23 +2598,23 @@
         <v>1</v>
       </c>
       <c r="AF29" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Materia y materiales</t>
+          <t>Ecuación química y su balanceo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2662,37 +2623,34 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K30" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="M30" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="N30" t="n">
         <v>1</v>
@@ -2712,17 +2670,17 @@
       <c r="S30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" t="n">
-        <v>1</v>
-      </c>
       <c r="U30" t="n">
         <v>1</v>
       </c>
       <c r="V30" t="n">
         <v>1</v>
       </c>
+      <c r="Z30" t="n">
+        <v>1</v>
+      </c>
       <c r="AF30" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
@@ -2738,7 +2696,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>Escala de pH</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2747,13 +2705,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
-      </c>
-      <c r="E31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
@@ -2765,22 +2720,16 @@
         <v>7</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J31" t="n">
-        <v>7</v>
-      </c>
-      <c r="K31" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="L31" t="n">
         <v>7.5</v>
       </c>
       <c r="M31" t="n">
-        <v>7</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
@@ -2797,20 +2746,14 @@
       <c r="S31" t="n">
         <v>1</v>
       </c>
-      <c r="T31" t="n">
-        <v>1</v>
-      </c>
       <c r="U31" t="n">
         <v>1</v>
       </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
-      <c r="Z31" t="n">
-        <v>1</v>
-      </c>
       <c r="AF31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
@@ -2826,7 +2769,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Neutralización y reacciones de los ácidos</t>
+          <t>Estados de la materia</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2835,28 +2778,40 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
       </c>
       <c r="F32" t="n">
         <v>8</v>
       </c>
       <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
         <v>3</v>
       </c>
-      <c r="H32" t="n">
-        <v>7</v>
-      </c>
-      <c r="I32" t="n">
-        <v>5</v>
-      </c>
       <c r="J32" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4</v>
       </c>
       <c r="L32" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M32" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
@@ -2873,6 +2828,9 @@
       <c r="S32" t="n">
         <v>1</v>
       </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
       <c r="U32" t="n">
         <v>1</v>
       </c>
@@ -2883,23 +2841,23 @@
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Propiedades físicas de los materiales</t>
+          <t>Estequiometría</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2908,40 +2866,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
-      </c>
-      <c r="H33" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K33" t="n">
-        <v>4</v>
-      </c>
-      <c r="L33" t="n">
-        <v>3</v>
-      </c>
-      <c r="M33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O33" t="n">
         <v>1</v>
@@ -2949,29 +2889,14 @@
       <c r="P33" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
       <c r="R33" t="n">
         <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
       </c>
-      <c r="T33" t="n">
-        <v>1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1</v>
-      </c>
       <c r="AF33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
@@ -2987,7 +2912,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sustancias puras: elementos y compuestos</t>
+          <t>Indicadores ácido-base</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2996,13 +2921,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
-      </c>
-      <c r="D34" t="n">
-        <v>5</v>
-      </c>
-      <c r="E34" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F34" t="n">
         <v>8</v>
@@ -3013,14 +2932,8 @@
       <c r="H34" t="n">
         <v>7</v>
       </c>
-      <c r="I34" t="n">
-        <v>6</v>
-      </c>
       <c r="J34" t="n">
-        <v>7</v>
-      </c>
-      <c r="K34" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="L34" t="n">
         <v>7.5</v>
@@ -3028,9 +2941,6 @@
       <c r="M34" t="n">
         <v>2.5</v>
       </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
       <c r="O34" t="n">
         <v>1</v>
       </c>
@@ -3040,30 +2950,21 @@
       <c r="Q34" t="n">
         <v>1</v>
       </c>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
       <c r="S34" t="n">
         <v>1</v>
       </c>
-      <c r="T34" t="n">
-        <v>1</v>
-      </c>
       <c r="U34" t="n">
         <v>1</v>
       </c>
       <c r="V34" t="n">
         <v>1</v>
       </c>
-      <c r="Z34" t="n">
-        <v>1</v>
-      </c>
       <c r="AF34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
@@ -3075,7 +2976,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Clasificación de las reacciones químicas</t>
+          <t>Materia y materiales</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3084,25 +2985,40 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
       </c>
       <c r="F35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
         <v>8</v>
       </c>
-      <c r="G35" t="n">
-        <v>6</v>
-      </c>
-      <c r="H35" t="n">
-        <v>7</v>
-      </c>
-      <c r="I35" t="n">
-        <v>6</v>
+      <c r="J35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4</v>
       </c>
       <c r="L35" t="n">
-        <v>7.5</v>
+        <v>3</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
@@ -3116,11 +3032,20 @@
       <c r="R35" t="n">
         <v>1</v>
       </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
       <c r="U35" t="n">
         <v>1</v>
       </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
       <c r="AF35" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
@@ -3136,22 +3061,40 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Aminoácidos y estructura de las proteínas</t>
+          <t>Minerales: composición y estructura cristalina</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7</v>
+      </c>
+      <c r="F36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>7</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
@@ -3160,26 +3103,29 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Metales, cerámicas y materiales compuestos</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="D37" t="n">
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" t="n">
         <v>8</v>
@@ -3190,6 +3136,18 @@
       <c r="H37" t="n">
         <v>7</v>
       </c>
+      <c r="I37" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>7</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4</v>
+      </c>
+      <c r="L37" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M37" t="n">
         <v>7</v>
       </c>
@@ -3205,6 +3163,18 @@
       <c r="Q37" t="n">
         <v>1</v>
       </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
       <c r="V37" t="n">
         <v>1</v>
       </c>
@@ -3212,28 +3182,28 @@
         <v>1</v>
       </c>
       <c r="AF37" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Combustión</t>
+          <t>Oxidación y corrosión de los metales</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3241,15 +3211,6 @@
       </c>
       <c r="D38" t="n">
         <v>7</v>
-      </c>
-      <c r="E38" t="n">
-        <v>8</v>
-      </c>
-      <c r="F38" t="n">
-        <v>8</v>
-      </c>
-      <c r="G38" t="n">
-        <v>3</v>
       </c>
       <c r="H38" t="n">
         <v>3</v>
@@ -3257,44 +3218,20 @@
       <c r="I38" t="n">
         <v>5</v>
       </c>
-      <c r="J38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L38" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M38" t="n">
         <v>2.5</v>
       </c>
-      <c r="N38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1</v>
-      </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
       </c>
-      <c r="S38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
       <c r="V38" t="n">
         <v>1</v>
       </c>
-      <c r="Z38" t="n">
-        <v>1</v>
-      </c>
       <c r="AF38" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
@@ -3303,63 +3240,51 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Composición del aire y contaminantes atmosféricos</t>
+          <t>Proceso de disolución y solvatación</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
-      </c>
-      <c r="F39" t="n">
+        <v>7</v>
+      </c>
+      <c r="H39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K39" t="n">
+        <v>6</v>
+      </c>
+      <c r="M39" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="n">
         <v>8</v>
       </c>
-      <c r="G39" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H39" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" t="n">
-        <v>5</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>7</v>
-      </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
@@ -3371,149 +3296,329 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Composición porcentual y fórmulas empírica y molecular</t>
+          <t>Propiedades físicas de los materiales</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" t="n">
         <v>6</v>
       </c>
-      <c r="D40" t="n">
-        <v>6</v>
-      </c>
-      <c r="G40" t="n">
-        <v>8.5</v>
+      <c r="J40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3</v>
+      </c>
+      <c r="M40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
       </c>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1</v>
+      </c>
       <c r="AF40" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Configuración electrónica por orbitales</t>
+          <t>Propiedades físicas y químicas</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="n">
+        <v>6</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K41" t="n">
+        <v>8</v>
+      </c>
+      <c r="L41" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
       </c>
       <c r="AF41" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Diagramas de fases</t>
+          <t>Sustancias puras: elementos y compuestos</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" t="n">
         <v>6</v>
       </c>
-      <c r="D42" t="n">
+      <c r="F42" t="n">
+        <v>8</v>
+      </c>
+      <c r="G42" t="n">
         <v>6</v>
       </c>
+      <c r="H42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I42" t="n">
+        <v>6</v>
+      </c>
+      <c r="J42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K42" t="n">
+        <v>6</v>
+      </c>
+      <c r="L42" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1</v>
+      </c>
       <c r="AF42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mezclas de gases, difusión y gases reales</t>
+          <t>Clasificación de las reacciones químicas</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C43" t="n">
+        <v>6</v>
+      </c>
+      <c r="D43" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" t="n">
         <v>8</v>
       </c>
-      <c r="D43" t="n">
-        <v>8</v>
-      </c>
-      <c r="J43" t="n">
-        <v>7</v>
+      <c r="G43" t="n">
+        <v>6</v>
+      </c>
+      <c r="H43" t="n">
+        <v>7</v>
+      </c>
+      <c r="I43" t="n">
+        <v>6</v>
       </c>
       <c r="L43" t="n">
         <v>7.5</v>
       </c>
-      <c r="S43" t="n">
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" t="n">
         <v>1</v>
       </c>
       <c r="U43" t="n">
         <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Distribución electrónica por niveles (modelo de capas)</t>
+          <t>Procesos de la industria química</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3522,32 +3627,32 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
-      </c>
-      <c r="F44" t="n">
         <v>8</v>
       </c>
       <c r="G44" t="n">
         <v>8.5</v>
       </c>
       <c r="K44" t="n">
+        <v>6</v>
+      </c>
+      <c r="M44" t="n">
+        <v>7</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="n">
         <v>8</v>
       </c>
-      <c r="O44" t="n">
-        <v>1</v>
-      </c>
-      <c r="P44" t="n">
-        <v>1</v>
-      </c>
-      <c r="T44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>5</v>
-      </c>
       <c r="AG44" t="inlineStr">
         <is>
           <t>sin_referente</t>
@@ -3555,14 +3660,14 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Energía de activación y perfil energético</t>
+          <t>Tipo de enlace y propiedades de las sustancias</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3571,19 +3676,37 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="F45" t="n">
+        <v>8</v>
       </c>
       <c r="G45" t="n">
         <v>6</v>
       </c>
+      <c r="H45" t="n">
+        <v>7</v>
+      </c>
+      <c r="M45" t="n">
+        <v>7</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
       <c r="P45" t="n">
         <v>1</v>
       </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
       <c r="AF45" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
@@ -3592,36 +3715,39 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Enlace metálico</t>
+          <t>Agentes oxidantes y reductores</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
-      </c>
-      <c r="D46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F46" t="n">
         <v>8</v>
       </c>
       <c r="G46" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H46" t="n">
         <v>7</v>
       </c>
+      <c r="I46" t="n">
+        <v>8</v>
+      </c>
+      <c r="M46" t="n">
+        <v>7</v>
+      </c>
       <c r="O46" t="n">
         <v>1</v>
       </c>
@@ -3631,67 +3757,49 @@
       <c r="Q46" t="n">
         <v>1</v>
       </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
       <c r="AF46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Enlace químico</t>
+          <t>Aminoácidos y estructura de las proteínas</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
-      </c>
-      <c r="F47" t="n">
-        <v>8</v>
-      </c>
-      <c r="G47" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H47" t="n">
-        <v>7</v>
-      </c>
-      <c r="L47" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AF47" t="n">
         <v>10</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
@@ -3703,19 +3811,16 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Equilibrio químico dinámico</t>
+          <t>Autoionización del agua, Kw y cálculo de pH</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
-      </c>
-      <c r="D48" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G48" t="n">
         <v>8.5</v>
@@ -3734,7 +3839,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
@@ -3746,40 +3851,34 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Fuerzas intermoleculares</t>
+          <t>Celdas galvánicas</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>6</v>
-      </c>
-      <c r="E49" t="n">
-        <v>6</v>
-      </c>
-      <c r="G49" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J49" t="n">
-        <v>7</v>
-      </c>
-      <c r="N49" t="n">
-        <v>1</v>
-      </c>
-      <c r="P49" t="n">
-        <v>1</v>
-      </c>
-      <c r="S49" t="n">
+        <v>4</v>
+      </c>
+      <c r="I49" t="n">
+        <v>5</v>
+      </c>
+      <c r="M49" t="n">
+        <v>7</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" t="n">
         <v>1</v>
       </c>
       <c r="AF49" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
@@ -3788,61 +3887,91 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Fundamentos de la reactividad orgánica</t>
+          <t>Metales, cerámicas y materiales compuestos</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
-      </c>
-      <c r="D50" t="n">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="E50" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" t="n">
+        <v>6</v>
+      </c>
+      <c r="H50" t="n">
+        <v>7</v>
+      </c>
+      <c r="M50" t="n">
+        <v>7</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1</v>
       </c>
       <c r="AF50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Masa atómica relativa</t>
+          <t>Cromatografía</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
-      </c>
-      <c r="D51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G51" t="n">
         <v>8.5</v>
       </c>
+      <c r="H51" t="n">
+        <v>7</v>
+      </c>
       <c r="L51" t="n">
         <v>7.5</v>
       </c>
@@ -3852,66 +3981,48 @@
       <c r="P51" t="n">
         <v>1</v>
       </c>
+      <c r="Q51" t="n">
+        <v>1</v>
+      </c>
       <c r="U51" t="n">
         <v>1</v>
       </c>
       <c r="V51" t="n">
         <v>1</v>
       </c>
-      <c r="Z51" t="n">
-        <v>1</v>
-      </c>
       <c r="AF51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Minerales: composición y estructura cristalina</t>
+          <t>Diagramas de fases</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
-      </c>
-      <c r="E52" t="n">
-        <v>7</v>
-      </c>
-      <c r="F52" t="n">
-        <v>8</v>
-      </c>
-      <c r="H52" t="n">
-        <v>7</v>
-      </c>
-      <c r="N52" t="n">
-        <v>1</v>
-      </c>
-      <c r="O52" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AF52" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
@@ -3920,47 +4031,41 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Compuestos inorgánicos: funciones y nomenclatura</t>
+          <t>Mezclas de gases, difusión y gases reales</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
-      </c>
-      <c r="F53" t="n">
         <v>8</v>
       </c>
-      <c r="G53" t="n">
-        <v>6</v>
-      </c>
-      <c r="M53" t="n">
-        <v>7</v>
-      </c>
-      <c r="O53" t="n">
-        <v>1</v>
-      </c>
-      <c r="P53" t="n">
-        <v>1</v>
-      </c>
-      <c r="V53" t="n">
+      <c r="J53" t="n">
+        <v>7</v>
+      </c>
+      <c r="L53" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
         <v>1</v>
       </c>
       <c r="AF53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
@@ -3969,45 +4074,36 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Nomenclatura orgánica IUPAC</t>
+          <t>Ecuación de los gases ideales y volumen molar</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
-      </c>
-      <c r="D54" t="n">
-        <v>7</v>
-      </c>
-      <c r="G54" t="n">
-        <v>6</v>
-      </c>
-      <c r="M54" t="n">
-        <v>7</v>
-      </c>
-      <c r="P54" t="n">
-        <v>1</v>
-      </c>
-      <c r="V54" t="n">
+        <v>10</v>
+      </c>
+      <c r="F54" t="n">
+        <v>8</v>
+      </c>
+      <c r="O54" t="n">
         <v>1</v>
       </c>
       <c r="AF54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH54" t="inlineStr">
@@ -4019,44 +4115,29 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Oxidación y corrosión de los metales</t>
+          <t>Ecuaciones y reacciones nucleares</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>7</v>
-      </c>
-      <c r="D55" t="n">
-        <v>7</v>
-      </c>
-      <c r="H55" t="n">
-        <v>3</v>
-      </c>
-      <c r="I55" t="n">
-        <v>5</v>
-      </c>
-      <c r="M55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>1</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1</v>
-      </c>
-      <c r="V55" t="n">
+        <v>10</v>
+      </c>
+      <c r="L55" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="U55" t="n">
         <v>1</v>
       </c>
       <c r="AF55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH55" t="inlineStr">
@@ -4068,74 +4149,71 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Proceso de disolución y solvatación</t>
+          <t>El carbono y las moléculas orgánicas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
-      </c>
-      <c r="D56" t="n">
-        <v>7</v>
-      </c>
-      <c r="H56" t="n">
-        <v>7</v>
-      </c>
-      <c r="K56" t="n">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="F56" t="n">
+        <v>8</v>
+      </c>
+      <c r="G56" t="n">
+        <v>8.5</v>
       </c>
       <c r="M56" t="n">
         <v>7</v>
       </c>
-      <c r="Q56" t="n">
-        <v>1</v>
-      </c>
-      <c r="T56" t="n">
+      <c r="O56" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" t="n">
         <v>1</v>
       </c>
       <c r="V56" t="n">
         <v>1</v>
       </c>
       <c r="AF56" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Procesos de la industria química</t>
+          <t>Electrólisis y celdas electrolíticas</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
-      </c>
-      <c r="D57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G57" t="n">
         <v>8.5</v>
       </c>
-      <c r="K57" t="n">
-        <v>6</v>
+      <c r="H57" t="n">
+        <v>7</v>
+      </c>
+      <c r="I57" t="n">
+        <v>8</v>
       </c>
       <c r="M57" t="n">
         <v>7</v>
@@ -4143,72 +4221,54 @@
       <c r="P57" t="n">
         <v>1</v>
       </c>
-      <c r="T57" t="n">
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
         <v>1</v>
       </c>
       <c r="V57" t="n">
         <v>1</v>
       </c>
       <c r="AF57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Propiedades físicas y químicas</t>
+          <t>Electrolitos fuertes y débiles</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F58" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
-      </c>
-      <c r="H58" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="I58" t="n">
-        <v>6</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K58" t="n">
         <v>8</v>
       </c>
-      <c r="L58" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M58" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N58" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O58" t="n">
         <v>1</v>
@@ -4216,54 +4276,48 @@
       <c r="P58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>1</v>
-      </c>
       <c r="R58" t="n">
         <v>1</v>
       </c>
-      <c r="S58" t="n">
-        <v>1</v>
-      </c>
-      <c r="T58" t="n">
-        <v>1</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1</v>
-      </c>
       <c r="V58" t="n">
         <v>1</v>
       </c>
       <c r="AF58" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Química de los carbohidratos</t>
+          <t>Energía de activación y perfil energético</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C59" t="n">
+        <v>5</v>
+      </c>
+      <c r="D59" t="n">
+        <v>5</v>
+      </c>
+      <c r="G59" t="n">
         <v>6</v>
       </c>
-      <c r="D59" t="n">
-        <v>6</v>
+      <c r="P59" t="n">
+        <v>1</v>
       </c>
       <c r="AF59" t="n">
         <v>10</v>
@@ -4282,24 +4336,21 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Radiactividad y emisiones nucleares</t>
+          <t>Energía de enlace</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
-      </c>
-      <c r="D60" t="n">
-        <v>5</v>
-      </c>
-      <c r="E60" t="n">
-        <v>8</v>
-      </c>
-      <c r="N60" t="n">
+        <v>10</v>
+      </c>
+      <c r="G60" t="n">
+        <v>6</v>
+      </c>
+      <c r="P60" t="n">
         <v>1</v>
       </c>
       <c r="AF60" t="n">
@@ -4307,7 +4358,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH60" t="inlineStr">
@@ -4319,80 +4370,80 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Factores que afectan la rapidez de reacción</t>
+          <t>Entalpía de reacción y ecuaciones termoquímicas</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
-      </c>
-      <c r="D61" t="n">
-        <v>6</v>
-      </c>
-      <c r="F61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G61" t="n">
-        <v>6</v>
-      </c>
-      <c r="H61" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I61" t="n">
         <v>7</v>
       </c>
       <c r="M61" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O61" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P61" t="n">
         <v>1</v>
       </c>
-      <c r="Q61" t="n">
+      <c r="R61" t="n">
         <v>1</v>
       </c>
       <c r="V61" t="n">
         <v>1</v>
       </c>
-      <c r="Z61" t="n">
-        <v>1</v>
-      </c>
       <c r="AF61" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Rendimiento de una reacción</t>
+          <t>Equilibrio químico dinámico</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M62" t="n">
+        <v>7</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
       </c>
       <c r="AF62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
@@ -4408,121 +4459,55 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Solubilidad y disoluciones saturadas</t>
+          <t>Equilibrio y rapidez en procesos industriales</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
-      </c>
-      <c r="D63" t="n">
-        <v>3</v>
-      </c>
-      <c r="F63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G63" t="n">
-        <v>3</v>
-      </c>
-      <c r="H63" t="n">
-        <v>2</v>
-      </c>
-      <c r="I63" t="n">
-        <v>4</v>
-      </c>
-      <c r="J63" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K63" t="n">
-        <v>6</v>
-      </c>
-      <c r="L63" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M63" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O63" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="P63" t="n">
         <v>1</v>
       </c>
-      <c r="Q63" t="n">
-        <v>1</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1</v>
-      </c>
-      <c r="S63" t="n">
-        <v>1</v>
-      </c>
-      <c r="T63" t="n">
-        <v>1</v>
-      </c>
-      <c r="U63" t="n">
-        <v>1</v>
-      </c>
-      <c r="V63" t="n">
-        <v>1</v>
-      </c>
       <c r="AF63" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Teoría cinética de los gases</t>
+          <t>Espectros atómicos y modelo de Bohr</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>8</v>
-      </c>
-      <c r="D64" t="n">
-        <v>8</v>
-      </c>
-      <c r="G64" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H64" t="n">
         <v>7</v>
       </c>
-      <c r="J64" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M64" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P64" t="n">
-        <v>1</v>
-      </c>
       <c r="Q64" t="n">
-        <v>1</v>
-      </c>
-      <c r="S64" t="n">
-        <v>1</v>
-      </c>
-      <c r="V64" t="n">
         <v>1</v>
       </c>
       <c r="AF64" t="n">
@@ -4530,7 +4515,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH64" t="inlineStr">
@@ -4542,62 +4527,41 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Tipo de enlace y propiedades de las sustancias</t>
+          <t>Estereoquímica y quiralidad</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6</v>
-      </c>
-      <c r="D65" t="n">
-        <v>6</v>
-      </c>
-      <c r="F65" t="n">
-        <v>8</v>
-      </c>
-      <c r="G65" t="n">
-        <v>6</v>
-      </c>
-      <c r="H65" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M65" t="n">
         <v>7</v>
       </c>
-      <c r="O65" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>1</v>
-      </c>
       <c r="V65" t="n">
         <v>1</v>
       </c>
       <c r="AF65" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Autoionización del agua, Kw y cálculo de pH</t>
+          <t>Esterificación e hidrólisis</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4606,22 +4570,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>9</v>
-      </c>
-      <c r="G66" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="M66" t="n">
         <v>7</v>
       </c>
-      <c r="P66" t="n">
-        <v>1</v>
-      </c>
       <c r="V66" t="n">
         <v>1</v>
       </c>
       <c r="AF66" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
@@ -4637,7 +4595,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Celdas galvánicas</t>
+          <t>Estructura y propiedades de los polímeros</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4646,21 +4604,33 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
-      </c>
-      <c r="D67" t="n">
-        <v>4</v>
-      </c>
-      <c r="I67" t="n">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="F67" t="n">
+        <v>8</v>
+      </c>
+      <c r="G67" t="n">
+        <v>6</v>
+      </c>
+      <c r="H67" t="n">
+        <v>7</v>
       </c>
       <c r="M67" t="n">
         <v>7</v>
       </c>
-      <c r="R67" t="n">
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z67" t="n">
         <v>1</v>
       </c>
       <c r="AF67" t="n">
@@ -4668,7 +4638,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH67" t="inlineStr">
@@ -4680,7 +4650,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cromatografía</t>
+          <t>Fuerza de ácidos y bases: Ka y Kb</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4689,34 +4659,28 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="F68" t="n">
+        <v>8</v>
       </c>
       <c r="G68" t="n">
         <v>8.5</v>
       </c>
-      <c r="H68" t="n">
-        <v>7</v>
-      </c>
-      <c r="L68" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M68" t="n">
         <v>7</v>
       </c>
+      <c r="O68" t="n">
+        <v>1</v>
+      </c>
       <c r="P68" t="n">
         <v>1</v>
       </c>
-      <c r="Q68" t="n">
-        <v>1</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1</v>
-      </c>
       <c r="V68" t="n">
         <v>1</v>
       </c>
       <c r="AF68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
@@ -4732,7 +4696,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ecuación de los gases ideales y volumen molar</t>
+          <t>Fundamentos de la reactividad orgánica</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4741,20 +4705,17 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>10</v>
-      </c>
-      <c r="F69" t="n">
-        <v>8</v>
-      </c>
-      <c r="O69" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D69" t="n">
+        <v>5</v>
       </c>
       <c r="AF69" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH69" t="inlineStr">
@@ -4766,7 +4727,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ecuaciones y reacciones nucleares</t>
+          <t>Grupos funcionales</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4775,16 +4736,28 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>10</v>
-      </c>
-      <c r="L70" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="U70" t="n">
+        <v>9</v>
+      </c>
+      <c r="F70" t="n">
+        <v>8</v>
+      </c>
+      <c r="G70" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M70" t="n">
+        <v>7</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="V70" t="n">
         <v>1</v>
       </c>
       <c r="AF70" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
@@ -4800,7 +4773,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>El carbono y las moléculas orgánicas</t>
+          <t>Hidrocarburos: alcanos, alquenos y alquinos</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4809,7 +4782,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F71" t="n">
         <v>8</v>
@@ -4829,6 +4802,9 @@
       <c r="V71" t="n">
         <v>1</v>
       </c>
+      <c r="Z71" t="n">
+        <v>1</v>
+      </c>
       <c r="AF71" t="n">
         <v>11</v>
       </c>
@@ -4846,7 +4822,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Electrólisis y celdas electrolíticas</t>
+          <t>Hidrocarburos aromáticos</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4855,34 +4831,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G72" t="n">
         <v>8.5</v>
       </c>
-      <c r="H72" t="n">
-        <v>7</v>
-      </c>
-      <c r="I72" t="n">
-        <v>8</v>
-      </c>
-      <c r="M72" t="n">
-        <v>7</v>
-      </c>
       <c r="P72" t="n">
         <v>1</v>
       </c>
-      <c r="Q72" t="n">
-        <v>1</v>
-      </c>
-      <c r="R72" t="n">
-        <v>1</v>
-      </c>
-      <c r="V72" t="n">
-        <v>1</v>
-      </c>
       <c r="AF72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
@@ -4898,7 +4856,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Electrolitos fuertes y débiles</t>
+          <t>Isomería estructural</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4907,34 +4865,22 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>8</v>
       </c>
-      <c r="G73" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I73" t="n">
-        <v>8</v>
-      </c>
       <c r="M73" t="n">
         <v>7</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
       </c>
-      <c r="P73" t="n">
-        <v>1</v>
-      </c>
-      <c r="R73" t="n">
-        <v>1</v>
-      </c>
       <c r="V73" t="n">
         <v>1</v>
       </c>
       <c r="AF73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
@@ -4950,7 +4896,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Energía de enlace</t>
+          <t>Ley de Hess y entalpías de formación</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4962,7 +4908,7 @@
         <v>10</v>
       </c>
       <c r="G74" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
@@ -4984,7 +4930,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Entalpía de reacción y ecuaciones termoquímicas</t>
+          <t>Leyes de los gases</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4995,22 +4941,16 @@
       <c r="C75" t="n">
         <v>10</v>
       </c>
-      <c r="G75" t="n">
-        <v>8.5</v>
-      </c>
       <c r="I75" t="n">
-        <v>7</v>
-      </c>
-      <c r="M75" t="n">
-        <v>7</v>
-      </c>
-      <c r="P75" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2.5</v>
       </c>
       <c r="R75" t="n">
         <v>1</v>
       </c>
-      <c r="V75" t="n">
+      <c r="S75" t="n">
         <v>1</v>
       </c>
       <c r="AF75" t="n">
@@ -5030,7 +4970,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Equilibrio y rapidez en procesos industriales</t>
+          <t>Leyes ponderales y volumétricas</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5039,12 +4979,18 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>9</v>
-      </c>
-      <c r="G76" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P76" t="n">
+        <v>10</v>
+      </c>
+      <c r="I76" t="n">
+        <v>7</v>
+      </c>
+      <c r="J76" t="n">
+        <v>7</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
+      <c r="S76" t="n">
         <v>1</v>
       </c>
       <c r="AF76" t="n">
@@ -5064,7 +5010,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Espectros atómicos y modelo de Bohr</t>
+          <t>Nomenclatura orgánica IUPAC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5073,20 +5019,29 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>10</v>
-      </c>
-      <c r="H77" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q77" t="n">
+        <v>7</v>
+      </c>
+      <c r="D77" t="n">
+        <v>7</v>
+      </c>
+      <c r="G77" t="n">
+        <v>6</v>
+      </c>
+      <c r="M77" t="n">
+        <v>7</v>
+      </c>
+      <c r="P77" t="n">
+        <v>1</v>
+      </c>
+      <c r="V77" t="n">
         <v>1</v>
       </c>
       <c r="AF77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH77" t="inlineStr">
@@ -5098,7 +5053,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Estereoquímica y quiralidad</t>
+          <t>Polimerización por adición y por condensación</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5107,12 +5062,15 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M78" t="n">
         <v>7</v>
       </c>
       <c r="V78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z78" t="n">
         <v>1</v>
       </c>
       <c r="AF78" t="n">
@@ -5132,7 +5090,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Esterificación e hidrólisis</t>
+          <t>Polímeros y ambiente</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5143,10 +5101,19 @@
       <c r="C79" t="n">
         <v>11</v>
       </c>
-      <c r="M79" t="n">
-        <v>7</v>
-      </c>
-      <c r="V79" t="n">
+      <c r="F79" t="n">
+        <v>8</v>
+      </c>
+      <c r="H79" t="n">
+        <v>7</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z79" t="n">
         <v>1</v>
       </c>
       <c r="AF79" t="n">
@@ -5166,7 +5133,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Estructura y propiedades de los polímeros</t>
+          <t>Potenciales estándar de electrodo y de celda</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5175,33 +5142,18 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F80" t="n">
         <v>8</v>
       </c>
       <c r="G80" t="n">
-        <v>6</v>
-      </c>
-      <c r="H80" t="n">
-        <v>7</v>
-      </c>
-      <c r="M80" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="O80" t="n">
         <v>1</v>
       </c>
       <c r="P80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>1</v>
-      </c>
-      <c r="V80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z80" t="n">
         <v>1</v>
       </c>
       <c r="AF80" t="n">
@@ -5221,7 +5173,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Fuerza de ácidos y bases: Ka y Kb</t>
+          <t>Principio de Le Chatelier</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5232,18 +5184,12 @@
       <c r="C81" t="n">
         <v>9</v>
       </c>
-      <c r="F81" t="n">
-        <v>8</v>
-      </c>
       <c r="G81" t="n">
         <v>8.5</v>
       </c>
       <c r="M81" t="n">
         <v>7</v>
       </c>
-      <c r="O81" t="n">
-        <v>1</v>
-      </c>
       <c r="P81" t="n">
         <v>1</v>
       </c>
@@ -5267,7 +5213,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Grupos funcionales</t>
+          <t>Química de los carbohidratos</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5276,32 +5222,17 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>9</v>
-      </c>
-      <c r="F82" t="n">
-        <v>8</v>
-      </c>
-      <c r="G82" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M82" t="n">
-        <v>7</v>
-      </c>
-      <c r="O82" t="n">
-        <v>1</v>
-      </c>
-      <c r="P82" t="n">
-        <v>1</v>
-      </c>
-      <c r="V82" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="D82" t="n">
+        <v>6</v>
       </c>
       <c r="AF82" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH82" t="inlineStr">
@@ -5313,7 +5244,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Hidrocarburos: alcanos, alquenos y alquinos</t>
+          <t>Química de los lípidos</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5322,35 +5253,17 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>11</v>
-      </c>
-      <c r="F83" t="n">
-        <v>8</v>
-      </c>
-      <c r="G83" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M83" t="n">
-        <v>7</v>
-      </c>
-      <c r="O83" t="n">
-        <v>1</v>
-      </c>
-      <c r="P83" t="n">
-        <v>1</v>
-      </c>
-      <c r="V83" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z83" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="D83" t="n">
+        <v>6</v>
       </c>
       <c r="AF83" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH83" t="inlineStr">
@@ -5362,7 +5275,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Hidrocarburos aromáticos</t>
+          <t>Química verde y economía atómica</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5376,7 +5289,13 @@
       <c r="G84" t="n">
         <v>8.5</v>
       </c>
+      <c r="H84" t="n">
+        <v>7</v>
+      </c>
       <c r="P84" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q84" t="n">
         <v>1</v>
       </c>
       <c r="AF84" t="n">
@@ -5396,7 +5315,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Isomería estructural</t>
+          <t>Radiactividad y emisiones nucleares</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5405,18 +5324,15 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10</v>
-      </c>
-      <c r="F85" t="n">
+        <v>5</v>
+      </c>
+      <c r="D85" t="n">
+        <v>5</v>
+      </c>
+      <c r="E85" t="n">
         <v>8</v>
       </c>
-      <c r="M85" t="n">
-        <v>7</v>
-      </c>
-      <c r="O85" t="n">
-        <v>1</v>
-      </c>
-      <c r="V85" t="n">
+      <c r="N85" t="n">
         <v>1</v>
       </c>
       <c r="AF85" t="n">
@@ -5424,7 +5340,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH85" t="inlineStr">
@@ -5436,7 +5352,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Ley de Hess y entalpías de formación</t>
+          <t>Factores que afectan la rapidez de reacción</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5445,32 +5361,56 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="D86" t="n">
+        <v>6</v>
+      </c>
+      <c r="F86" t="n">
+        <v>8</v>
       </c>
       <c r="G86" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H86" t="n">
+        <v>7</v>
+      </c>
+      <c r="M86" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1</v>
       </c>
       <c r="P86" t="n">
         <v>1</v>
       </c>
+      <c r="Q86" t="n">
+        <v>1</v>
+      </c>
+      <c r="V86" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>1</v>
+      </c>
       <c r="AF86" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Leyes de los gases</t>
+          <t>Reacciones de precipitación e identificación de iones</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5479,18 +5419,24 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="H87" t="n">
+        <v>7</v>
       </c>
       <c r="I87" t="n">
-        <v>6</v>
-      </c>
-      <c r="J87" t="n">
-        <v>2.5</v>
+        <v>8</v>
+      </c>
+      <c r="M87" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1</v>
       </c>
       <c r="R87" t="n">
         <v>1</v>
       </c>
-      <c r="S87" t="n">
+      <c r="V87" t="n">
         <v>1</v>
       </c>
       <c r="AF87" t="n">
@@ -5510,7 +5456,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Leyes ponderales y volumétricas</t>
+          <t>Reacciones orgánicas características</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5519,22 +5465,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10</v>
-      </c>
-      <c r="I88" t="n">
-        <v>7</v>
-      </c>
-      <c r="J88" t="n">
-        <v>7</v>
-      </c>
-      <c r="R88" t="n">
-        <v>1</v>
-      </c>
-      <c r="S88" t="n">
+        <v>11</v>
+      </c>
+      <c r="M88" t="n">
+        <v>7</v>
+      </c>
+      <c r="V88" t="n">
         <v>1</v>
       </c>
       <c r="AF88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
@@ -5550,7 +5490,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Polimerización por adición y por condensación</t>
+          <t>Reactivo limitante y en exceso</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5559,19 +5499,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>11</v>
-      </c>
-      <c r="M89" t="n">
-        <v>7</v>
-      </c>
-      <c r="V89" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z89" t="n">
+        <v>10</v>
+      </c>
+      <c r="G89" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P89" t="n">
         <v>1</v>
       </c>
       <c r="AF89" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
@@ -5587,7 +5524,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Polímeros y ambiente</t>
+          <t>Redes covalentes y alótropos del carbono</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5596,25 +5533,28 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F90" t="n">
         <v>8</v>
       </c>
-      <c r="H90" t="n">
+      <c r="G90" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M90" t="n">
         <v>7</v>
       </c>
       <c r="O90" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z90" t="n">
+      <c r="P90" t="n">
+        <v>1</v>
+      </c>
+      <c r="V90" t="n">
         <v>1</v>
       </c>
       <c r="AF90" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG90" t="inlineStr">
         <is>
@@ -5630,7 +5570,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Potenciales estándar de electrodo y de celda</t>
+          <t>Semivida, series de desintegración y residuos radiactivos</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5641,12 +5581,18 @@
       <c r="C91" t="n">
         <v>10</v>
       </c>
+      <c r="E91" t="n">
+        <v>8</v>
+      </c>
       <c r="F91" t="n">
         <v>8</v>
       </c>
       <c r="G91" t="n">
         <v>8.5</v>
       </c>
+      <c r="N91" t="n">
+        <v>1</v>
+      </c>
       <c r="O91" t="n">
         <v>1</v>
       </c>
@@ -5670,7 +5616,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Principio de Le Chatelier</t>
+          <t>Teoría cinética de los gases</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5679,26 +5625,41 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="D92" t="n">
+        <v>8</v>
       </c>
       <c r="G92" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H92" t="n">
+        <v>7</v>
+      </c>
+      <c r="J92" t="n">
+        <v>2.5</v>
       </c>
       <c r="M92" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="P92" t="n">
         <v>1</v>
       </c>
+      <c r="Q92" t="n">
+        <v>1</v>
+      </c>
+      <c r="S92" t="n">
+        <v>1</v>
+      </c>
       <c r="V92" t="n">
         <v>1</v>
       </c>
       <c r="AF92" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
@@ -5710,7 +5671,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Química de los lípidos</t>
+          <t>Teoría de colisiones</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5719,17 +5680,35 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>6</v>
-      </c>
-      <c r="D93" t="n">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="F93" t="n">
+        <v>8</v>
+      </c>
+      <c r="G93" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M93" t="n">
+        <v>7</v>
+      </c>
+      <c r="O93" t="n">
+        <v>1</v>
+      </c>
+      <c r="P93" t="n">
+        <v>1</v>
+      </c>
+      <c r="V93" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>1</v>
       </c>
       <c r="AF93" t="n">
         <v>10</v>
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH93" t="inlineStr">
@@ -5741,7 +5720,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Química verde y economía atómica</t>
+          <t>Teorías ácido-base (Arrhenius, Brønsted-Lowry, Lewis)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5750,22 +5729,34 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="F94" t="n">
+        <v>8</v>
       </c>
       <c r="G94" t="n">
         <v>8.5</v>
       </c>
-      <c r="H94" t="n">
-        <v>7</v>
+      <c r="I94" t="n">
+        <v>8</v>
+      </c>
+      <c r="M94" t="n">
+        <v>7</v>
+      </c>
+      <c r="O94" t="n">
+        <v>1</v>
       </c>
       <c r="P94" t="n">
         <v>1</v>
       </c>
-      <c r="Q94" t="n">
+      <c r="R94" t="n">
+        <v>1</v>
+      </c>
+      <c r="V94" t="n">
         <v>1</v>
       </c>
       <c r="AF94" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
@@ -5781,7 +5772,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Reacciones de precipitación e identificación de iones</t>
+          <t>Medición de la velocidad de reacción</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5790,24 +5781,12 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>9</v>
-      </c>
-      <c r="H95" t="n">
-        <v>7</v>
-      </c>
-      <c r="I95" t="n">
-        <v>8</v>
-      </c>
-      <c r="M95" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>1</v>
-      </c>
-      <c r="R95" t="n">
-        <v>1</v>
-      </c>
-      <c r="V95" t="n">
+        <v>10</v>
+      </c>
+      <c r="G95" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P95" t="n">
         <v>1</v>
       </c>
       <c r="AF95" t="n">
@@ -5827,50 +5806,62 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Reacciones orgánicas características</t>
+          <t>Catalizadores</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="D96" t="n">
+        <v>6</v>
+      </c>
+      <c r="G96" t="n">
+        <v>6</v>
       </c>
       <c r="M96" t="n">
         <v>7</v>
       </c>
+      <c r="P96" t="n">
+        <v>1</v>
+      </c>
       <c r="V96" t="n">
         <v>1</v>
       </c>
       <c r="AF96" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Reactivo limitante y en exceso</t>
+          <t>Composición porcentual y fórmulas empírica y molecular</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="D97" t="n">
+        <v>6</v>
       </c>
       <c r="G97" t="n">
         <v>8.5</v>
@@ -5883,7 +5874,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH97" t="inlineStr">
@@ -5895,157 +5886,118 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Redes covalentes y alótropos del carbono</t>
+          <t>Configuración electrónica por orbitales</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>10</v>
-      </c>
-      <c r="F98" t="n">
-        <v>8</v>
-      </c>
-      <c r="G98" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M98" t="n">
-        <v>7</v>
-      </c>
-      <c r="O98" t="n">
-        <v>1</v>
-      </c>
-      <c r="P98" t="n">
-        <v>1</v>
-      </c>
-      <c r="V98" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D98" t="n">
+        <v>5</v>
       </c>
       <c r="AF98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Semivida, series de desintegración y residuos radiactivos</t>
+          <t>Electronegatividad y polaridad de enlace</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>10</v>
-      </c>
-      <c r="E99" t="n">
-        <v>8</v>
-      </c>
-      <c r="F99" t="n">
-        <v>8</v>
-      </c>
-      <c r="G99" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="N99" t="n">
-        <v>1</v>
-      </c>
-      <c r="O99" t="n">
-        <v>1</v>
-      </c>
-      <c r="P99" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="D99" t="n">
+        <v>6</v>
       </c>
       <c r="AF99" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Teoría de colisiones</t>
+          <t>Electrones de valencia y regla del octeto</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>9</v>
-      </c>
-      <c r="F100" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="D100" t="n">
+        <v>5</v>
       </c>
       <c r="G100" t="n">
         <v>8.5</v>
       </c>
-      <c r="M100" t="n">
-        <v>7</v>
-      </c>
-      <c r="O100" t="n">
-        <v>1</v>
-      </c>
       <c r="P100" t="n">
         <v>1</v>
       </c>
-      <c r="V100" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z100" t="n">
-        <v>1</v>
-      </c>
       <c r="AF100" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Teorías ácido-base (Arrhenius, Brønsted-Lowry, Lewis)</t>
+          <t>Enlace covalente</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="D101" t="n">
+        <v>6</v>
       </c>
       <c r="F101" t="n">
         <v>8</v>
@@ -6053,76 +6005,73 @@
       <c r="G101" t="n">
         <v>8.5</v>
       </c>
-      <c r="I101" t="n">
-        <v>8</v>
-      </c>
-      <c r="M101" t="n">
-        <v>7</v>
-      </c>
       <c r="O101" t="n">
         <v>1</v>
       </c>
       <c r="P101" t="n">
         <v>1</v>
       </c>
-      <c r="R101" t="n">
-        <v>1</v>
-      </c>
-      <c r="V101" t="n">
-        <v>1</v>
-      </c>
       <c r="AF101" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Medición de la velocidad de reacción</t>
+          <t>Enlace iónico</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="D102" t="n">
+        <v>5</v>
+      </c>
+      <c r="F102" t="n">
+        <v>8</v>
       </c>
       <c r="G102" t="n">
         <v>8.5</v>
       </c>
+      <c r="O102" t="n">
+        <v>1</v>
+      </c>
       <c r="P102" t="n">
         <v>1</v>
       </c>
       <c r="AF102" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Catalizadores</t>
+          <t>Enlace metálico</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6136,16 +6085,22 @@
       <c r="D103" t="n">
         <v>6</v>
       </c>
+      <c r="F103" t="n">
+        <v>8</v>
+      </c>
       <c r="G103" t="n">
-        <v>6</v>
-      </c>
-      <c r="M103" t="n">
-        <v>7</v>
+        <v>8.5</v>
+      </c>
+      <c r="H103" t="n">
+        <v>7</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1</v>
       </c>
       <c r="P103" t="n">
         <v>1</v>
       </c>
-      <c r="V103" t="n">
+      <c r="Q103" t="n">
         <v>1</v>
       </c>
       <c r="AF103" t="n">
@@ -6158,14 +6113,14 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Electronegatividad y polaridad de enlace</t>
+          <t>Enlace químico</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6174,29 +6129,53 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D104" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="F104" t="n">
+        <v>8</v>
+      </c>
+      <c r="G104" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H104" t="n">
+        <v>7</v>
+      </c>
+      <c r="L104" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O104" t="n">
+        <v>1</v>
+      </c>
+      <c r="P104" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>1</v>
+      </c>
+      <c r="U104" t="n">
+        <v>1</v>
       </c>
       <c r="AF104" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Electrones de valencia y regla del octeto</t>
+          <t>Notación y estructuras de Lewis</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6205,10 +6184,10 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G105" t="n">
         <v>8.5</v>
@@ -6233,7 +6212,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Enlace covalente</t>
+          <t>Fuerzas intermoleculares</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6247,16 +6226,22 @@
       <c r="D106" t="n">
         <v>6</v>
       </c>
-      <c r="F106" t="n">
-        <v>8</v>
+      <c r="E106" t="n">
+        <v>6</v>
       </c>
       <c r="G106" t="n">
         <v>8.5</v>
       </c>
-      <c r="O106" t="n">
+      <c r="J106" t="n">
+        <v>7</v>
+      </c>
+      <c r="N106" t="n">
         <v>1</v>
       </c>
       <c r="P106" t="n">
+        <v>1</v>
+      </c>
+      <c r="S106" t="n">
         <v>1</v>
       </c>
       <c r="AF106" t="n">
@@ -6269,14 +6254,14 @@
       </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Enlace iónico</t>
+          <t>Geometría molecular (RPECV)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6285,25 +6270,19 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
-      </c>
-      <c r="F107" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G107" t="n">
         <v>8.5</v>
       </c>
-      <c r="O107" t="n">
-        <v>1</v>
-      </c>
       <c r="P107" t="n">
         <v>1</v>
       </c>
       <c r="AF107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
@@ -6319,7 +6298,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Notación y estructuras de Lewis</t>
+          <t>Isótopos</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6328,19 +6307,25 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G108" t="n">
         <v>8.5</v>
       </c>
+      <c r="L108" t="n">
+        <v>7.5</v>
+      </c>
       <c r="P108" t="n">
         <v>1</v>
       </c>
+      <c r="U108" t="n">
+        <v>1</v>
+      </c>
       <c r="AF108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG108" t="inlineStr">
         <is>
@@ -6356,7 +6341,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Geometría molecular (RPECV)</t>
+          <t>Masa molar</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6365,19 +6350,25 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D109" t="n">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="F109" t="n">
+        <v>8</v>
       </c>
       <c r="G109" t="n">
         <v>8.5</v>
       </c>
+      <c r="O109" t="n">
+        <v>1</v>
+      </c>
       <c r="P109" t="n">
         <v>1</v>
       </c>
       <c r="AF109" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG109" t="inlineStr">
         <is>
@@ -6393,7 +6384,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Isótopos</t>
+          <t>Modelo mecanocuántico y orbitales atómicos</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6407,18 +6398,6 @@
       <c r="D110" t="n">
         <v>5</v>
       </c>
-      <c r="G110" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L110" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P110" t="n">
-        <v>1</v>
-      </c>
-      <c r="U110" t="n">
-        <v>1</v>
-      </c>
       <c r="AF110" t="n">
         <v>5</v>
       </c>
@@ -6436,7 +6415,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Masa molar</t>
+          <t>Mol y número de Avogadro</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6479,7 +6458,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Modelo mecanocuántico y orbitales atómicos</t>
+          <t>Molaridad y unidades químicas de concentración</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6488,13 +6467,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D112" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF112" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
@@ -6510,7 +6489,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Mol y número de Avogadro</t>
+          <t>Compuestos inorgánicos: funciones y nomenclatura</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6519,16 +6498,19 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D113" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F113" t="n">
         <v>8</v>
       </c>
       <c r="G113" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="M113" t="n">
+        <v>7</v>
       </c>
       <c r="O113" t="n">
         <v>1</v>
@@ -6536,8 +6518,11 @@
       <c r="P113" t="n">
         <v>1</v>
       </c>
+      <c r="V113" t="n">
+        <v>1</v>
+      </c>
       <c r="AF113" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG113" t="inlineStr">
         <is>
@@ -6546,14 +6531,14 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Molaridad y unidades químicas de concentración</t>
+          <t>Número de oxidación</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6562,13 +6547,19 @@
         </is>
       </c>
       <c r="C114" t="n">
+        <v>5</v>
+      </c>
+      <c r="D114" t="n">
+        <v>5</v>
+      </c>
+      <c r="F114" t="n">
         <v>8</v>
       </c>
-      <c r="D114" t="n">
-        <v>8</v>
+      <c r="O114" t="n">
+        <v>1</v>
       </c>
       <c r="AF114" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG114" t="inlineStr">
         <is>
@@ -6584,7 +6575,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Número de oxidación</t>
+          <t>Números cuánticos</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6598,12 +6589,6 @@
       <c r="D115" t="n">
         <v>5</v>
       </c>
-      <c r="F115" t="n">
-        <v>8</v>
-      </c>
-      <c r="O115" t="n">
-        <v>1</v>
-      </c>
       <c r="AF115" t="n">
         <v>5</v>
       </c>
@@ -6621,7 +6606,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Números cuánticos</t>
+          <t>Polaridad molecular</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6630,13 +6615,25 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D116" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="F116" t="n">
+        <v>8</v>
+      </c>
+      <c r="K116" t="n">
+        <v>6</v>
+      </c>
+      <c r="O116" t="n">
+        <v>1</v>
+      </c>
+      <c r="T116" t="n">
+        <v>1</v>
       </c>
       <c r="AF116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG116" t="inlineStr">
         <is>
@@ -6652,7 +6649,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Polaridad molecular</t>
+          <t>Propiedades coligativas</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6661,25 +6658,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D117" t="n">
-        <v>6</v>
-      </c>
-      <c r="F117" t="n">
         <v>8</v>
       </c>
-      <c r="K117" t="n">
-        <v>6</v>
-      </c>
-      <c r="O117" t="n">
-        <v>1</v>
-      </c>
-      <c r="T117" t="n">
-        <v>1</v>
-      </c>
       <c r="AF117" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG117" t="inlineStr">
         <is>
@@ -6695,7 +6680,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Propiedades coligativas</t>
+          <t>Rendimiento de una reacción</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6710,7 +6695,7 @@
         <v>8</v>
       </c>
       <c r="AF118" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG118" t="inlineStr">
         <is>
@@ -6719,7 +6704,7 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
@@ -6757,7 +6742,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Agentes oxidantes y reductores</t>
+          <t>Neutralización y reacciones de los ácidos</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6766,22 +6751,28 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F120" t="n">
         <v>8</v>
       </c>
       <c r="G120" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
       </c>
       <c r="I120" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="J120" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L120" t="n">
+        <v>7.5</v>
       </c>
       <c r="M120" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O120" t="n">
         <v>1</v>
@@ -6795,15 +6786,24 @@
       <c r="R120" t="n">
         <v>1</v>
       </c>
+      <c r="S120" t="n">
+        <v>1</v>
+      </c>
+      <c r="U120" t="n">
+        <v>1</v>
+      </c>
       <c r="V120" t="n">
         <v>1</v>
       </c>
+      <c r="Z120" t="n">
+        <v>1</v>
+      </c>
       <c r="AF120" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="AH120" t="inlineStr">

--- a/internacional/2_8/Contraste_quimica.xlsx
+++ b/internacional/2_8/Contraste_quimica.xlsx
@@ -1044,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fuerzas intermoleculares y propiedades físicas</t>
+          <t>Iones</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
         <v>8</v>
@@ -1064,7 +1064,16 @@
       <c r="G8" t="n">
         <v>8.5</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M8" t="n">
         <v>7</v>
       </c>
       <c r="O8" t="n">
@@ -1073,30 +1082,36 @@
       <c r="P8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" t="n">
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
         <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Iones</t>
+          <t>Masa atómica relativa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1110,40 +1125,25 @@
       <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="F9" t="n">
-        <v>8</v>
-      </c>
       <c r="G9" t="n">
         <v>8.5</v>
       </c>
-      <c r="I9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>7</v>
-      </c>
       <c r="L9" t="n">
         <v>7.5</v>
       </c>
       <c r="M9" t="n">
         <v>7</v>
       </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
       <c r="U9" t="n">
         <v>1</v>
       </c>
       <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AF9" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Masa atómica relativa</t>
+          <t>Reutilización y reciclaje de materiales</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1172,13 +1172,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>7.5</v>
@@ -1186,9 +1198,21 @@
       <c r="M10" t="n">
         <v>7</v>
       </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
       <c r="U10" t="n">
         <v>1</v>
       </c>
@@ -1199,11 +1223,11 @@
         <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -1215,7 +1239,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Reutilización y reciclaje de materiales</t>
+          <t>Mezclas homogéneas y heterogéneas</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1229,26 +1253,35 @@
       <c r="D11" t="n">
         <v>2</v>
       </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
         <v>6</v>
-      </c>
-      <c r="H11" t="n">
-        <v>7</v>
       </c>
       <c r="J11" t="n">
         <v>4.5</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1257,6 +1290,9 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
@@ -1291,7 +1327,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mezclas homogéneas y heterogéneas</t>
+          <t>Evolución de los modelos atómicos</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1300,70 +1336,43 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" t="n">
         <v>6</v>
       </c>
-      <c r="F12" t="n">
+      <c r="K12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>7</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
         <v>5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L12" t="n">
-        <v>5</v>
-      </c>
-      <c r="M12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -1379,7 +1388,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Evolución de los modelos atómicos</t>
+          <t>Moléculas y fórmulas químicas</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1394,13 +1403,25 @@
         <v>5</v>
       </c>
       <c r="E13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" t="n">
         <v>8</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
       </c>
+      <c r="H13" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>7</v>
+      </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
         <v>7.5</v>
@@ -1411,9 +1432,21 @@
       <c r="N13" t="n">
         <v>1</v>
       </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
       <c r="P13" t="n">
         <v>1</v>
       </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
@@ -1421,6 +1454,9 @@
         <v>1</v>
       </c>
       <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
         <v>1</v>
       </c>
       <c r="AF13" t="n">
@@ -1440,7 +1476,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Moléculas y fórmulas químicas</t>
+          <t>Propiedades periódicas</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1454,55 +1490,19 @@
       <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="E14" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" t="n">
-        <v>8</v>
-      </c>
       <c r="G14" t="n">
         <v>6</v>
       </c>
-      <c r="H14" t="n">
-        <v>7</v>
-      </c>
-      <c r="I14" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>7</v>
-      </c>
       <c r="K14" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
         <v>7</v>
       </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
       <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
         <v>1</v>
       </c>
       <c r="V14" t="n">
@@ -1528,7 +1528,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Propiedades periódicas</t>
+          <t>Propiedades singulares del agua</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1537,34 +1537,43 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
         <v>5</v>
       </c>
       <c r="G15" t="n">
         <v>6</v>
       </c>
+      <c r="H15" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
       <c r="K15" t="n">
-        <v>8</v>
-      </c>
-      <c r="M15" t="n">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
       </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="V15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1</v>
-      </c>
       <c r="AF15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
@@ -1580,7 +1589,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Propiedades singulares del agua</t>
+          <t>Química descriptiva de los elementos</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1589,43 +1598,40 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7</v>
+      </c>
+      <c r="M16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
         <v>5</v>
-      </c>
-      <c r="G16" t="n">
-        <v>6</v>
-      </c>
-      <c r="H16" t="n">
-        <v>7</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>6</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>3</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
@@ -1641,7 +1647,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Química descriptiva de los elementos</t>
+          <t>Reacción química y sus evidencias</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1650,22 +1656,40 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
         <v>5</v>
       </c>
       <c r="F17" t="n">
         <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7.5</v>
       </c>
       <c r="M17" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
@@ -1676,14 +1700,23 @@
       <c r="Q17" t="n">
         <v>1</v>
       </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
       <c r="V17" t="n">
         <v>1</v>
       </c>
-      <c r="Z17" t="n">
-        <v>1</v>
-      </c>
       <c r="AF17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
@@ -1699,7 +1732,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Reacción química y sus evidencias</t>
+          <t>Métodos físicos de separación de mezclas</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1714,31 +1747,31 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="n">
         <v>5</v>
-      </c>
-      <c r="F18" t="n">
-        <v>8</v>
       </c>
       <c r="G18" t="n">
         <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
         <v>4.5</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
         <v>7.5</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
@@ -1765,6 +1798,9 @@
         <v>1</v>
       </c>
       <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
         <v>1</v>
       </c>
       <c r="AF18" t="n">
@@ -1784,7 +1820,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Métodos físicos de separación de mezclas</t>
+          <t>Solubilidad y disoluciones saturadas</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1793,16 +1829,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
         <v>3</v>
@@ -1825,9 +1858,6 @@
       <c r="M19" t="n">
         <v>2.5</v>
       </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
       <c r="O19" t="n">
         <v>1</v>
       </c>
@@ -1852,11 +1882,8 @@
       <c r="V19" t="n">
         <v>1</v>
       </c>
-      <c r="Z19" t="n">
-        <v>1</v>
-      </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
@@ -1865,14 +1892,14 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Solubilidad y disoluciones saturadas</t>
+          <t>Organización de la tabla periódica</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1881,34 +1908,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F20" t="n">
         <v>8</v>
       </c>
       <c r="G20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" t="n">
         <v>3</v>
       </c>
-      <c r="H20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" t="n">
-        <v>4</v>
-      </c>
       <c r="J20" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L20" t="n">
         <v>7.5</v>
       </c>
       <c r="M20" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -1919,9 +1943,6 @@
       <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
@@ -1934,8 +1955,11 @@
       <c r="V20" t="n">
         <v>1</v>
       </c>
+      <c r="Z20" t="n">
+        <v>1</v>
+      </c>
       <c r="AF20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -1944,14 +1968,14 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Organización de la tabla periódica</t>
+          <t>Calidad y tratamiento del agua</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1960,58 +1984,49 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
         <v>5</v>
       </c>
-      <c r="D21" t="n">
+      <c r="G21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L21" t="n">
         <v>5</v>
       </c>
-      <c r="F21" t="n">
-        <v>8</v>
-      </c>
-      <c r="G21" t="n">
-        <v>6</v>
-      </c>
-      <c r="H21" t="n">
+      <c r="M21" t="n">
+        <v>7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="n">
         <v>3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>7</v>
-      </c>
-      <c r="K21" t="n">
-        <v>8</v>
-      </c>
-      <c r="L21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>7</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>5</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -2027,37 +2042,40 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Calidad y tratamiento del agua</t>
+          <t>Ácidos y bases: propiedades</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
+        <v>8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7</v>
+      </c>
+      <c r="I22" t="n">
         <v>5</v>
       </c>
-      <c r="G22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>7</v>
+      <c r="J22" t="n">
+        <v>4.5</v>
       </c>
       <c r="L22" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="M22" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
         <v>1</v>
@@ -2068,7 +2086,10 @@
       <c r="Q22" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="U22" t="n">
@@ -2078,23 +2099,23 @@
         <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ácidos y bases: propiedades</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2103,32 +2124,41 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
       </c>
       <c r="F23" t="n">
         <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M23" t="n">
         <v>2.5</v>
       </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
       <c r="O23" t="n">
         <v>1</v>
       </c>
@@ -2144,14 +2174,20 @@
       <c r="S23" t="n">
         <v>1</v>
       </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="n">
         <v>1</v>
       </c>
+      <c r="Z23" t="n">
+        <v>1</v>
+      </c>
       <c r="AF23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
@@ -2167,7 +2203,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Combustibles fósiles y biocombustibles</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2176,40 +2212,25 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F24" t="n">
         <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" t="n">
         <v>3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2.5</v>
       </c>
       <c r="K24" t="n">
         <v>4</v>
       </c>
-      <c r="L24" t="n">
-        <v>4</v>
-      </c>
       <c r="M24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
@@ -2220,18 +2241,9 @@
       <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
       <c r="T24" t="n">
         <v>1</v>
       </c>
-      <c r="U24" t="n">
-        <v>1</v>
-      </c>
       <c r="V24" t="n">
         <v>1</v>
       </c>
@@ -2239,7 +2251,7 @@
         <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
@@ -2255,7 +2267,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Combustibles fósiles y biocombustibles</t>
+          <t>Combustión</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2268,21 +2280,33 @@
       </c>
       <c r="D25" t="n">
         <v>7</v>
+      </c>
+      <c r="E25" t="n">
+        <v>8</v>
       </c>
       <c r="F25" t="n">
         <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
       </c>
-      <c r="K25" t="n">
-        <v>4</v>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>7.5</v>
       </c>
       <c r="M25" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -2293,7 +2317,13 @@
       <c r="Q25" t="n">
         <v>1</v>
       </c>
-      <c r="T25" t="n">
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
         <v>1</v>
       </c>
       <c r="V25" t="n">
@@ -2312,14 +2342,14 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Combustión</t>
+          <t>Composición del aire y contaminantes atmosféricos</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2328,38 +2358,26 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
-      </c>
-      <c r="E26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
         <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
         <v>5</v>
       </c>
       <c r="J26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L26" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M26" t="n">
         <v>2.5</v>
       </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
@@ -2375,33 +2393,24 @@
       <c r="S26" t="n">
         <v>1</v>
       </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1</v>
-      </c>
       <c r="AF26" t="n">
         <v>7</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
           <t>alineado</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Composición del aire y contaminantes atmosféricos</t>
+          <t>Conservación de la masa</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2410,25 +2419,37 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="E27" t="n">
+        <v>8</v>
       </c>
       <c r="F27" t="n">
         <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="L27" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
       </c>
       <c r="O27" t="n">
         <v>1</v>
@@ -2445,24 +2466,30 @@
       <c r="S27" t="n">
         <v>1</v>
       </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
       <c r="AF27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Conservación de la masa</t>
+          <t>Disolución y rapidez de disolución</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2471,40 +2498,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
-      </c>
-      <c r="E28" t="n">
-        <v>8</v>
-      </c>
-      <c r="F28" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
         <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>6</v>
       </c>
       <c r="L28" t="n">
         <v>7.5</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
         <v>1</v>
@@ -2518,6 +2536,9 @@
       <c r="S28" t="n">
         <v>1</v>
       </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
       <c r="U28" t="n">
         <v>1</v>
       </c>
@@ -2525,7 +2546,7 @@
         <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
@@ -2534,14 +2555,14 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Disolución y rapidez de disolución</t>
+          <t>Ecuación química y su balanceo</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2550,31 +2571,40 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="E29" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J29" t="n">
         <v>4.5</v>
       </c>
-      <c r="K29" t="n">
-        <v>6</v>
-      </c>
       <c r="L29" t="n">
         <v>7.5</v>
       </c>
       <c r="M29" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
@@ -2588,17 +2618,17 @@
       <c r="S29" t="n">
         <v>1</v>
       </c>
-      <c r="T29" t="n">
-        <v>1</v>
-      </c>
       <c r="U29" t="n">
         <v>1</v>
       </c>
       <c r="V29" t="n">
         <v>1</v>
       </c>
+      <c r="Z29" t="n">
+        <v>1</v>
+      </c>
       <c r="AF29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
@@ -2614,7 +2644,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ecuación química y su balanceo</t>
+          <t>Escala de pH</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2623,13 +2653,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
-      </c>
-      <c r="E30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F30" t="n">
         <v>8</v>
@@ -2641,7 +2668,7 @@
         <v>7</v>
       </c>
       <c r="I30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
         <v>4.5</v>
@@ -2650,10 +2677,7 @@
         <v>7.5</v>
       </c>
       <c r="M30" t="n">
-        <v>7</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
@@ -2674,9 +2698,6 @@
         <v>1</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z30" t="n">
         <v>1</v>
       </c>
       <c r="AF30" t="n">
@@ -2696,7 +2717,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Escala de pH</t>
+          <t>Estados de la materia</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2705,31 +2726,40 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4</v>
       </c>
       <c r="L31" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
@@ -2746,14 +2776,20 @@
       <c r="S31" t="n">
         <v>1</v>
       </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
       <c r="U31" t="n">
         <v>1</v>
       </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
+      <c r="Z31" t="n">
+        <v>1</v>
+      </c>
       <c r="AF31" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
@@ -2769,7 +2805,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Estados de la materia</t>
+          <t>Estequiometría</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2778,40 +2814,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F32" t="n">
         <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
-      </c>
-      <c r="H32" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L32" t="n">
-        <v>4</v>
-      </c>
-      <c r="M32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
@@ -2819,29 +2837,14 @@
       <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
       <c r="R32" t="n">
         <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
-      <c r="T32" t="n">
-        <v>1</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1</v>
-      </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
@@ -2857,7 +2860,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Estequiometría</t>
+          <t>Indicadores ácido-base</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2866,22 +2869,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>8</v>
-      </c>
-      <c r="D33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F33" t="n">
         <v>8</v>
       </c>
       <c r="G33" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I33" t="n">
+        <v>6</v>
+      </c>
+      <c r="H33" t="n">
         <v>7</v>
       </c>
       <c r="J33" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2.5</v>
       </c>
       <c r="O33" t="n">
         <v>1</v>
@@ -2889,30 +2895,36 @@
       <c r="P33" t="n">
         <v>1</v>
       </c>
-      <c r="R33" t="n">
+      <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
       </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
       <c r="AF33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Indicadores ácido-base</t>
+          <t>Materia y materiales</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2921,26 +2933,41 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
       </c>
       <c r="F34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
         <v>8</v>
       </c>
-      <c r="G34" t="n">
-        <v>6</v>
-      </c>
-      <c r="H34" t="n">
-        <v>7</v>
-      </c>
       <c r="J34" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4</v>
       </c>
       <c r="L34" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
         <v>2.5</v>
       </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
       <c r="O34" t="n">
         <v>1</v>
       </c>
@@ -2950,9 +2977,15 @@
       <c r="Q34" t="n">
         <v>1</v>
       </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
       <c r="S34" t="n">
         <v>1</v>
       </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
       <c r="U34" t="n">
         <v>1</v>
       </c>
@@ -2960,23 +2993,23 @@
         <v>1</v>
       </c>
       <c r="AF34" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Materia y materiales</t>
+          <t>Minerales: composición y estructura cristalina</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2985,71 +3018,35 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
-      </c>
-      <c r="I35" t="n">
+        <v>7</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="n">
         <v>8</v>
       </c>
-      <c r="J35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K35" t="n">
-        <v>4</v>
-      </c>
-      <c r="L35" t="n">
-        <v>3</v>
-      </c>
-      <c r="M35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2</v>
-      </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
@@ -3061,7 +3058,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Minerales: composición y estructura cristalina</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3070,35 +3067,74 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F36" t="n">
         <v>8</v>
       </c>
+      <c r="G36" t="n">
+        <v>6</v>
+      </c>
       <c r="H36" t="n">
         <v>7</v>
       </c>
+      <c r="I36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M36" t="n">
+        <v>7</v>
+      </c>
       <c r="N36" t="n">
         <v>1</v>
       </c>
       <c r="O36" t="n">
         <v>1</v>
       </c>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1</v>
+      </c>
       <c r="AF36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -3110,7 +3146,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>Compuestos inorgánicos: funciones y nomenclatura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3119,13 +3155,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
-      </c>
-      <c r="E37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F37" t="n">
         <v>8</v>
@@ -3133,60 +3166,24 @@
       <c r="G37" t="n">
         <v>6</v>
       </c>
-      <c r="H37" t="n">
-        <v>7</v>
-      </c>
-      <c r="I37" t="n">
-        <v>3</v>
-      </c>
-      <c r="J37" t="n">
-        <v>7</v>
-      </c>
-      <c r="K37" t="n">
-        <v>4</v>
-      </c>
-      <c r="L37" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M37" t="n">
         <v>7</v>
       </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
       <c r="O37" t="n">
         <v>1</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
       </c>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
       <c r="V37" t="n">
         <v>1</v>
       </c>
-      <c r="Z37" t="n">
-        <v>1</v>
-      </c>
       <c r="AF37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
@@ -6261,7 +6258,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Geometría molecular (RPECV)</t>
+          <t>Fuerzas intermoleculares y propiedades físicas</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6270,19 +6267,34 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D107" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="F107" t="n">
+        <v>8</v>
       </c>
       <c r="G107" t="n">
         <v>8.5</v>
       </c>
+      <c r="H107" t="n">
+        <v>7</v>
+      </c>
+      <c r="O107" t="n">
+        <v>1</v>
+      </c>
       <c r="P107" t="n">
         <v>1</v>
       </c>
+      <c r="Q107" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>1</v>
+      </c>
       <c r="AF107" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
@@ -6291,14 +6303,14 @@
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Isótopos</t>
+          <t>Geometría molecular (RPECV)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6307,25 +6319,19 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G108" t="n">
         <v>8.5</v>
       </c>
-      <c r="L108" t="n">
-        <v>7.5</v>
-      </c>
       <c r="P108" t="n">
         <v>1</v>
       </c>
-      <c r="U108" t="n">
-        <v>1</v>
-      </c>
       <c r="AF108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG108" t="inlineStr">
         <is>
@@ -6341,7 +6347,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Masa molar</t>
+          <t>Isótopos</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6350,25 +6356,25 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D109" t="n">
-        <v>8</v>
-      </c>
-      <c r="F109" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G109" t="n">
         <v>8.5</v>
       </c>
-      <c r="O109" t="n">
-        <v>1</v>
+      <c r="L109" t="n">
+        <v>7.5</v>
       </c>
       <c r="P109" t="n">
         <v>1</v>
       </c>
+      <c r="U109" t="n">
+        <v>1</v>
+      </c>
       <c r="AF109" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG109" t="inlineStr">
         <is>
@@ -6384,7 +6390,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Modelo mecanocuántico y orbitales atómicos</t>
+          <t>Masa molar</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6393,13 +6399,25 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="F110" t="n">
+        <v>8</v>
+      </c>
+      <c r="G110" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O110" t="n">
+        <v>1</v>
+      </c>
+      <c r="P110" t="n">
+        <v>1</v>
       </c>
       <c r="AF110" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG110" t="inlineStr">
         <is>
@@ -6415,7 +6433,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Mol y número de Avogadro</t>
+          <t>Modelo mecanocuántico y orbitales atómicos</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6424,25 +6442,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D111" t="n">
-        <v>8</v>
-      </c>
-      <c r="F111" t="n">
-        <v>8</v>
-      </c>
-      <c r="G111" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O111" t="n">
-        <v>1</v>
-      </c>
-      <c r="P111" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF111" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG111" t="inlineStr">
         <is>
@@ -6458,7 +6464,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Molaridad y unidades químicas de concentración</t>
+          <t>Mol y número de Avogadro</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6472,6 +6478,18 @@
       <c r="D112" t="n">
         <v>8</v>
       </c>
+      <c r="F112" t="n">
+        <v>8</v>
+      </c>
+      <c r="G112" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O112" t="n">
+        <v>1</v>
+      </c>
+      <c r="P112" t="n">
+        <v>1</v>
+      </c>
       <c r="AF112" t="n">
         <v>8</v>
       </c>
@@ -6489,7 +6507,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Compuestos inorgánicos: funciones y nomenclatura</t>
+          <t>Molaridad y unidades químicas de concentración</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6498,31 +6516,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D113" t="n">
-        <v>5</v>
-      </c>
-      <c r="F113" t="n">
         <v>8</v>
       </c>
-      <c r="G113" t="n">
-        <v>6</v>
-      </c>
-      <c r="M113" t="n">
-        <v>7</v>
-      </c>
-      <c r="O113" t="n">
-        <v>1</v>
-      </c>
-      <c r="P113" t="n">
-        <v>1</v>
-      </c>
-      <c r="V113" t="n">
-        <v>1</v>
-      </c>
       <c r="AF113" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG113" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>

--- a/internacional/2_8/Contraste_quimica.xlsx
+++ b/internacional/2_8/Contraste_quimica.xlsx
@@ -5391,7 +5391,7 @@
         <v>1</v>
       </c>
       <c r="AF86" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
         <v>1</v>
       </c>
       <c r="AF96" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG96" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
@@ -5954,10 +5954,10 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G100" t="n">
         <v>8.5</v>
@@ -6294,7 +6294,7 @@
         <v>1</v>
       </c>
       <c r="AF107" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>

--- a/internacional/2_8/Contraste_quimica.xlsx
+++ b/internacional/2_8/Contraste_quimica.xlsx
@@ -3554,7 +3554,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Clasificación de las reacciones químicas</t>
+          <t>Tipo de enlace y propiedades de las sustancias</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3577,11 +3577,8 @@
       <c r="H43" t="n">
         <v>7</v>
       </c>
-      <c r="I43" t="n">
-        <v>6</v>
-      </c>
-      <c r="L43" t="n">
-        <v>7.5</v>
+      <c r="M43" t="n">
+        <v>7</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
@@ -3592,10 +3589,7 @@
       <c r="Q43" t="n">
         <v>1</v>
       </c>
-      <c r="R43" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>1</v>
       </c>
       <c r="AF43" t="n">
@@ -3603,7 +3597,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
@@ -3615,44 +3609,56 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Procesos de la industria química</t>
+          <t>Clasificación de las reacciones químicas</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="n">
         <v>8</v>
       </c>
-      <c r="D44" t="n">
-        <v>8</v>
-      </c>
       <c r="G44" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K44" t="n">
         <v>6</v>
       </c>
-      <c r="M44" t="n">
-        <v>7</v>
+      <c r="H44" t="n">
+        <v>7</v>
+      </c>
+      <c r="I44" t="n">
+        <v>6</v>
+      </c>
+      <c r="L44" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
-      <c r="T44" t="n">
-        <v>1</v>
-      </c>
-      <c r="V44" t="n">
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
         <v>1</v>
       </c>
       <c r="AF44" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
@@ -3664,19 +3670,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tipo de enlace y propiedades de las sustancias</t>
+          <t>Agentes oxidantes y reductores</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
-      </c>
-      <c r="D45" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F45" t="n">
         <v>8</v>
@@ -3687,6 +3690,9 @@
       <c r="H45" t="n">
         <v>7</v>
       </c>
+      <c r="I45" t="n">
+        <v>8</v>
+      </c>
       <c r="M45" t="n">
         <v>7</v>
       </c>
@@ -3699,27 +3705,30 @@
       <c r="Q45" t="n">
         <v>1</v>
       </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
       <c r="V45" t="n">
         <v>1</v>
       </c>
       <c r="AF45" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Agentes oxidantes y reductores</t>
+          <t>Aminoácidos y estructura de las proteínas</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3728,56 +3737,29 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>10</v>
-      </c>
-      <c r="F46" t="n">
-        <v>8</v>
-      </c>
-      <c r="G46" t="n">
         <v>6</v>
       </c>
-      <c r="H46" t="n">
-        <v>7</v>
-      </c>
-      <c r="I46" t="n">
-        <v>8</v>
-      </c>
-      <c r="M46" t="n">
-        <v>7</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1</v>
+      <c r="D46" t="n">
+        <v>6</v>
       </c>
       <c r="AF46" t="n">
         <v>10</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Aminoácidos y estructura de las proteínas</t>
+          <t>Autoionización del agua, Kw y cálculo de pH</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3786,17 +3768,26 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
-      </c>
-      <c r="D47" t="n">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="G47" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M47" t="n">
+        <v>7</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
       </c>
       <c r="AF47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
@@ -3808,7 +3799,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Autoionización del agua, Kw y cálculo de pH</t>
+          <t>Celdas galvánicas</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3817,26 +3808,29 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
-      </c>
-      <c r="G48" t="n">
-        <v>8.5</v>
+        <v>4</v>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+      <c r="I48" t="n">
+        <v>5</v>
       </c>
       <c r="M48" t="n">
         <v>7</v>
       </c>
-      <c r="P48" t="n">
+      <c r="R48" t="n">
         <v>1</v>
       </c>
       <c r="V48" t="n">
         <v>1</v>
       </c>
       <c r="AF48" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
@@ -3848,7 +3842,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Celdas galvánicas</t>
+          <t>Metales, cerámicas y materiales compuestos</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3857,41 +3851,59 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
-      </c>
-      <c r="D49" t="n">
-        <v>4</v>
-      </c>
-      <c r="I49" t="n">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" t="n">
+        <v>6</v>
+      </c>
+      <c r="H49" t="n">
+        <v>7</v>
       </c>
       <c r="M49" t="n">
         <v>7</v>
       </c>
-      <c r="R49" t="n">
+      <c r="N49" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" t="n">
         <v>1</v>
       </c>
       <c r="V49" t="n">
         <v>1</v>
       </c>
+      <c r="Z49" t="n">
+        <v>1</v>
+      </c>
       <c r="AF49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Metales, cerámicas y materiales compuestos</t>
+          <t>Cromatografía</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3902,37 +3914,28 @@
       <c r="C50" t="n">
         <v>10</v>
       </c>
-      <c r="E50" t="n">
-        <v>3</v>
-      </c>
-      <c r="F50" t="n">
-        <v>8</v>
-      </c>
       <c r="G50" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H50" t="n">
         <v>7</v>
       </c>
+      <c r="L50" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M50" t="n">
         <v>7</v>
       </c>
-      <c r="N50" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1</v>
-      </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
       </c>
+      <c r="U50" t="n">
+        <v>1</v>
+      </c>
       <c r="V50" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z50" t="n">
         <v>1</v>
       </c>
       <c r="AF50" t="n">
@@ -3945,14 +3948,14 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cromatografía</t>
+          <t>Diagramas de fases</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3961,38 +3964,17 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10</v>
-      </c>
-      <c r="G51" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H51" t="n">
-        <v>7</v>
-      </c>
-      <c r="L51" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M51" t="n">
-        <v>7</v>
-      </c>
-      <c r="P51" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>1</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="D51" t="n">
+        <v>6</v>
       </c>
       <c r="AF51" t="n">
         <v>10</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
@@ -4004,7 +3986,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Diagramas de fases</t>
+          <t>Mezclas de gases, difusión y gases reales</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4013,10 +3995,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D52" t="n">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="J52" t="n">
+        <v>7</v>
+      </c>
+      <c r="L52" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
       <c r="AF52" t="n">
         <v>10</v>
@@ -4035,7 +4029,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mezclas de gases, difusión y gases reales</t>
+          <t>Ecuación de los gases ideales y volumen molar</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4044,21 +4038,12 @@
         </is>
       </c>
       <c r="C53" t="n">
+        <v>10</v>
+      </c>
+      <c r="F53" t="n">
         <v>8</v>
       </c>
-      <c r="D53" t="n">
-        <v>8</v>
-      </c>
-      <c r="J53" t="n">
-        <v>7</v>
-      </c>
-      <c r="L53" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S53" t="n">
-        <v>1</v>
-      </c>
-      <c r="U53" t="n">
+      <c r="O53" t="n">
         <v>1</v>
       </c>
       <c r="AF53" t="n">
@@ -4066,7 +4051,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH53" t="inlineStr">
@@ -4078,7 +4063,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ecuación de los gases ideales y volumen molar</t>
+          <t>Ecuaciones y reacciones nucleares</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4089,10 +4074,10 @@
       <c r="C54" t="n">
         <v>10</v>
       </c>
-      <c r="F54" t="n">
-        <v>8</v>
-      </c>
-      <c r="O54" t="n">
+      <c r="L54" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="U54" t="n">
         <v>1</v>
       </c>
       <c r="AF54" t="n">
@@ -4112,7 +4097,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ecuaciones y reacciones nucleares</t>
+          <t>El carbono y las moléculas orgánicas</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4123,14 +4108,26 @@
       <c r="C55" t="n">
         <v>10</v>
       </c>
-      <c r="L55" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="U55" t="n">
+      <c r="F55" t="n">
+        <v>8</v>
+      </c>
+      <c r="G55" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M55" t="n">
+        <v>7</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="V55" t="n">
         <v>1</v>
       </c>
       <c r="AF55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -4146,7 +4143,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>El carbono y las moléculas orgánicas</t>
+          <t>Electrólisis y celdas electrolíticas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4157,26 +4154,32 @@
       <c r="C56" t="n">
         <v>10</v>
       </c>
-      <c r="F56" t="n">
-        <v>8</v>
-      </c>
       <c r="G56" t="n">
         <v>8.5</v>
       </c>
+      <c r="H56" t="n">
+        <v>7</v>
+      </c>
+      <c r="I56" t="n">
+        <v>8</v>
+      </c>
       <c r="M56" t="n">
         <v>7</v>
       </c>
-      <c r="O56" t="n">
-        <v>1</v>
-      </c>
       <c r="P56" t="n">
         <v>1</v>
       </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
       <c r="V56" t="n">
         <v>1</v>
       </c>
       <c r="AF56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
@@ -4192,7 +4195,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Electrólisis y celdas electrolíticas</t>
+          <t>Electrolitos fuertes y débiles</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4201,26 +4204,26 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="F57" t="n">
+        <v>8</v>
       </c>
       <c r="G57" t="n">
         <v>8.5</v>
       </c>
-      <c r="H57" t="n">
-        <v>7</v>
-      </c>
       <c r="I57" t="n">
         <v>8</v>
       </c>
       <c r="M57" t="n">
         <v>7</v>
       </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
       <c r="P57" t="n">
         <v>1</v>
       </c>
-      <c r="Q57" t="n">
-        <v>1</v>
-      </c>
       <c r="R57" t="n">
         <v>1</v>
       </c>
@@ -4228,7 +4231,7 @@
         <v>1</v>
       </c>
       <c r="AF57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
@@ -4244,7 +4247,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Electrolitos fuertes y débiles</t>
+          <t>Energía de activación y perfil energético</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4253,38 +4256,23 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>9</v>
-      </c>
-      <c r="F58" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="D58" t="n">
+        <v>5</v>
       </c>
       <c r="G58" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I58" t="n">
-        <v>8</v>
-      </c>
-      <c r="M58" t="n">
-        <v>7</v>
-      </c>
-      <c r="O58" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P58" t="n">
         <v>1</v>
       </c>
-      <c r="R58" t="n">
-        <v>1</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1</v>
-      </c>
       <c r="AF58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH58" t="inlineStr">
@@ -4296,7 +4284,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Energía de activación y perfil energético</t>
+          <t>Energía de enlace</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4305,10 +4293,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
-      </c>
-      <c r="D59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G59" t="n">
         <v>6</v>
@@ -4321,7 +4306,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH59" t="inlineStr">
@@ -4333,7 +4318,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Energía de enlace</t>
+          <t>Entalpía de reacción y ecuaciones termoquímicas</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4345,9 +4330,21 @@
         <v>10</v>
       </c>
       <c r="G60" t="n">
-        <v>6</v>
+        <v>8.5</v>
+      </c>
+      <c r="I60" t="n">
+        <v>7</v>
+      </c>
+      <c r="M60" t="n">
+        <v>7</v>
       </c>
       <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1</v>
+      </c>
+      <c r="V60" t="n">
         <v>1</v>
       </c>
       <c r="AF60" t="n">
@@ -4367,7 +4364,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Entalpía de reacción y ecuaciones termoquímicas</t>
+          <t>Equilibrio químico dinámico</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4376,32 +4373,29 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="D61" t="n">
+        <v>6</v>
       </c>
       <c r="G61" t="n">
         <v>8.5</v>
       </c>
-      <c r="I61" t="n">
-        <v>7</v>
-      </c>
       <c r="M61" t="n">
         <v>7</v>
       </c>
       <c r="P61" t="n">
         <v>1</v>
       </c>
-      <c r="R61" t="n">
-        <v>1</v>
-      </c>
       <c r="V61" t="n">
         <v>1</v>
       </c>
       <c r="AF61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
@@ -4413,7 +4407,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Equilibrio químico dinámico</t>
+          <t>Equilibrio y rapidez en procesos industriales</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4422,29 +4416,20 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
-      </c>
-      <c r="D62" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G62" t="n">
         <v>8.5</v>
       </c>
-      <c r="M62" t="n">
-        <v>7</v>
-      </c>
       <c r="P62" t="n">
         <v>1</v>
       </c>
-      <c r="V62" t="n">
-        <v>1</v>
-      </c>
       <c r="AF62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH62" t="inlineStr">
@@ -4456,7 +4441,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Equilibrio y rapidez en procesos industriales</t>
+          <t>Espectros atómicos y modelo de Bohr</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4465,12 +4450,12 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
-      </c>
-      <c r="G63" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P63" t="n">
+        <v>10</v>
+      </c>
+      <c r="H63" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q63" t="n">
         <v>1</v>
       </c>
       <c r="AF63" t="n">
@@ -4490,7 +4475,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Espectros atómicos y modelo de Bohr</t>
+          <t>Estereoquímica y quiralidad</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4501,14 +4486,14 @@
       <c r="C64" t="n">
         <v>10</v>
       </c>
-      <c r="H64" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q64" t="n">
+      <c r="M64" t="n">
+        <v>7</v>
+      </c>
+      <c r="V64" t="n">
         <v>1</v>
       </c>
       <c r="AF64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
@@ -4524,7 +4509,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Estereoquímica y quiralidad</t>
+          <t>Esterificación e hidrólisis</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4533,7 +4518,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M65" t="n">
         <v>7</v>
@@ -4558,7 +4543,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Esterificación e hidrólisis</t>
+          <t>Estructura y propiedades de los polímeros</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4569,10 +4554,31 @@
       <c r="C66" t="n">
         <v>11</v>
       </c>
+      <c r="F66" t="n">
+        <v>8</v>
+      </c>
+      <c r="G66" t="n">
+        <v>6</v>
+      </c>
+      <c r="H66" t="n">
+        <v>7</v>
+      </c>
       <c r="M66" t="n">
         <v>7</v>
       </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1</v>
+      </c>
       <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z66" t="n">
         <v>1</v>
       </c>
       <c r="AF66" t="n">
@@ -4592,7 +4598,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Estructura y propiedades de los polímeros</t>
+          <t>Fuerza de ácidos y bases: Ka y Kb</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4601,16 +4607,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F67" t="n">
         <v>8</v>
       </c>
       <c r="G67" t="n">
-        <v>6</v>
-      </c>
-      <c r="H67" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="M67" t="n">
         <v>7</v>
@@ -4621,17 +4624,11 @@
       <c r="P67" t="n">
         <v>1</v>
       </c>
-      <c r="Q67" t="n">
-        <v>1</v>
-      </c>
       <c r="V67" t="n">
         <v>1</v>
       </c>
-      <c r="Z67" t="n">
-        <v>1</v>
-      </c>
       <c r="AF67" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
@@ -4647,7 +4644,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Fuerza de ácidos y bases: Ka y Kb</t>
+          <t>Fundamentos de la reactividad orgánica</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4656,32 +4653,17 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>9</v>
-      </c>
-      <c r="F68" t="n">
-        <v>8</v>
-      </c>
-      <c r="G68" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M68" t="n">
-        <v>7</v>
-      </c>
-      <c r="O68" t="n">
-        <v>1</v>
-      </c>
-      <c r="P68" t="n">
-        <v>1</v>
-      </c>
-      <c r="V68" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D68" t="n">
+        <v>5</v>
       </c>
       <c r="AF68" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH68" t="inlineStr">
@@ -4693,7 +4675,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Fundamentos de la reactividad orgánica</t>
+          <t>Grupos funcionales</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4702,17 +4684,32 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
-      </c>
-      <c r="D69" t="n">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="F69" t="n">
+        <v>8</v>
+      </c>
+      <c r="G69" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M69" t="n">
+        <v>7</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
       </c>
       <c r="AF69" t="n">
         <v>11</v>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH69" t="inlineStr">
@@ -4724,7 +4721,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Grupos funcionales</t>
+          <t>Hidrocarburos: alcanos, alquenos y alquinos</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4733,7 +4730,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F70" t="n">
         <v>8</v>
@@ -4753,6 +4750,9 @@
       <c r="V70" t="n">
         <v>1</v>
       </c>
+      <c r="Z70" t="n">
+        <v>1</v>
+      </c>
       <c r="AF70" t="n">
         <v>11</v>
       </c>
@@ -4770,7 +4770,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Hidrocarburos: alcanos, alquenos y alquinos</t>
+          <t>Hidrocarburos aromáticos</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4781,25 +4781,10 @@
       <c r="C71" t="n">
         <v>11</v>
       </c>
-      <c r="F71" t="n">
-        <v>8</v>
-      </c>
       <c r="G71" t="n">
         <v>8.5</v>
       </c>
-      <c r="M71" t="n">
-        <v>7</v>
-      </c>
-      <c r="O71" t="n">
-        <v>1</v>
-      </c>
       <c r="P71" t="n">
-        <v>1</v>
-      </c>
-      <c r="V71" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z71" t="n">
         <v>1</v>
       </c>
       <c r="AF71" t="n">
@@ -4819,7 +4804,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Hidrocarburos aromáticos</t>
+          <t>Isomería estructural</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4828,16 +4813,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>11</v>
-      </c>
-      <c r="G72" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P72" t="n">
+        <v>10</v>
+      </c>
+      <c r="F72" t="n">
+        <v>8</v>
+      </c>
+      <c r="M72" t="n">
+        <v>7</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="V72" t="n">
         <v>1</v>
       </c>
       <c r="AF72" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
@@ -4853,7 +4844,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Isomería estructural</t>
+          <t>Ley de Hess y entalpías de formación</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4864,16 +4855,10 @@
       <c r="C73" t="n">
         <v>10</v>
       </c>
-      <c r="F73" t="n">
-        <v>8</v>
-      </c>
-      <c r="M73" t="n">
-        <v>7</v>
-      </c>
-      <c r="O73" t="n">
-        <v>1</v>
-      </c>
-      <c r="V73" t="n">
+      <c r="G73" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P73" t="n">
         <v>1</v>
       </c>
       <c r="AF73" t="n">
@@ -4893,7 +4878,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ley de Hess y entalpías de formación</t>
+          <t>Leyes de los gases</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4904,10 +4889,16 @@
       <c r="C74" t="n">
         <v>10</v>
       </c>
-      <c r="G74" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P74" t="n">
+      <c r="I74" t="n">
+        <v>6</v>
+      </c>
+      <c r="J74" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" t="n">
         <v>1</v>
       </c>
       <c r="AF74" t="n">
@@ -4927,7 +4918,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Leyes de los gases</t>
+          <t>Leyes ponderales y volumétricas</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4939,10 +4930,10 @@
         <v>10</v>
       </c>
       <c r="I75" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J75" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="R75" t="n">
         <v>1</v>
@@ -4967,7 +4958,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Leyes ponderales y volumétricas</t>
+          <t>Nomenclatura orgánica IUPAC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4976,26 +4967,29 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>10</v>
-      </c>
-      <c r="I76" t="n">
-        <v>7</v>
-      </c>
-      <c r="J76" t="n">
-        <v>7</v>
-      </c>
-      <c r="R76" t="n">
-        <v>1</v>
-      </c>
-      <c r="S76" t="n">
+        <v>7</v>
+      </c>
+      <c r="D76" t="n">
+        <v>7</v>
+      </c>
+      <c r="G76" t="n">
+        <v>6</v>
+      </c>
+      <c r="M76" t="n">
+        <v>7</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="V76" t="n">
         <v>1</v>
       </c>
       <c r="AF76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH76" t="inlineStr">
@@ -5007,7 +5001,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Nomenclatura orgánica IUPAC</t>
+          <t>Polimerización por adición y por condensación</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5016,21 +5010,15 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>7</v>
-      </c>
-      <c r="D77" t="n">
-        <v>7</v>
-      </c>
-      <c r="G77" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M77" t="n">
         <v>7</v>
       </c>
-      <c r="P77" t="n">
-        <v>1</v>
-      </c>
       <c r="V77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z77" t="n">
         <v>1</v>
       </c>
       <c r="AF77" t="n">
@@ -5038,7 +5026,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH77" t="inlineStr">
@@ -5050,7 +5038,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Polimerización por adición y por condensación</t>
+          <t>Polímeros y ambiente</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5061,10 +5049,16 @@
       <c r="C78" t="n">
         <v>11</v>
       </c>
-      <c r="M78" t="n">
-        <v>7</v>
-      </c>
-      <c r="V78" t="n">
+      <c r="F78" t="n">
+        <v>8</v>
+      </c>
+      <c r="H78" t="n">
+        <v>7</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="n">
         <v>1</v>
       </c>
       <c r="Z78" t="n">
@@ -5087,7 +5081,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Polímeros y ambiente</t>
+          <t>Potenciales estándar de electrodo y de celda</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5096,21 +5090,18 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F79" t="n">
         <v>8</v>
       </c>
-      <c r="H79" t="n">
-        <v>7</v>
+      <c r="G79" t="n">
+        <v>8.5</v>
       </c>
       <c r="O79" t="n">
         <v>1</v>
       </c>
-      <c r="Q79" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z79" t="n">
+      <c r="P79" t="n">
         <v>1</v>
       </c>
       <c r="AF79" t="n">
@@ -5130,7 +5121,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Potenciales estándar de electrodo y de celda</t>
+          <t>Principio de Le Chatelier</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5139,22 +5130,22 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>10</v>
-      </c>
-      <c r="F80" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G80" t="n">
         <v>8.5</v>
       </c>
-      <c r="O80" t="n">
-        <v>1</v>
+      <c r="M80" t="n">
+        <v>7</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
       </c>
+      <c r="V80" t="n">
+        <v>1</v>
+      </c>
       <c r="AF80" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG80" t="inlineStr">
         <is>
@@ -5170,7 +5161,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Principio de Le Chatelier</t>
+          <t>Procesos de la industria química</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5179,31 +5170,40 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="D81" t="n">
+        <v>8</v>
       </c>
       <c r="G81" t="n">
         <v>8.5</v>
       </c>
+      <c r="K81" t="n">
+        <v>6</v>
+      </c>
       <c r="M81" t="n">
         <v>7</v>
       </c>
       <c r="P81" t="n">
         <v>1</v>
       </c>
+      <c r="T81" t="n">
+        <v>1</v>
+      </c>
       <c r="V81" t="n">
         <v>1</v>
       </c>
       <c r="AF81" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>

--- a/internacional/2_8/Contraste_quimica.xlsx
+++ b/internacional/2_8/Contraste_quimica.xlsx
@@ -5630,9 +5630,6 @@
       <c r="G92" t="n">
         <v>6</v>
       </c>
-      <c r="H92" t="n">
-        <v>7</v>
-      </c>
       <c r="J92" t="n">
         <v>2.5</v>
       </c>
@@ -5642,13 +5639,13 @@
       <c r="P92" t="n">
         <v>1</v>
       </c>
-      <c r="Q92" t="n">
-        <v>1</v>
-      </c>
       <c r="S92" t="n">
         <v>1</v>
       </c>
       <c r="V92" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z92" t="n">
         <v>1</v>
       </c>
       <c r="AF92" t="n">

--- a/internacional/2_8/Contraste_quimica.xlsx
+++ b/internacional/2_8/Contraste_quimica.xlsx
@@ -888,7 +888,7 @@
         <v>4.5</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>7.5</v>
@@ -1190,7 +1190,7 @@
         <v>4.5</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>7.5</v>
@@ -1272,7 +1272,7 @@
         <v>4.5</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>5</v>
@@ -1555,7 +1555,7 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
@@ -1999,7 +1999,7 @@
         <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
         <v>5</v>
@@ -2148,7 +2148,7 @@
         <v>2.5</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L23" t="n">
         <v>4</v>
@@ -2227,7 +2227,7 @@
         <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
         <v>7</v>
@@ -2516,7 +2516,7 @@
         <v>4.5</v>
       </c>
       <c r="K28" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L28" t="n">
         <v>7.5</v>
@@ -2750,7 +2750,7 @@
         <v>2.5</v>
       </c>
       <c r="K31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
         <v>4</v>
@@ -2957,7 +2957,7 @@
         <v>2.5</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L34" t="n">
         <v>3</v>
@@ -3326,7 +3326,7 @@
         <v>2.5</v>
       </c>
       <c r="K40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L40" t="n">
         <v>3</v>
@@ -3414,7 +3414,7 @@
         <v>2.5</v>
       </c>
       <c r="K41" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L41" t="n">
         <v>7.5</v>
@@ -5055,10 +5055,16 @@
       <c r="H78" t="n">
         <v>7</v>
       </c>
+      <c r="K78" t="n">
+        <v>8</v>
+      </c>
       <c r="O78" t="n">
         <v>1</v>
       </c>
       <c r="Q78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
         <v>1</v>
       </c>
       <c r="Z78" t="n">
@@ -5179,7 +5185,7 @@
         <v>8.5</v>
       </c>
       <c r="K81" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M81" t="n">
         <v>7</v>
@@ -5289,10 +5295,16 @@
       <c r="H84" t="n">
         <v>7</v>
       </c>
+      <c r="K84" t="n">
+        <v>4</v>
+      </c>
       <c r="P84" t="n">
         <v>1</v>
       </c>
       <c r="Q84" t="n">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
         <v>1</v>
       </c>
       <c r="AF84" t="n">

--- a/internacional/2_8/Contraste_quimica.xlsx
+++ b/internacional/2_8/Contraste_quimica.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH122"/>
+  <dimension ref="A1:AH121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3955,7 +3955,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Diagramas de fases</t>
+          <t>Mezclas de gases, difusión y gases reales</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3964,10 +3964,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="J51" t="n">
+        <v>7</v>
+      </c>
+      <c r="L51" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
       <c r="AF51" t="n">
         <v>10</v>
@@ -3986,7 +3998,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mezclas de gases, difusión y gases reales</t>
+          <t>Ecuación de los gases ideales y volumen molar</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3995,21 +4007,12 @@
         </is>
       </c>
       <c r="C52" t="n">
+        <v>10</v>
+      </c>
+      <c r="F52" t="n">
         <v>8</v>
       </c>
-      <c r="D52" t="n">
-        <v>8</v>
-      </c>
-      <c r="J52" t="n">
-        <v>7</v>
-      </c>
-      <c r="L52" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S52" t="n">
-        <v>1</v>
-      </c>
-      <c r="U52" t="n">
+      <c r="O52" t="n">
         <v>1</v>
       </c>
       <c r="AF52" t="n">
@@ -4017,7 +4020,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
@@ -4029,7 +4032,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ecuación de los gases ideales y volumen molar</t>
+          <t>Ecuaciones y reacciones nucleares</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4040,10 +4043,10 @@
       <c r="C53" t="n">
         <v>10</v>
       </c>
-      <c r="F53" t="n">
-        <v>8</v>
-      </c>
-      <c r="O53" t="n">
+      <c r="L53" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="U53" t="n">
         <v>1</v>
       </c>
       <c r="AF53" t="n">
@@ -4063,7 +4066,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ecuaciones y reacciones nucleares</t>
+          <t>El carbono y las moléculas orgánicas</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4074,14 +4077,26 @@
       <c r="C54" t="n">
         <v>10</v>
       </c>
-      <c r="L54" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="U54" t="n">
+      <c r="F54" t="n">
+        <v>8</v>
+      </c>
+      <c r="G54" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M54" t="n">
+        <v>7</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="V54" t="n">
         <v>1</v>
       </c>
       <c r="AF54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
@@ -4097,7 +4112,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>El carbono y las moléculas orgánicas</t>
+          <t>Electrólisis y celdas electrolíticas</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4108,26 +4123,32 @@
       <c r="C55" t="n">
         <v>10</v>
       </c>
-      <c r="F55" t="n">
-        <v>8</v>
-      </c>
       <c r="G55" t="n">
         <v>8.5</v>
       </c>
+      <c r="H55" t="n">
+        <v>7</v>
+      </c>
+      <c r="I55" t="n">
+        <v>8</v>
+      </c>
       <c r="M55" t="n">
         <v>7</v>
       </c>
-      <c r="O55" t="n">
-        <v>1</v>
-      </c>
       <c r="P55" t="n">
         <v>1</v>
       </c>
+      <c r="Q55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
       <c r="V55" t="n">
         <v>1</v>
       </c>
       <c r="AF55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -4143,7 +4164,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Electrólisis y celdas electrolíticas</t>
+          <t>Electrolitos fuertes y débiles</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4152,26 +4173,26 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="F56" t="n">
+        <v>8</v>
       </c>
       <c r="G56" t="n">
         <v>8.5</v>
       </c>
-      <c r="H56" t="n">
-        <v>7</v>
-      </c>
       <c r="I56" t="n">
         <v>8</v>
       </c>
       <c r="M56" t="n">
         <v>7</v>
       </c>
+      <c r="O56" t="n">
+        <v>1</v>
+      </c>
       <c r="P56" t="n">
         <v>1</v>
       </c>
-      <c r="Q56" t="n">
-        <v>1</v>
-      </c>
       <c r="R56" t="n">
         <v>1</v>
       </c>
@@ -4179,7 +4200,7 @@
         <v>1</v>
       </c>
       <c r="AF56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
@@ -4195,7 +4216,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Electrolitos fuertes y débiles</t>
+          <t>Energía de activación y perfil energético</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4204,38 +4225,23 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>9</v>
-      </c>
-      <c r="F57" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="D57" t="n">
+        <v>5</v>
       </c>
       <c r="G57" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I57" t="n">
-        <v>8</v>
-      </c>
-      <c r="M57" t="n">
-        <v>7</v>
-      </c>
-      <c r="O57" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P57" t="n">
         <v>1</v>
       </c>
-      <c r="R57" t="n">
-        <v>1</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1</v>
-      </c>
       <c r="AF57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
@@ -4247,7 +4253,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Energía de activación y perfil energético</t>
+          <t>Energía de enlace</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4256,10 +4262,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
-      </c>
-      <c r="D58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G58" t="n">
         <v>6</v>
@@ -4272,7 +4275,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH58" t="inlineStr">
@@ -4284,7 +4287,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Energía de enlace</t>
+          <t>Entalpía de reacción y ecuaciones termoquímicas</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4296,9 +4299,21 @@
         <v>10</v>
       </c>
       <c r="G59" t="n">
-        <v>6</v>
+        <v>8.5</v>
+      </c>
+      <c r="I59" t="n">
+        <v>7</v>
+      </c>
+      <c r="M59" t="n">
+        <v>7</v>
       </c>
       <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
+      <c r="V59" t="n">
         <v>1</v>
       </c>
       <c r="AF59" t="n">
@@ -4318,7 +4333,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Entalpía de reacción y ecuaciones termoquímicas</t>
+          <t>Equilibrio químico dinámico</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4327,32 +4342,29 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="D60" t="n">
+        <v>6</v>
       </c>
       <c r="G60" t="n">
         <v>8.5</v>
       </c>
-      <c r="I60" t="n">
-        <v>7</v>
-      </c>
       <c r="M60" t="n">
         <v>7</v>
       </c>
       <c r="P60" t="n">
         <v>1</v>
       </c>
-      <c r="R60" t="n">
-        <v>1</v>
-      </c>
       <c r="V60" t="n">
         <v>1</v>
       </c>
       <c r="AF60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH60" t="inlineStr">
@@ -4364,7 +4376,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Equilibrio químico dinámico</t>
+          <t>Equilibrio y rapidez en procesos industriales</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4373,29 +4385,20 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
-      </c>
-      <c r="D61" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G61" t="n">
         <v>8.5</v>
       </c>
-      <c r="M61" t="n">
-        <v>7</v>
-      </c>
       <c r="P61" t="n">
         <v>1</v>
       </c>
-      <c r="V61" t="n">
-        <v>1</v>
-      </c>
       <c r="AF61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
@@ -4407,7 +4410,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Equilibrio y rapidez en procesos industriales</t>
+          <t>Espectros atómicos y modelo de Bohr</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4416,12 +4419,12 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9</v>
-      </c>
-      <c r="G62" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P62" t="n">
+        <v>10</v>
+      </c>
+      <c r="H62" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q62" t="n">
         <v>1</v>
       </c>
       <c r="AF62" t="n">
@@ -4441,7 +4444,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Espectros atómicos y modelo de Bohr</t>
+          <t>Estereoquímica y quiralidad</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4452,14 +4455,14 @@
       <c r="C63" t="n">
         <v>10</v>
       </c>
-      <c r="H63" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q63" t="n">
+      <c r="M63" t="n">
+        <v>7</v>
+      </c>
+      <c r="V63" t="n">
         <v>1</v>
       </c>
       <c r="AF63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
@@ -4475,7 +4478,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Estereoquímica y quiralidad</t>
+          <t>Esterificación e hidrólisis</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4484,7 +4487,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M64" t="n">
         <v>7</v>
@@ -4509,7 +4512,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Esterificación e hidrólisis</t>
+          <t>Estructura y propiedades de los polímeros</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4520,10 +4523,31 @@
       <c r="C65" t="n">
         <v>11</v>
       </c>
+      <c r="F65" t="n">
+        <v>8</v>
+      </c>
+      <c r="G65" t="n">
+        <v>6</v>
+      </c>
+      <c r="H65" t="n">
+        <v>7</v>
+      </c>
       <c r="M65" t="n">
         <v>7</v>
       </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
       <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z65" t="n">
         <v>1</v>
       </c>
       <c r="AF65" t="n">
@@ -4543,7 +4567,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Estructura y propiedades de los polímeros</t>
+          <t>Fuerza de ácidos y bases: Ka y Kb</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4552,16 +4576,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F66" t="n">
         <v>8</v>
       </c>
       <c r="G66" t="n">
-        <v>6</v>
-      </c>
-      <c r="H66" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="M66" t="n">
         <v>7</v>
@@ -4572,17 +4593,11 @@
       <c r="P66" t="n">
         <v>1</v>
       </c>
-      <c r="Q66" t="n">
-        <v>1</v>
-      </c>
       <c r="V66" t="n">
         <v>1</v>
       </c>
-      <c r="Z66" t="n">
-        <v>1</v>
-      </c>
       <c r="AF66" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
@@ -4598,7 +4613,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Fuerza de ácidos y bases: Ka y Kb</t>
+          <t>Fundamentos de la reactividad orgánica</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4607,32 +4622,17 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>9</v>
-      </c>
-      <c r="F67" t="n">
-        <v>8</v>
-      </c>
-      <c r="G67" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M67" t="n">
-        <v>7</v>
-      </c>
-      <c r="O67" t="n">
-        <v>1</v>
-      </c>
-      <c r="P67" t="n">
-        <v>1</v>
-      </c>
-      <c r="V67" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D67" t="n">
+        <v>5</v>
       </c>
       <c r="AF67" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH67" t="inlineStr">
@@ -4644,7 +4644,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Fundamentos de la reactividad orgánica</t>
+          <t>Grupos funcionales</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4653,17 +4653,32 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
-      </c>
-      <c r="D68" t="n">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="F68" t="n">
+        <v>8</v>
+      </c>
+      <c r="G68" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M68" t="n">
+        <v>7</v>
+      </c>
+      <c r="O68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
       </c>
       <c r="AF68" t="n">
         <v>11</v>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH68" t="inlineStr">
@@ -4675,7 +4690,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Grupos funcionales</t>
+          <t>Hidrocarburos: alcanos, alquenos y alquinos</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4684,7 +4699,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F69" t="n">
         <v>8</v>
@@ -4704,6 +4719,9 @@
       <c r="V69" t="n">
         <v>1</v>
       </c>
+      <c r="Z69" t="n">
+        <v>1</v>
+      </c>
       <c r="AF69" t="n">
         <v>11</v>
       </c>
@@ -4721,7 +4739,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Hidrocarburos: alcanos, alquenos y alquinos</t>
+          <t>Hidrocarburos aromáticos</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4732,25 +4750,10 @@
       <c r="C70" t="n">
         <v>11</v>
       </c>
-      <c r="F70" t="n">
-        <v>8</v>
-      </c>
       <c r="G70" t="n">
         <v>8.5</v>
       </c>
-      <c r="M70" t="n">
-        <v>7</v>
-      </c>
-      <c r="O70" t="n">
-        <v>1</v>
-      </c>
       <c r="P70" t="n">
-        <v>1</v>
-      </c>
-      <c r="V70" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z70" t="n">
         <v>1</v>
       </c>
       <c r="AF70" t="n">
@@ -4770,7 +4773,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Hidrocarburos aromáticos</t>
+          <t>Isomería estructural</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4779,16 +4782,22 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>11</v>
-      </c>
-      <c r="G71" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P71" t="n">
+        <v>10</v>
+      </c>
+      <c r="F71" t="n">
+        <v>8</v>
+      </c>
+      <c r="M71" t="n">
+        <v>7</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="V71" t="n">
         <v>1</v>
       </c>
       <c r="AF71" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG71" t="inlineStr">
         <is>
@@ -4804,7 +4813,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Isomería estructural</t>
+          <t>Ley de Hess y entalpías de formación</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4815,16 +4824,10 @@
       <c r="C72" t="n">
         <v>10</v>
       </c>
-      <c r="F72" t="n">
-        <v>8</v>
-      </c>
-      <c r="M72" t="n">
-        <v>7</v>
-      </c>
-      <c r="O72" t="n">
-        <v>1</v>
-      </c>
-      <c r="V72" t="n">
+      <c r="G72" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P72" t="n">
         <v>1</v>
       </c>
       <c r="AF72" t="n">
@@ -4844,7 +4847,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ley de Hess y entalpías de formación</t>
+          <t>Leyes de los gases</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,10 +4858,16 @@
       <c r="C73" t="n">
         <v>10</v>
       </c>
-      <c r="G73" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P73" t="n">
+      <c r="I73" t="n">
+        <v>6</v>
+      </c>
+      <c r="J73" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1</v>
+      </c>
+      <c r="S73" t="n">
         <v>1</v>
       </c>
       <c r="AF73" t="n">
@@ -4878,7 +4887,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Leyes de los gases</t>
+          <t>Leyes ponderales y volumétricas</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4890,10 +4899,10 @@
         <v>10</v>
       </c>
       <c r="I74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J74" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="R74" t="n">
         <v>1</v>
@@ -4918,7 +4927,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Leyes ponderales y volumétricas</t>
+          <t>Nomenclatura orgánica IUPAC</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4927,26 +4936,29 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>10</v>
-      </c>
-      <c r="I75" t="n">
-        <v>7</v>
-      </c>
-      <c r="J75" t="n">
-        <v>7</v>
-      </c>
-      <c r="R75" t="n">
-        <v>1</v>
-      </c>
-      <c r="S75" t="n">
+        <v>7</v>
+      </c>
+      <c r="D75" t="n">
+        <v>7</v>
+      </c>
+      <c r="G75" t="n">
+        <v>6</v>
+      </c>
+      <c r="M75" t="n">
+        <v>7</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
         <v>1</v>
       </c>
       <c r="AF75" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH75" t="inlineStr">
@@ -4958,7 +4970,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Nomenclatura orgánica IUPAC</t>
+          <t>Polimerización por adición y por condensación</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4967,21 +4979,15 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>7</v>
-      </c>
-      <c r="D76" t="n">
-        <v>7</v>
-      </c>
-      <c r="G76" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M76" t="n">
         <v>7</v>
       </c>
-      <c r="P76" t="n">
-        <v>1</v>
-      </c>
       <c r="V76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z76" t="n">
         <v>1</v>
       </c>
       <c r="AF76" t="n">
@@ -4989,7 +4995,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH76" t="inlineStr">
@@ -5001,7 +5007,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Polimerización por adición y por condensación</t>
+          <t>Polímeros y ambiente</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5012,10 +5018,22 @@
       <c r="C77" t="n">
         <v>11</v>
       </c>
-      <c r="M77" t="n">
-        <v>7</v>
-      </c>
-      <c r="V77" t="n">
+      <c r="F77" t="n">
+        <v>8</v>
+      </c>
+      <c r="H77" t="n">
+        <v>7</v>
+      </c>
+      <c r="K77" t="n">
+        <v>8</v>
+      </c>
+      <c r="O77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
         <v>1</v>
       </c>
       <c r="Z77" t="n">
@@ -5038,7 +5056,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Polímeros y ambiente</t>
+          <t>Potenciales estándar de electrodo y de celda</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5047,27 +5065,18 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F78" t="n">
         <v>8</v>
       </c>
-      <c r="H78" t="n">
-        <v>7</v>
-      </c>
-      <c r="K78" t="n">
-        <v>8</v>
+      <c r="G78" t="n">
+        <v>8.5</v>
       </c>
       <c r="O78" t="n">
         <v>1</v>
       </c>
-      <c r="Q78" t="n">
-        <v>1</v>
-      </c>
-      <c r="T78" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z78" t="n">
+      <c r="P78" t="n">
         <v>1</v>
       </c>
       <c r="AF78" t="n">
@@ -5087,7 +5096,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Potenciales estándar de electrodo y de celda</t>
+          <t>Principio de Le Chatelier</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5096,22 +5105,22 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>10</v>
-      </c>
-      <c r="F79" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G79" t="n">
         <v>8.5</v>
       </c>
-      <c r="O79" t="n">
-        <v>1</v>
+      <c r="M79" t="n">
+        <v>7</v>
       </c>
       <c r="P79" t="n">
         <v>1</v>
       </c>
+      <c r="V79" t="n">
+        <v>1</v>
+      </c>
       <c r="AF79" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
@@ -5127,7 +5136,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Principio de Le Chatelier</t>
+          <t>Procesos de la industria química</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5136,38 +5145,47 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="D80" t="n">
+        <v>8</v>
       </c>
       <c r="G80" t="n">
         <v>8.5</v>
       </c>
+      <c r="K80" t="n">
+        <v>4</v>
+      </c>
       <c r="M80" t="n">
         <v>7</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
       </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
       <c r="V80" t="n">
         <v>1</v>
       </c>
       <c r="AF80" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Procesos de la industria química</t>
+          <t>Química de los carbohidratos</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5176,31 +5194,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D81" t="n">
-        <v>8</v>
-      </c>
-      <c r="G81" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K81" t="n">
-        <v>4</v>
-      </c>
-      <c r="M81" t="n">
-        <v>7</v>
-      </c>
-      <c r="P81" t="n">
-        <v>1</v>
-      </c>
-      <c r="T81" t="n">
-        <v>1</v>
-      </c>
-      <c r="V81" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AF81" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG81" t="inlineStr">
         <is>
@@ -5209,14 +5209,14 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Química de los carbohidratos</t>
+          <t>Química de los lípidos</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5247,7 +5247,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Química de los lípidos</t>
+          <t>Química verde y economía atómica</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5256,17 +5256,32 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>6</v>
-      </c>
-      <c r="D83" t="n">
-        <v>6</v>
+        <v>11</v>
+      </c>
+      <c r="G83" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H83" t="n">
+        <v>7</v>
+      </c>
+      <c r="K83" t="n">
+        <v>4</v>
+      </c>
+      <c r="P83" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>1</v>
       </c>
       <c r="AF83" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH83" t="inlineStr">
@@ -5278,7 +5293,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Química verde y economía atómica</t>
+          <t>Radiactividad y emisiones nucleares</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5287,32 +5302,23 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>11</v>
-      </c>
-      <c r="G84" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H84" t="n">
-        <v>7</v>
-      </c>
-      <c r="K84" t="n">
-        <v>4</v>
-      </c>
-      <c r="P84" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>1</v>
-      </c>
-      <c r="T84" t="n">
+        <v>5</v>
+      </c>
+      <c r="D84" t="n">
+        <v>5</v>
+      </c>
+      <c r="E84" t="n">
+        <v>8</v>
+      </c>
+      <c r="N84" t="n">
         <v>1</v>
       </c>
       <c r="AF84" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH84" t="inlineStr">
@@ -5324,7 +5330,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Radiactividad y emisiones nucleares</t>
+          <t>Factores que afectan la rapidez de reacción</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5333,23 +5339,44 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D85" t="n">
-        <v>5</v>
-      </c>
-      <c r="E85" t="n">
+        <v>6</v>
+      </c>
+      <c r="F85" t="n">
         <v>8</v>
       </c>
-      <c r="N85" t="n">
+      <c r="G85" t="n">
+        <v>6</v>
+      </c>
+      <c r="H85" t="n">
+        <v>7</v>
+      </c>
+      <c r="M85" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1</v>
+      </c>
+      <c r="P85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1</v>
+      </c>
+      <c r="V85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z85" t="n">
         <v>1</v>
       </c>
       <c r="AF85" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH85" t="inlineStr">
@@ -5361,7 +5388,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Factores que afectan la rapidez de reacción</t>
+          <t>Reacciones de precipitación e identificación de iones</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5370,44 +5397,32 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>6</v>
-      </c>
-      <c r="D86" t="n">
-        <v>6</v>
-      </c>
-      <c r="F86" t="n">
+        <v>9</v>
+      </c>
+      <c r="H86" t="n">
+        <v>7</v>
+      </c>
+      <c r="I86" t="n">
         <v>8</v>
       </c>
-      <c r="G86" t="n">
-        <v>6</v>
-      </c>
-      <c r="H86" t="n">
-        <v>7</v>
-      </c>
       <c r="M86" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O86" t="n">
-        <v>1</v>
-      </c>
-      <c r="P86" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q86" t="n">
         <v>1</v>
       </c>
+      <c r="R86" t="n">
+        <v>1</v>
+      </c>
       <c r="V86" t="n">
         <v>1</v>
       </c>
-      <c r="Z86" t="n">
-        <v>1</v>
-      </c>
       <c r="AF86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH86" t="inlineStr">
@@ -5419,7 +5434,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Reacciones de precipitación e identificación de iones</t>
+          <t>Reacciones orgánicas características</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5428,28 +5443,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>9</v>
-      </c>
-      <c r="H87" t="n">
-        <v>7</v>
-      </c>
-      <c r="I87" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M87" t="n">
         <v>7</v>
       </c>
-      <c r="Q87" t="n">
-        <v>1</v>
-      </c>
-      <c r="R87" t="n">
-        <v>1</v>
-      </c>
       <c r="V87" t="n">
         <v>1</v>
       </c>
       <c r="AF87" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
@@ -5465,7 +5468,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Reacciones orgánicas características</t>
+          <t>Reactivo limitante y en exceso</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5474,16 +5477,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>11</v>
-      </c>
-      <c r="M88" t="n">
-        <v>7</v>
-      </c>
-      <c r="V88" t="n">
+        <v>10</v>
+      </c>
+      <c r="G88" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P88" t="n">
         <v>1</v>
       </c>
       <c r="AF88" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
@@ -5499,7 +5502,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Reactivo limitante y en exceso</t>
+          <t>Redes covalentes y alótropos del carbono</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5510,10 +5513,22 @@
       <c r="C89" t="n">
         <v>10</v>
       </c>
+      <c r="F89" t="n">
+        <v>8</v>
+      </c>
       <c r="G89" t="n">
         <v>8.5</v>
       </c>
+      <c r="M89" t="n">
+        <v>7</v>
+      </c>
+      <c r="O89" t="n">
+        <v>1</v>
+      </c>
       <c r="P89" t="n">
+        <v>1</v>
+      </c>
+      <c r="V89" t="n">
         <v>1</v>
       </c>
       <c r="AF89" t="n">
@@ -5533,7 +5548,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Redes covalentes y alótropos del carbono</t>
+          <t>Semivida, series de desintegración y residuos radiactivos</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5544,14 +5559,17 @@
       <c r="C90" t="n">
         <v>10</v>
       </c>
+      <c r="E90" t="n">
+        <v>8</v>
+      </c>
       <c r="F90" t="n">
         <v>8</v>
       </c>
       <c r="G90" t="n">
         <v>8.5</v>
       </c>
-      <c r="M90" t="n">
-        <v>7</v>
+      <c r="N90" t="n">
+        <v>1</v>
       </c>
       <c r="O90" t="n">
         <v>1</v>
@@ -5559,11 +5577,8 @@
       <c r="P90" t="n">
         <v>1</v>
       </c>
-      <c r="V90" t="n">
-        <v>1</v>
-      </c>
       <c r="AF90" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG90" t="inlineStr">
         <is>
@@ -5579,7 +5594,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Semivida, series de desintegración y residuos radiactivos</t>
+          <t>Teoría cinética de los gases</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5588,32 +5603,38 @@
         </is>
       </c>
       <c r="C91" t="n">
+        <v>8</v>
+      </c>
+      <c r="D91" t="n">
+        <v>8</v>
+      </c>
+      <c r="G91" t="n">
+        <v>6</v>
+      </c>
+      <c r="J91" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M91" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P91" t="n">
+        <v>1</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1</v>
+      </c>
+      <c r="V91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF91" t="n">
         <v>10</v>
       </c>
-      <c r="E91" t="n">
-        <v>8</v>
-      </c>
-      <c r="F91" t="n">
-        <v>8</v>
-      </c>
-      <c r="G91" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="N91" t="n">
-        <v>1</v>
-      </c>
-      <c r="O91" t="n">
-        <v>1</v>
-      </c>
-      <c r="P91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF91" t="n">
-        <v>11</v>
-      </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH91" t="inlineStr">
@@ -5625,7 +5646,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Teoría cinética de los gases</t>
+          <t>Teoría de colisiones</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5634,24 +5655,21 @@
         </is>
       </c>
       <c r="C92" t="n">
+        <v>9</v>
+      </c>
+      <c r="F92" t="n">
         <v>8</v>
       </c>
-      <c r="D92" t="n">
-        <v>8</v>
-      </c>
       <c r="G92" t="n">
-        <v>6</v>
-      </c>
-      <c r="J92" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="M92" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="O92" t="n">
+        <v>1</v>
       </c>
       <c r="P92" t="n">
-        <v>1</v>
-      </c>
-      <c r="S92" t="n">
         <v>1</v>
       </c>
       <c r="V92" t="n">
@@ -5665,7 +5683,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
@@ -5677,7 +5695,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Teoría de colisiones</t>
+          <t>Teorías ácido-base (Arrhenius, Brønsted-Lowry, Lewis)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5694,6 +5712,9 @@
       <c r="G93" t="n">
         <v>8.5</v>
       </c>
+      <c r="I93" t="n">
+        <v>8</v>
+      </c>
       <c r="M93" t="n">
         <v>7</v>
       </c>
@@ -5703,14 +5724,14 @@
       <c r="P93" t="n">
         <v>1</v>
       </c>
+      <c r="R93" t="n">
+        <v>1</v>
+      </c>
       <c r="V93" t="n">
         <v>1</v>
       </c>
-      <c r="Z93" t="n">
-        <v>1</v>
-      </c>
       <c r="AF93" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG93" t="inlineStr">
         <is>
@@ -5726,7 +5747,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Teorías ácido-base (Arrhenius, Brønsted-Lowry, Lewis)</t>
+          <t>Medición de la velocidad de reacción</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5735,34 +5756,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>9</v>
-      </c>
-      <c r="F94" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G94" t="n">
         <v>8.5</v>
       </c>
-      <c r="I94" t="n">
-        <v>8</v>
-      </c>
-      <c r="M94" t="n">
-        <v>7</v>
-      </c>
-      <c r="O94" t="n">
-        <v>1</v>
-      </c>
       <c r="P94" t="n">
         <v>1</v>
       </c>
-      <c r="R94" t="n">
-        <v>1</v>
-      </c>
-      <c r="V94" t="n">
-        <v>1</v>
-      </c>
       <c r="AF94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
@@ -5778,21 +5781,30 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Medición de la velocidad de reacción</t>
+          <t>Catalizadores</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="D95" t="n">
+        <v>6</v>
       </c>
       <c r="G95" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="M95" t="n">
+        <v>7</v>
       </c>
       <c r="P95" t="n">
+        <v>1</v>
+      </c>
+      <c r="V95" t="n">
         <v>1</v>
       </c>
       <c r="AF95" t="n">
@@ -5800,7 +5812,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH95" t="inlineStr">
@@ -5812,7 +5824,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Catalizadores</t>
+          <t>Composición porcentual y fórmulas empírica y molecular</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5827,15 +5839,9 @@
         <v>6</v>
       </c>
       <c r="G96" t="n">
-        <v>6</v>
-      </c>
-      <c r="M96" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="P96" t="n">
-        <v>1</v>
-      </c>
-      <c r="V96" t="n">
         <v>1</v>
       </c>
       <c r="AF96" t="n">
@@ -5855,7 +5861,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Composición porcentual y fórmulas empírica y molecular</t>
+          <t>Configuración electrónica por orbitales</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5864,19 +5870,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D97" t="n">
-        <v>6</v>
-      </c>
-      <c r="G97" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P97" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
@@ -5885,14 +5885,14 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Configuración electrónica por orbitales</t>
+          <t>Electronegatividad y polaridad de enlace</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5901,13 +5901,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG98" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Electronegatividad y polaridad de enlace</t>
+          <t>Electrones de valencia y regla del octeto</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5937,6 +5937,12 @@
       <c r="D99" t="n">
         <v>6</v>
       </c>
+      <c r="G99" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P99" t="n">
+        <v>1</v>
+      </c>
       <c r="AF99" t="n">
         <v>6</v>
       </c>
@@ -5954,7 +5960,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Electrones de valencia y regla del octeto</t>
+          <t>Enlace covalente</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5968,9 +5974,15 @@
       <c r="D100" t="n">
         <v>6</v>
       </c>
+      <c r="F100" t="n">
+        <v>8</v>
+      </c>
       <c r="G100" t="n">
         <v>8.5</v>
       </c>
+      <c r="O100" t="n">
+        <v>1</v>
+      </c>
       <c r="P100" t="n">
         <v>1</v>
       </c>
@@ -5991,7 +6003,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Enlace covalente</t>
+          <t>Enlace iónico</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6000,10 +6012,10 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F101" t="n">
         <v>8</v>
@@ -6018,7 +6030,7 @@
         <v>1</v>
       </c>
       <c r="AF101" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG101" t="inlineStr">
         <is>
@@ -6034,7 +6046,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Enlace iónico</t>
+          <t>Enlace metálico</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6043,10 +6055,10 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F102" t="n">
         <v>8</v>
@@ -6054,14 +6066,20 @@
       <c r="G102" t="n">
         <v>8.5</v>
       </c>
+      <c r="H102" t="n">
+        <v>7</v>
+      </c>
       <c r="O102" t="n">
         <v>1</v>
       </c>
       <c r="P102" t="n">
         <v>1</v>
       </c>
+      <c r="Q102" t="n">
+        <v>1</v>
+      </c>
       <c r="AF102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG102" t="inlineStr">
         <is>
@@ -6070,14 +6088,14 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Enlace metálico</t>
+          <t>Enlace químico</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6086,10 +6104,10 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F103" t="n">
         <v>8</v>
@@ -6100,6 +6118,9 @@
       <c r="H103" t="n">
         <v>7</v>
       </c>
+      <c r="L103" t="n">
+        <v>7.5</v>
+      </c>
       <c r="O103" t="n">
         <v>1</v>
       </c>
@@ -6109,24 +6130,27 @@
       <c r="Q103" t="n">
         <v>1</v>
       </c>
+      <c r="U103" t="n">
+        <v>1</v>
+      </c>
       <c r="AF103" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Enlace químico</t>
+          <t>Notación y estructuras de Lewis</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6135,53 +6159,35 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D104" t="n">
-        <v>5</v>
-      </c>
-      <c r="F104" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G104" t="n">
         <v>8.5</v>
       </c>
-      <c r="H104" t="n">
-        <v>7</v>
-      </c>
-      <c r="L104" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O104" t="n">
-        <v>1</v>
-      </c>
       <c r="P104" t="n">
         <v>1</v>
       </c>
-      <c r="Q104" t="n">
-        <v>1</v>
-      </c>
-      <c r="U104" t="n">
-        <v>1</v>
-      </c>
       <c r="AF104" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Notación y estructuras de Lewis</t>
+          <t>Fuerzas intermoleculares</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6195,10 +6201,22 @@
       <c r="D105" t="n">
         <v>6</v>
       </c>
+      <c r="E105" t="n">
+        <v>6</v>
+      </c>
       <c r="G105" t="n">
         <v>8.5</v>
       </c>
+      <c r="J105" t="n">
+        <v>7</v>
+      </c>
+      <c r="N105" t="n">
+        <v>1</v>
+      </c>
       <c r="P105" t="n">
+        <v>1</v>
+      </c>
+      <c r="S105" t="n">
         <v>1</v>
       </c>
       <c r="AF105" t="n">
@@ -6211,14 +6229,14 @@
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Fuerzas intermoleculares</t>
+          <t>Fuerzas intermoleculares y propiedades físicas</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6227,27 +6245,30 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>6</v>
-      </c>
-      <c r="E106" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="F106" t="n">
+        <v>8</v>
       </c>
       <c r="G106" t="n">
         <v>8.5</v>
       </c>
-      <c r="J106" t="n">
-        <v>7</v>
-      </c>
-      <c r="N106" t="n">
+      <c r="H106" t="n">
+        <v>7</v>
+      </c>
+      <c r="O106" t="n">
         <v>1</v>
       </c>
       <c r="P106" t="n">
         <v>1</v>
       </c>
-      <c r="S106" t="n">
+      <c r="Q106" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z106" t="n">
         <v>1</v>
       </c>
       <c r="AF106" t="n">
@@ -6260,14 +6281,14 @@
       </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Fuerzas intermoleculares y propiedades físicas</t>
+          <t>Geometría molecular (RPECV)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6276,30 +6297,15 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D107" t="n">
-        <v>3</v>
-      </c>
-      <c r="F107" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G107" t="n">
         <v>8.5</v>
       </c>
-      <c r="H107" t="n">
-        <v>7</v>
-      </c>
-      <c r="O107" t="n">
-        <v>1</v>
-      </c>
       <c r="P107" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z107" t="n">
         <v>1</v>
       </c>
       <c r="AF107" t="n">
@@ -6312,14 +6318,14 @@
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Geometría molecular (RPECV)</t>
+          <t>Isótopos</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6328,19 +6334,25 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G108" t="n">
         <v>8.5</v>
       </c>
+      <c r="L108" t="n">
+        <v>7.5</v>
+      </c>
       <c r="P108" t="n">
         <v>1</v>
       </c>
+      <c r="U108" t="n">
+        <v>1</v>
+      </c>
       <c r="AF108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG108" t="inlineStr">
         <is>
@@ -6356,7 +6368,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Isótopos</t>
+          <t>Masa molar</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6365,25 +6377,25 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="F109" t="n">
+        <v>8</v>
       </c>
       <c r="G109" t="n">
         <v>8.5</v>
       </c>
-      <c r="L109" t="n">
-        <v>7.5</v>
+      <c r="O109" t="n">
+        <v>1</v>
       </c>
       <c r="P109" t="n">
         <v>1</v>
       </c>
-      <c r="U109" t="n">
-        <v>1</v>
-      </c>
       <c r="AF109" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG109" t="inlineStr">
         <is>
@@ -6399,7 +6411,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Masa molar</t>
+          <t>Modelo mecanocuántico y orbitales atómicos</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6408,25 +6420,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D110" t="n">
-        <v>8</v>
-      </c>
-      <c r="F110" t="n">
-        <v>8</v>
-      </c>
-      <c r="G110" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O110" t="n">
-        <v>1</v>
-      </c>
-      <c r="P110" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF110" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG110" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Modelo mecanocuántico y orbitales atómicos</t>
+          <t>Mol y número de Avogadro</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6451,13 +6451,25 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D111" t="n">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="F111" t="n">
+        <v>8</v>
+      </c>
+      <c r="G111" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O111" t="n">
+        <v>1</v>
+      </c>
+      <c r="P111" t="n">
+        <v>1</v>
       </c>
       <c r="AF111" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG111" t="inlineStr">
         <is>
@@ -6473,7 +6485,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Mol y número de Avogadro</t>
+          <t>Molaridad y unidades químicas de concentración</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6487,18 +6499,6 @@
       <c r="D112" t="n">
         <v>8</v>
       </c>
-      <c r="F112" t="n">
-        <v>8</v>
-      </c>
-      <c r="G112" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O112" t="n">
-        <v>1</v>
-      </c>
-      <c r="P112" t="n">
-        <v>1</v>
-      </c>
       <c r="AF112" t="n">
         <v>8</v>
       </c>
@@ -6516,7 +6516,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Molaridad y unidades químicas de concentración</t>
+          <t>Número de oxidación</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6525,13 +6525,19 @@
         </is>
       </c>
       <c r="C113" t="n">
+        <v>5</v>
+      </c>
+      <c r="D113" t="n">
+        <v>5</v>
+      </c>
+      <c r="F113" t="n">
         <v>8</v>
       </c>
-      <c r="D113" t="n">
-        <v>8</v>
+      <c r="O113" t="n">
+        <v>1</v>
       </c>
       <c r="AF113" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG113" t="inlineStr">
         <is>
@@ -6547,7 +6553,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Número de oxidación</t>
+          <t>Números cuánticos</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6561,12 +6567,6 @@
       <c r="D114" t="n">
         <v>5</v>
       </c>
-      <c r="F114" t="n">
-        <v>8</v>
-      </c>
-      <c r="O114" t="n">
-        <v>1</v>
-      </c>
       <c r="AF114" t="n">
         <v>5</v>
       </c>
@@ -6584,7 +6584,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Números cuánticos</t>
+          <t>Polaridad molecular</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6593,13 +6593,25 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D115" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="F115" t="n">
+        <v>8</v>
+      </c>
+      <c r="K115" t="n">
+        <v>6</v>
+      </c>
+      <c r="O115" t="n">
+        <v>1</v>
+      </c>
+      <c r="T115" t="n">
+        <v>1</v>
       </c>
       <c r="AF115" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG115" t="inlineStr">
         <is>
@@ -6615,7 +6627,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Polaridad molecular</t>
+          <t>Propiedades coligativas</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6624,25 +6636,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D116" t="n">
-        <v>6</v>
-      </c>
-      <c r="F116" t="n">
         <v>8</v>
       </c>
-      <c r="K116" t="n">
-        <v>6</v>
-      </c>
-      <c r="O116" t="n">
-        <v>1</v>
-      </c>
-      <c r="T116" t="n">
-        <v>1</v>
-      </c>
       <c r="AF116" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG116" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Propiedades coligativas</t>
+          <t>Rendimiento de una reacción</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6673,7 +6673,7 @@
         <v>8</v>
       </c>
       <c r="AF117" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG117" t="inlineStr">
         <is>
@@ -6682,14 +6682,14 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Rendimiento de una reacción</t>
+          <t>Sólidos cristalinos y amorfos</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6704,7 +6704,7 @@
         <v>8</v>
       </c>
       <c r="AF118" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG118" t="inlineStr">
         <is>
@@ -6713,45 +6713,87 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sólidos cristalinos y amorfos</t>
+          <t>Neutralización y reacciones de los ácidos</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="C119" t="n">
+        <v>9</v>
+      </c>
+      <c r="F119" t="n">
         <v>8</v>
       </c>
-      <c r="D119" t="n">
-        <v>8</v>
+      <c r="G119" t="n">
+        <v>3</v>
+      </c>
+      <c r="H119" t="n">
+        <v>7</v>
+      </c>
+      <c r="I119" t="n">
+        <v>5</v>
+      </c>
+      <c r="J119" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L119" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M119" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O119" t="n">
+        <v>1</v>
+      </c>
+      <c r="P119" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>1</v>
+      </c>
+      <c r="R119" t="n">
+        <v>1</v>
+      </c>
+      <c r="S119" t="n">
+        <v>1</v>
+      </c>
+      <c r="U119" t="n">
+        <v>1</v>
+      </c>
+      <c r="V119" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>1</v>
       </c>
       <c r="AF119" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Neutralización y reacciones de los ácidos</t>
+          <t>Oxidación y reducción</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6760,28 +6802,25 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F120" t="n">
         <v>8</v>
       </c>
       <c r="G120" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
       </c>
       <c r="I120" t="n">
-        <v>5</v>
-      </c>
-      <c r="J120" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="L120" t="n">
         <v>7.5</v>
       </c>
       <c r="M120" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O120" t="n">
         <v>1</v>
@@ -6795,20 +6834,14 @@
       <c r="R120" t="n">
         <v>1</v>
       </c>
-      <c r="S120" t="n">
-        <v>1</v>
-      </c>
       <c r="U120" t="n">
         <v>1</v>
       </c>
       <c r="V120" t="n">
         <v>1</v>
       </c>
-      <c r="Z120" t="n">
-        <v>1</v>
-      </c>
       <c r="AF120" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG120" t="inlineStr">
         <is>
@@ -6824,7 +6857,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Oxidación y reducción</t>
+          <t>Reacciones exotérmicas y endotérmicas</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6835,6 +6868,9 @@
       <c r="C121" t="n">
         <v>10</v>
       </c>
+      <c r="E121" t="n">
+        <v>7</v>
+      </c>
       <c r="F121" t="n">
         <v>8</v>
       </c>
@@ -6847,12 +6883,15 @@
       <c r="I121" t="n">
         <v>7</v>
       </c>
-      <c r="L121" t="n">
-        <v>7.5</v>
+      <c r="J121" t="n">
+        <v>7</v>
       </c>
       <c r="M121" t="n">
         <v>7</v>
       </c>
+      <c r="N121" t="n">
+        <v>1</v>
+      </c>
       <c r="O121" t="n">
         <v>1</v>
       </c>
@@ -6865,14 +6904,17 @@
       <c r="R121" t="n">
         <v>1</v>
       </c>
-      <c r="U121" t="n">
+      <c r="S121" t="n">
         <v>1</v>
       </c>
       <c r="V121" t="n">
         <v>1</v>
       </c>
+      <c r="Z121" t="n">
+        <v>1</v>
+      </c>
       <c r="AF121" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG121" t="inlineStr">
         <is>
@@ -6880,79 +6922,6 @@
         </is>
       </c>
       <c r="AH121" t="inlineStr">
-        <is>
-          <t>tardio</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Reacciones exotérmicas y endotérmicas</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>tardio</t>
-        </is>
-      </c>
-      <c r="C122" t="n">
-        <v>10</v>
-      </c>
-      <c r="E122" t="n">
-        <v>7</v>
-      </c>
-      <c r="F122" t="n">
-        <v>8</v>
-      </c>
-      <c r="G122" t="n">
-        <v>6</v>
-      </c>
-      <c r="H122" t="n">
-        <v>7</v>
-      </c>
-      <c r="I122" t="n">
-        <v>7</v>
-      </c>
-      <c r="J122" t="n">
-        <v>7</v>
-      </c>
-      <c r="M122" t="n">
-        <v>7</v>
-      </c>
-      <c r="N122" t="n">
-        <v>1</v>
-      </c>
-      <c r="O122" t="n">
-        <v>1</v>
-      </c>
-      <c r="P122" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>1</v>
-      </c>
-      <c r="R122" t="n">
-        <v>1</v>
-      </c>
-      <c r="S122" t="n">
-        <v>1</v>
-      </c>
-      <c r="V122" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z122" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF122" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>tardio</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
         <is>
           <t>tardio</t>
         </is>
@@ -6969,7 +6938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J122"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -12064,48 +12033,6 @@
       </c>
       <c r="J121">
         <f>Datos!B121</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122">
-        <f>Datos!A122</f>
-        <v/>
-      </c>
-      <c r="B122">
-        <f>IF(Datos!C122="","",Datos!C122)</f>
-        <v/>
-      </c>
-      <c r="C122">
-        <f>COUNT(Datos!E122:M122)</f>
-        <v/>
-      </c>
-      <c r="D122">
-        <f>IF(C122=0,"",MEDIAN(Datos!E122:M122))</f>
-        <v/>
-      </c>
-      <c r="E122">
-        <f>COUNT(Datos!W122:AE122)</f>
-        <v/>
-      </c>
-      <c r="F122">
-        <f>IF(OR(B122="",D122=""),"",B122-D122)</f>
-        <v/>
-      </c>
-      <c r="G122">
-        <f>IF(Datos!D122="","",Datos!D122)</f>
-        <v/>
-      </c>
-      <c r="H122">
-        <f>COUNT(Datos!N122:V122)</f>
-        <v/>
-      </c>
-      <c r="I122">
-        <f>IF(B122="",IF(C122&gt;=5,"falta en SV",""),IF(G122="",IF(B122&gt;8,IF(C122&gt;=5,"SV tarde","despues del tramo"),IF(H122&gt;=5,"no retomado en 2-8","previo")),IF(B122&lt;2,"retomado",IF(AND(C122&lt;=1,E122&gt;=3),"solo especializacion",IF(F122="","coherente",IF(F122&lt;=-1.5,"SV adelantado",IF(F122&gt;=2,"SV tarde","coherente")))))))</f>
-        <v/>
-      </c>
-      <c r="J122">
-        <f>Datos!B122</f>
         <v/>
       </c>
     </row>
@@ -12145,7 +12072,7 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIF(Datos!B2:B122,A2)</f>
+        <f>COUNTIF(Datos!B2:B121,A2)</f>
         <v/>
       </c>
     </row>
@@ -12156,7 +12083,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(Datos!B2:B122,A3)</f>
+        <f>COUNTIF(Datos!B2:B121,A3)</f>
         <v/>
       </c>
     </row>
@@ -12167,7 +12094,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(Datos!B2:B122,A4)</f>
+        <f>COUNTIF(Datos!B2:B121,A4)</f>
         <v/>
       </c>
     </row>
@@ -12178,7 +12105,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(Datos!B2:B122,A5)</f>
+        <f>COUNTIF(Datos!B2:B121,A5)</f>
         <v/>
       </c>
     </row>
@@ -12189,7 +12116,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(Datos!B2:B122,A6)</f>
+        <f>COUNTIF(Datos!B2:B121,A6)</f>
         <v/>
       </c>
     </row>
@@ -12200,7 +12127,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF(Datos!B2:B122,A7)</f>
+        <f>COUNTIF(Datos!B2:B121,A7)</f>
         <v/>
       </c>
     </row>
@@ -12211,7 +12138,7 @@
         </is>
       </c>
       <c r="B8">
-        <f>COUNTIF(Datos!B2:B122,A8)</f>
+        <f>COUNTIF(Datos!B2:B121,A8)</f>
         <v/>
       </c>
     </row>

--- a/internacional/2_8/Contraste_quimica.xlsx
+++ b/internacional/2_8/Contraste_quimica.xlsx
@@ -1147,7 +1147,7 @@
         <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>Compuestos inorgánicos: funciones y nomenclatura</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3067,13 +3067,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
-      </c>
-      <c r="E36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F36" t="n">
         <v>8</v>
@@ -3081,60 +3078,24 @@
       <c r="G36" t="n">
         <v>6</v>
       </c>
-      <c r="H36" t="n">
-        <v>7</v>
-      </c>
-      <c r="I36" t="n">
-        <v>3</v>
-      </c>
-      <c r="J36" t="n">
-        <v>7</v>
-      </c>
-      <c r="K36" t="n">
-        <v>4</v>
-      </c>
-      <c r="L36" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M36" t="n">
         <v>7</v>
       </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
       <c r="O36" t="n">
         <v>1</v>
       </c>
       <c r="P36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1</v>
-      </c>
       <c r="V36" t="n">
         <v>1</v>
       </c>
-      <c r="Z36" t="n">
-        <v>1</v>
-      </c>
       <c r="AF36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -3146,7 +3107,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Compuestos inorgánicos: funciones y nomenclatura</t>
+          <t>Oxidación y corrosión de los metales</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3155,47 +3116,44 @@
         </is>
       </c>
       <c r="C37" t="n">
+        <v>11</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" t="n">
         <v>5</v>
       </c>
-      <c r="D37" t="n">
-        <v>5</v>
-      </c>
-      <c r="F37" t="n">
-        <v>8</v>
-      </c>
-      <c r="G37" t="n">
-        <v>6</v>
-      </c>
       <c r="M37" t="n">
-        <v>7</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1</v>
-      </c>
-      <c r="P37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="n">
         <v>1</v>
       </c>
       <c r="V37" t="n">
         <v>1</v>
       </c>
       <c r="AF37" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Oxidación y corrosión de los metales</t>
+          <t>Proceso de disolución y solvatación</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3210,41 +3168,41 @@
         <v>7</v>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
-      </c>
-      <c r="I38" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="K38" t="n">
+        <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="V38" t="n">
         <v>1</v>
       </c>
       <c r="AF38" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
           <t>alineado</t>
-        </is>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Proceso de disolución y solvatación</t>
+          <t>Propiedades físicas de los materiales</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3253,35 +3211,74 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>6</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.5</v>
       </c>
       <c r="K39" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
       </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
+      <c r="U39" t="n">
+        <v>1</v>
+      </c>
       <c r="V39" t="n">
         <v>1</v>
       </c>
+      <c r="Z39" t="n">
+        <v>1</v>
+      </c>
       <c r="AF39" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
@@ -3293,7 +3290,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Propiedades físicas de los materiales</t>
+          <t>Propiedades físicas y químicas</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3311,7 +3308,7 @@
         <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G40" t="n">
         <v>2</v>
@@ -3329,10 +3326,10 @@
         <v>2</v>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="M40" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="N40" t="n">
         <v>1</v>
@@ -3359,9 +3356,6 @@
         <v>1</v>
       </c>
       <c r="V40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z40" t="n">
         <v>1</v>
       </c>
       <c r="AF40" t="n">
@@ -3369,7 +3363,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -3381,7 +3375,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Propiedades físicas y químicas</t>
+          <t>Sustancias puras: elementos y compuestos</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3390,37 +3384,37 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F41" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I41" t="n">
         <v>6</v>
       </c>
       <c r="J41" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K41" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L41" t="n">
         <v>7.5</v>
       </c>
       <c r="M41" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="N41" t="n">
         <v>1</v>
@@ -3449,24 +3443,27 @@
       <c r="V41" t="n">
         <v>1</v>
       </c>
+      <c r="Z41" t="n">
+        <v>1</v>
+      </c>
       <c r="AF41" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sustancias puras: elementos y compuestos</t>
+          <t>Tipo de enlace y propiedades de las sustancias</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3475,12 +3472,9 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
-      </c>
-      <c r="E42" t="n">
         <v>6</v>
       </c>
       <c r="F42" t="n">
@@ -3492,69 +3486,39 @@
       <c r="H42" t="n">
         <v>7</v>
       </c>
-      <c r="I42" t="n">
+      <c r="M42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF42" t="n">
         <v>6</v>
       </c>
-      <c r="J42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K42" t="n">
-        <v>6</v>
-      </c>
-      <c r="L42" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1</v>
-      </c>
-      <c r="S42" t="n">
-        <v>1</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>8</v>
-      </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tipo de enlace y propiedades de las sustancias</t>
+          <t>Clasificación de las reacciones químicas</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3577,8 +3541,11 @@
       <c r="H43" t="n">
         <v>7</v>
       </c>
-      <c r="M43" t="n">
-        <v>7</v>
+      <c r="I43" t="n">
+        <v>6</v>
+      </c>
+      <c r="L43" t="n">
+        <v>7.5</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
@@ -3589,7 +3556,10 @@
       <c r="Q43" t="n">
         <v>1</v>
       </c>
-      <c r="V43" t="n">
+      <c r="R43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
         <v>1</v>
       </c>
       <c r="AF43" t="n">
@@ -3597,7 +3567,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
@@ -3609,12 +3579,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Clasificación de las reacciones químicas</t>
+          <t>Cromatografía</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3623,23 +3593,17 @@
       <c r="D44" t="n">
         <v>6</v>
       </c>
-      <c r="F44" t="n">
-        <v>8</v>
-      </c>
       <c r="G44" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H44" t="n">
         <v>7</v>
-      </c>
-      <c r="I44" t="n">
-        <v>6</v>
       </c>
       <c r="L44" t="n">
         <v>7.5</v>
       </c>
-      <c r="O44" t="n">
-        <v>1</v>
+      <c r="M44" t="n">
+        <v>7</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -3647,39 +3611,45 @@
       <c r="Q44" t="n">
         <v>1</v>
       </c>
-      <c r="R44" t="n">
-        <v>1</v>
-      </c>
       <c r="U44" t="n">
         <v>1</v>
       </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
       <c r="AF44" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Agentes oxidantes y reductores</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4</v>
       </c>
       <c r="F45" t="n">
         <v>8</v>
@@ -3691,11 +3661,23 @@
         <v>7</v>
       </c>
       <c r="I45" t="n">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="J45" t="n">
+        <v>7</v>
+      </c>
+      <c r="K45" t="n">
+        <v>4</v>
+      </c>
+      <c r="L45" t="n">
+        <v>7.5</v>
       </c>
       <c r="M45" t="n">
         <v>7</v>
       </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
       <c r="O45" t="n">
         <v>1</v>
       </c>
@@ -3708,32 +3690,44 @@
       <c r="R45" t="n">
         <v>1</v>
       </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
+      </c>
       <c r="V45" t="n">
         <v>1</v>
       </c>
+      <c r="Z45" t="n">
+        <v>1</v>
+      </c>
       <c r="AF45" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Aminoácidos y estructura de las proteínas</t>
+          <t>Química de los ácidos nucleicos</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -3759,35 +3753,44 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Autoionización del agua, Kw y cálculo de pH</t>
+          <t>Semivida, series de desintegración y residuos radiactivos</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="D47" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" t="n">
+        <v>8</v>
+      </c>
+      <c r="F47" t="n">
+        <v>8</v>
       </c>
       <c r="G47" t="n">
         <v>8.5</v>
       </c>
-      <c r="M47" t="n">
-        <v>7</v>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
       </c>
-      <c r="V47" t="n">
-        <v>1</v>
-      </c>
       <c r="AF47" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
@@ -3799,96 +3802,66 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Celdas galvánicas</t>
+          <t>Energía de enlace</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
-      </c>
-      <c r="D48" t="n">
-        <v>4</v>
-      </c>
-      <c r="I48" t="n">
-        <v>5</v>
-      </c>
-      <c r="M48" t="n">
-        <v>7</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF48" t="n">
         <v>11</v>
       </c>
+      <c r="G48" t="n">
+        <v>6</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Metales, cerámicas y materiales compuestos</t>
+          <t>Redes covalentes y alótropos del carbono</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>10</v>
       </c>
-      <c r="E49" t="n">
-        <v>3</v>
-      </c>
       <c r="F49" t="n">
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
-      </c>
-      <c r="H49" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="M49" t="n">
         <v>7</v>
       </c>
-      <c r="N49" t="n">
-        <v>1</v>
-      </c>
       <c r="O49" t="n">
         <v>1</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
       </c>
-      <c r="Q49" t="n">
-        <v>1</v>
-      </c>
       <c r="V49" t="n">
         <v>1</v>
       </c>
-      <c r="Z49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>10</v>
-      </c>
       <c r="AG49" t="inlineStr">
         <is>
           <t>posterior</t>
@@ -3896,14 +3869,14 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cromatografía</t>
+          <t>Agentes oxidantes y reductores</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3911,51 +3884,51 @@
           <t>posterior</t>
         </is>
       </c>
-      <c r="C50" t="n">
-        <v>10</v>
+      <c r="F50" t="n">
+        <v>8</v>
       </c>
       <c r="G50" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H50" t="n">
         <v>7</v>
       </c>
-      <c r="L50" t="n">
-        <v>7.5</v>
+      <c r="I50" t="n">
+        <v>8</v>
       </c>
       <c r="M50" t="n">
         <v>7</v>
       </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
       </c>
-      <c r="U50" t="n">
+      <c r="R50" t="n">
         <v>1</v>
       </c>
       <c r="V50" t="n">
         <v>1</v>
       </c>
-      <c r="AF50" t="n">
-        <v>10</v>
-      </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>faltante</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mezclas de gases, difusión y gases reales</t>
+          <t>Aminoácidos y estructura de las proteínas</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3964,22 +3937,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>8</v>
-      </c>
-      <c r="J51" t="n">
-        <v>7</v>
-      </c>
-      <c r="L51" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S51" t="n">
-        <v>1</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AF51" t="n">
         <v>10</v>
@@ -3998,7 +3959,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ecuación de los gases ideales y volumen molar</t>
+          <t>Autoionización del agua, Kw y cálculo de pH</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4007,16 +3968,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>10</v>
-      </c>
-      <c r="F52" t="n">
-        <v>8</v>
-      </c>
-      <c r="O52" t="n">
+        <v>9</v>
+      </c>
+      <c r="G52" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M52" t="n">
+        <v>7</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
+      <c r="V52" t="n">
         <v>1</v>
       </c>
       <c r="AF52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
@@ -4032,7 +3999,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ecuaciones y reacciones nucleares</t>
+          <t>Celdas galvánicas</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4041,20 +4008,29 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
-      </c>
-      <c r="L53" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="U53" t="n">
+        <v>4</v>
+      </c>
+      <c r="D53" t="n">
+        <v>4</v>
+      </c>
+      <c r="I53" t="n">
+        <v>5</v>
+      </c>
+      <c r="M53" t="n">
+        <v>7</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="V53" t="n">
         <v>1</v>
       </c>
       <c r="AF53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH53" t="inlineStr">
@@ -4066,7 +4042,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>El carbono y las moléculas orgánicas</t>
+          <t>Metales, cerámicas y materiales compuestos</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4077,26 +4053,41 @@
       <c r="C54" t="n">
         <v>10</v>
       </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
       <c r="F54" t="n">
         <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H54" t="n">
+        <v>7</v>
       </c>
       <c r="M54" t="n">
         <v>7</v>
       </c>
+      <c r="N54" t="n">
+        <v>1</v>
+      </c>
       <c r="O54" t="n">
         <v>1</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
       </c>
+      <c r="Q54" t="n">
+        <v>1</v>
+      </c>
       <c r="V54" t="n">
         <v>1</v>
       </c>
+      <c r="Z54" t="n">
+        <v>1</v>
+      </c>
       <c r="AF54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
@@ -4105,14 +4096,14 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Electrólisis y celdas electrolíticas</t>
+          <t>Mezclas de gases, difusión y gases reales</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4121,30 +4112,21 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>10</v>
-      </c>
-      <c r="G55" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H55" t="n">
-        <v>7</v>
-      </c>
-      <c r="I55" t="n">
         <v>8</v>
       </c>
-      <c r="M55" t="n">
-        <v>7</v>
-      </c>
-      <c r="P55" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>1</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1</v>
-      </c>
-      <c r="V55" t="n">
+      <c r="D55" t="n">
+        <v>8</v>
+      </c>
+      <c r="J55" t="n">
+        <v>7</v>
+      </c>
+      <c r="L55" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
         <v>1</v>
       </c>
       <c r="AF55" t="n">
@@ -4152,7 +4134,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH55" t="inlineStr">
@@ -4164,7 +4146,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Electrolitos fuertes y débiles</t>
+          <t>Ecuación de los gases ideales y volumen molar</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4173,34 +4155,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>8</v>
       </c>
-      <c r="G56" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I56" t="n">
-        <v>8</v>
-      </c>
-      <c r="M56" t="n">
-        <v>7</v>
-      </c>
       <c r="O56" t="n">
         <v>1</v>
       </c>
-      <c r="P56" t="n">
-        <v>1</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1</v>
-      </c>
       <c r="AF56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
@@ -4216,7 +4180,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Energía de activación y perfil energético</t>
+          <t>Ecuaciones y reacciones nucleares</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4225,23 +4189,20 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
-      </c>
-      <c r="D57" t="n">
-        <v>5</v>
-      </c>
-      <c r="G57" t="n">
-        <v>6</v>
-      </c>
-      <c r="P57" t="n">
+        <v>11</v>
+      </c>
+      <c r="L57" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="U57" t="n">
         <v>1</v>
       </c>
       <c r="AF57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
@@ -4253,7 +4214,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Energía de enlace</t>
+          <t>El carbono y las moléculas orgánicas</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4262,16 +4223,28 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F58" t="n">
+        <v>8</v>
       </c>
       <c r="G58" t="n">
-        <v>6</v>
+        <v>8.5</v>
+      </c>
+      <c r="M58" t="n">
+        <v>7</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
       </c>
       <c r="P58" t="n">
         <v>1</v>
       </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
       <c r="AF58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
@@ -4287,7 +4260,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Entalpía de reacción y ecuaciones termoquímicas</t>
+          <t>Electrólisis y celdas electrolíticas</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4296,13 +4269,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G59" t="n">
         <v>8.5</v>
       </c>
+      <c r="H59" t="n">
+        <v>7</v>
+      </c>
       <c r="I59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M59" t="n">
         <v>7</v>
@@ -4310,6 +4286,9 @@
       <c r="P59" t="n">
         <v>1</v>
       </c>
+      <c r="Q59" t="n">
+        <v>1</v>
+      </c>
       <c r="R59" t="n">
         <v>1</v>
       </c>
@@ -4317,7 +4296,7 @@
         <v>1</v>
       </c>
       <c r="AF59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
@@ -4333,7 +4312,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Equilibrio químico dinámico</t>
+          <t>Electrolitos fuertes y débiles</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4342,18 +4321,27 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
-      </c>
-      <c r="D60" t="n">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="F60" t="n">
+        <v>8</v>
       </c>
       <c r="G60" t="n">
         <v>8.5</v>
       </c>
+      <c r="I60" t="n">
+        <v>8</v>
+      </c>
       <c r="M60" t="n">
         <v>7</v>
       </c>
+      <c r="O60" t="n">
+        <v>1</v>
+      </c>
       <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
         <v>1</v>
       </c>
       <c r="V60" t="n">
@@ -4364,7 +4352,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH60" t="inlineStr">
@@ -4376,7 +4364,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Equilibrio y rapidez en procesos industriales</t>
+          <t>Energía de activación y perfil energético</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4385,10 +4373,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="D61" t="n">
+        <v>5</v>
       </c>
       <c r="G61" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="P61" t="n">
         <v>1</v>
@@ -4398,7 +4389,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
@@ -4410,7 +4401,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Espectros atómicos y modelo de Bohr</t>
+          <t>Entalpía de reacción y ecuaciones termoquímicas</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4421,10 +4412,22 @@
       <c r="C62" t="n">
         <v>10</v>
       </c>
-      <c r="H62" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q62" t="n">
+      <c r="G62" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I62" t="n">
+        <v>7</v>
+      </c>
+      <c r="M62" t="n">
+        <v>7</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1</v>
+      </c>
+      <c r="V62" t="n">
         <v>1</v>
       </c>
       <c r="AF62" t="n">
@@ -4444,7 +4447,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Estereoquímica y quiralidad</t>
+          <t>Equilibrio químico dinámico</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4453,20 +4456,29 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="D63" t="n">
+        <v>6</v>
+      </c>
+      <c r="G63" t="n">
+        <v>8.5</v>
       </c>
       <c r="M63" t="n">
         <v>7</v>
       </c>
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
       <c r="V63" t="n">
         <v>1</v>
       </c>
       <c r="AF63" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH63" t="inlineStr">
@@ -4478,7 +4490,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Esterificación e hidrólisis</t>
+          <t>Equilibrio y rapidez en procesos industriales</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4487,12 +4499,12 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>11</v>
-      </c>
-      <c r="M64" t="n">
-        <v>7</v>
-      </c>
-      <c r="V64" t="n">
+        <v>9</v>
+      </c>
+      <c r="G64" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P64" t="n">
         <v>1</v>
       </c>
       <c r="AF64" t="n">
@@ -4512,7 +4524,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Estructura y propiedades de los polímeros</t>
+          <t>Espectros atómicos y modelo de Bohr</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4521,37 +4533,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>11</v>
-      </c>
-      <c r="F65" t="n">
-        <v>8</v>
-      </c>
-      <c r="G65" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H65" t="n">
         <v>7</v>
       </c>
-      <c r="M65" t="n">
-        <v>7</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" t="n">
-        <v>1</v>
-      </c>
       <c r="Q65" t="n">
         <v>1</v>
       </c>
-      <c r="V65" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>1</v>
-      </c>
       <c r="AF65" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
@@ -4567,7 +4558,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Fuerza de ácidos y bases: Ka y Kb</t>
+          <t>Estereoquímica y quiralidad</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4576,28 +4567,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>9</v>
-      </c>
-      <c r="F66" t="n">
-        <v>8</v>
-      </c>
-      <c r="G66" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="M66" t="n">
         <v>7</v>
       </c>
-      <c r="O66" t="n">
-        <v>1</v>
-      </c>
-      <c r="P66" t="n">
-        <v>1</v>
-      </c>
       <c r="V66" t="n">
         <v>1</v>
       </c>
       <c r="AF66" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
@@ -4613,7 +4592,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Fundamentos de la reactividad orgánica</t>
+          <t>Esterificación e hidrólisis</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4622,17 +4601,20 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
-      </c>
-      <c r="D67" t="n">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="M67" t="n">
+        <v>7</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
       </c>
       <c r="AF67" t="n">
         <v>11</v>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH67" t="inlineStr">
@@ -4644,7 +4626,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Grupos funcionales</t>
+          <t>Estructura y propiedades de los polímeros</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4653,13 +4635,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F68" t="n">
         <v>8</v>
       </c>
       <c r="G68" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H68" t="n">
+        <v>7</v>
       </c>
       <c r="M68" t="n">
         <v>7</v>
@@ -4670,7 +4655,13 @@
       <c r="P68" t="n">
         <v>1</v>
       </c>
+      <c r="Q68" t="n">
+        <v>1</v>
+      </c>
       <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z68" t="n">
         <v>1</v>
       </c>
       <c r="AF68" t="n">
@@ -4690,7 +4681,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Hidrocarburos: alcanos, alquenos y alquinos</t>
+          <t>Fuerza de ácidos y bases: Ka y Kb</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4699,7 +4690,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F69" t="n">
         <v>8</v>
@@ -4719,11 +4710,8 @@
       <c r="V69" t="n">
         <v>1</v>
       </c>
-      <c r="Z69" t="n">
-        <v>1</v>
-      </c>
       <c r="AF69" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
@@ -4739,7 +4727,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Hidrocarburos aromáticos</t>
+          <t>Fundamentos de la reactividad orgánica</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4748,20 +4736,17 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>11</v>
-      </c>
-      <c r="G70" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P70" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D70" t="n">
+        <v>5</v>
       </c>
       <c r="AF70" t="n">
         <v>11</v>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH70" t="inlineStr">
@@ -4773,7 +4758,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Isomería estructural</t>
+          <t>Grupos funcionales</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4782,22 +4767,28 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F71" t="n">
         <v>8</v>
       </c>
+      <c r="G71" t="n">
+        <v>8.5</v>
+      </c>
       <c r="M71" t="n">
         <v>7</v>
       </c>
       <c r="O71" t="n">
         <v>1</v>
       </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
       <c r="V71" t="n">
         <v>1</v>
       </c>
       <c r="AF71" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG71" t="inlineStr">
         <is>
@@ -4813,7 +4804,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ley de Hess y entalpías de formación</t>
+          <t>Hidrocarburos: alcanos, alquenos y alquinos</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4822,16 +4813,31 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F72" t="n">
+        <v>8</v>
       </c>
       <c r="G72" t="n">
         <v>8.5</v>
       </c>
+      <c r="M72" t="n">
+        <v>7</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
       <c r="P72" t="n">
         <v>1</v>
       </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>1</v>
+      </c>
       <c r="AF72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
@@ -4847,7 +4853,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Leyes de los gases</t>
+          <t>Hidrocarburos aromáticos</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4856,22 +4862,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>10</v>
-      </c>
-      <c r="I73" t="n">
-        <v>6</v>
-      </c>
-      <c r="J73" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R73" t="n">
-        <v>1</v>
-      </c>
-      <c r="S73" t="n">
+        <v>11</v>
+      </c>
+      <c r="G73" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P73" t="n">
         <v>1</v>
       </c>
       <c r="AF73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Leyes ponderales y volumétricas</t>
+          <t>Isomería estructural</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4896,22 +4896,22 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>10</v>
-      </c>
-      <c r="I74" t="n">
-        <v>7</v>
-      </c>
-      <c r="J74" t="n">
-        <v>7</v>
-      </c>
-      <c r="R74" t="n">
-        <v>1</v>
-      </c>
-      <c r="S74" t="n">
+        <v>11</v>
+      </c>
+      <c r="F74" t="n">
+        <v>8</v>
+      </c>
+      <c r="M74" t="n">
+        <v>7</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="V74" t="n">
         <v>1</v>
       </c>
       <c r="AF74" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Nomenclatura orgánica IUPAC</t>
+          <t>Ley de Hess y entalpías de formación</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4936,29 +4936,20 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>7</v>
-      </c>
-      <c r="D75" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G75" t="n">
-        <v>6</v>
-      </c>
-      <c r="M75" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="P75" t="n">
         <v>1</v>
       </c>
-      <c r="V75" t="n">
-        <v>1</v>
-      </c>
       <c r="AF75" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH75" t="inlineStr">
@@ -4970,7 +4961,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Polimerización por adición y por condensación</t>
+          <t>Leyes de los gases</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4979,19 +4970,22 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>11</v>
-      </c>
-      <c r="M76" t="n">
-        <v>7</v>
-      </c>
-      <c r="V76" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z76" t="n">
+        <v>10</v>
+      </c>
+      <c r="I76" t="n">
+        <v>6</v>
+      </c>
+      <c r="J76" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
+      <c r="S76" t="n">
         <v>1</v>
       </c>
       <c r="AF76" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG76" t="inlineStr">
         <is>
@@ -5007,7 +5001,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Polímeros y ambiente</t>
+          <t>Leyes ponderales y volumétricas</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5016,31 +5010,22 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>11</v>
-      </c>
-      <c r="F77" t="n">
-        <v>8</v>
-      </c>
-      <c r="H77" t="n">
-        <v>7</v>
-      </c>
-      <c r="K77" t="n">
-        <v>8</v>
-      </c>
-      <c r="O77" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>1</v>
-      </c>
-      <c r="T77" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z77" t="n">
+        <v>10</v>
+      </c>
+      <c r="I77" t="n">
+        <v>7</v>
+      </c>
+      <c r="J77" t="n">
+        <v>7</v>
+      </c>
+      <c r="R77" t="n">
+        <v>1</v>
+      </c>
+      <c r="S77" t="n">
         <v>1</v>
       </c>
       <c r="AF77" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
@@ -5056,7 +5041,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Potenciales estándar de electrodo y de celda</t>
+          <t>Nomenclatura orgánica IUPAC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5065,18 +5050,21 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>10</v>
-      </c>
-      <c r="F78" t="n">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D78" t="n">
+        <v>7</v>
       </c>
       <c r="G78" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O78" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="M78" t="n">
+        <v>7</v>
       </c>
       <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="V78" t="n">
         <v>1</v>
       </c>
       <c r="AF78" t="n">
@@ -5084,7 +5072,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH78" t="inlineStr">
@@ -5096,7 +5084,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Principio de Le Chatelier</t>
+          <t>Polimerización por adición y por condensación</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5105,22 +5093,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>9</v>
-      </c>
-      <c r="G79" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="M79" t="n">
         <v>7</v>
       </c>
-      <c r="P79" t="n">
-        <v>1</v>
-      </c>
       <c r="V79" t="n">
         <v>1</v>
       </c>
+      <c r="Z79" t="n">
+        <v>1</v>
+      </c>
       <c r="AF79" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
@@ -5136,7 +5121,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Procesos de la industria química</t>
+          <t>Polímeros y ambiente</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5145,47 +5130,47 @@
         </is>
       </c>
       <c r="C80" t="n">
+        <v>11</v>
+      </c>
+      <c r="F80" t="n">
         <v>8</v>
       </c>
-      <c r="D80" t="n">
+      <c r="H80" t="n">
+        <v>7</v>
+      </c>
+      <c r="K80" t="n">
         <v>8</v>
       </c>
-      <c r="G80" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K80" t="n">
-        <v>4</v>
-      </c>
-      <c r="M80" t="n">
-        <v>7</v>
-      </c>
-      <c r="P80" t="n">
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
         <v>1</v>
       </c>
       <c r="T80" t="n">
         <v>1</v>
       </c>
-      <c r="V80" t="n">
+      <c r="Z80" t="n">
         <v>1</v>
       </c>
       <c r="AF80" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Química de los carbohidratos</t>
+          <t>Potenciales estándar de electrodo y de celda</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5194,17 +5179,26 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
-      </c>
-      <c r="D81" t="n">
-        <v>6</v>
+        <v>11</v>
+      </c>
+      <c r="F81" t="n">
+        <v>8</v>
+      </c>
+      <c r="G81" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1</v>
       </c>
       <c r="AF81" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH81" t="inlineStr">
@@ -5216,7 +5210,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Química de los lípidos</t>
+          <t>Principio de Le Chatelier</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5225,17 +5219,26 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
-      </c>
-      <c r="D82" t="n">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="G82" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M82" t="n">
+        <v>7</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1</v>
+      </c>
+      <c r="V82" t="n">
+        <v>1</v>
       </c>
       <c r="AF82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH82" t="inlineStr">
@@ -5247,7 +5250,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Química verde y economía atómica</t>
+          <t>Procesos de la industria química</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5256,44 +5259,47 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="D83" t="n">
+        <v>8</v>
       </c>
       <c r="G83" t="n">
         <v>8.5</v>
       </c>
-      <c r="H83" t="n">
-        <v>7</v>
-      </c>
       <c r="K83" t="n">
         <v>4</v>
       </c>
+      <c r="M83" t="n">
+        <v>7</v>
+      </c>
       <c r="P83" t="n">
         <v>1</v>
       </c>
-      <c r="Q83" t="n">
-        <v>1</v>
-      </c>
       <c r="T83" t="n">
         <v>1</v>
       </c>
+      <c r="V83" t="n">
+        <v>1</v>
+      </c>
       <c r="AF83" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Radiactividad y emisiones nucleares</t>
+          <t>Química de los lípidos</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5302,16 +5308,10 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
-      </c>
-      <c r="E84" t="n">
-        <v>8</v>
-      </c>
-      <c r="N84" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AF84" t="n">
         <v>10</v>
@@ -5330,7 +5330,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Factores que afectan la rapidez de reacción</t>
+          <t>Química verde y economía atómica</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5339,25 +5339,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>6</v>
-      </c>
-      <c r="D85" t="n">
-        <v>6</v>
-      </c>
-      <c r="F85" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G85" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H85" t="n">
         <v>7</v>
       </c>
-      <c r="M85" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O85" t="n">
-        <v>1</v>
+      <c r="K85" t="n">
+        <v>4</v>
       </c>
       <c r="P85" t="n">
         <v>1</v>
@@ -5365,18 +5356,15 @@
       <c r="Q85" t="n">
         <v>1</v>
       </c>
-      <c r="V85" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z85" t="n">
+      <c r="T85" t="n">
         <v>1</v>
       </c>
       <c r="AF85" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH85" t="inlineStr">
@@ -5388,7 +5376,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Reacciones de precipitación e identificación de iones</t>
+          <t>Radiactividad y emisiones nucleares</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5397,24 +5385,12 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>9</v>
-      </c>
-      <c r="H86" t="n">
-        <v>7</v>
-      </c>
-      <c r="I86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="n">
         <v>8</v>
       </c>
-      <c r="M86" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>1</v>
-      </c>
-      <c r="R86" t="n">
-        <v>1</v>
-      </c>
-      <c r="V86" t="n">
+      <c r="N86" t="n">
         <v>1</v>
       </c>
       <c r="AF86" t="n">
@@ -5434,7 +5410,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Reacciones orgánicas características</t>
+          <t>Factores que afectan la rapidez de reacción</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5443,20 +5419,44 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="D87" t="n">
+        <v>6</v>
+      </c>
+      <c r="F87" t="n">
+        <v>8</v>
+      </c>
+      <c r="G87" t="n">
+        <v>6</v>
+      </c>
+      <c r="H87" t="n">
+        <v>7</v>
       </c>
       <c r="M87" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="O87" t="n">
+        <v>1</v>
+      </c>
+      <c r="P87" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1</v>
       </c>
       <c r="V87" t="n">
         <v>1</v>
       </c>
+      <c r="Z87" t="n">
+        <v>1</v>
+      </c>
       <c r="AF87" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
@@ -5468,7 +5468,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Reactivo limitante y en exceso</t>
+          <t>Reacciones de precipitación e identificación de iones</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5477,16 +5477,28 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10</v>
-      </c>
-      <c r="G88" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P88" t="n">
+        <v>11</v>
+      </c>
+      <c r="H88" t="n">
+        <v>7</v>
+      </c>
+      <c r="I88" t="n">
+        <v>8</v>
+      </c>
+      <c r="M88" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>1</v>
+      </c>
+      <c r="R88" t="n">
+        <v>1</v>
+      </c>
+      <c r="V88" t="n">
         <v>1</v>
       </c>
       <c r="AF88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
@@ -5502,7 +5514,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Redes covalentes y alótropos del carbono</t>
+          <t>Reacciones orgánicas características</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5511,28 +5523,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10</v>
-      </c>
-      <c r="F89" t="n">
-        <v>8</v>
-      </c>
-      <c r="G89" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="M89" t="n">
         <v>7</v>
       </c>
-      <c r="O89" t="n">
-        <v>1</v>
-      </c>
-      <c r="P89" t="n">
-        <v>1</v>
-      </c>
       <c r="V89" t="n">
         <v>1</v>
       </c>
       <c r="AF89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Semivida, series de desintegración y residuos radiactivos</t>
+          <t>Reactivo limitante y en exceso</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5559,26 +5559,14 @@
       <c r="C90" t="n">
         <v>10</v>
       </c>
-      <c r="E90" t="n">
-        <v>8</v>
-      </c>
-      <c r="F90" t="n">
-        <v>8</v>
-      </c>
       <c r="G90" t="n">
         <v>8.5</v>
       </c>
-      <c r="N90" t="n">
-        <v>1</v>
-      </c>
-      <c r="O90" t="n">
-        <v>1</v>
-      </c>
       <c r="P90" t="n">
         <v>1</v>
       </c>
       <c r="AF90" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG90" t="inlineStr">
         <is>
@@ -5655,7 +5643,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F92" t="n">
         <v>8</v>
@@ -5932,10 +5920,10 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G99" t="n">
         <v>8.5</v>
@@ -5944,7 +5932,7 @@
         <v>1</v>
       </c>
       <c r="AF99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG99" t="inlineStr">
         <is>
@@ -6104,10 +6092,10 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F103" t="n">
         <v>8</v>
@@ -6133,9 +6121,6 @@
       <c r="U103" t="n">
         <v>1</v>
       </c>
-      <c r="AF103" t="n">
-        <v>10</v>
-      </c>
       <c r="AG103" t="inlineStr">
         <is>
           <t>adelantado</t>
@@ -6143,7 +6128,7 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6714,10 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="D119" t="n">
+        <v>7</v>
       </c>
       <c r="F119" t="n">
         <v>8</v>
@@ -6777,16 +6765,16 @@
         <v>1</v>
       </c>
       <c r="AF119" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>

--- a/internacional/2_8/Contraste_quimica.xlsx
+++ b/internacional/2_8/Contraste_quimica.xlsx
@@ -2489,7 +2489,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Disolución y rapidez de disolución</t>
+          <t>Cromatografía</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2498,31 +2498,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
-      </c>
-      <c r="I28" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L28" t="n">
         <v>7.5</v>
       </c>
       <c r="M28" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="P28" t="n">
         <v>1</v>
@@ -2530,15 +2521,6 @@
       <c r="Q28" t="n">
         <v>1</v>
       </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1</v>
-      </c>
       <c r="U28" t="n">
         <v>1</v>
       </c>
@@ -2546,23 +2528,23 @@
         <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ecuación química y su balanceo</t>
+          <t>Disolución y rapidez de disolución</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2571,40 +2553,31 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
-      </c>
-      <c r="E29" t="n">
-        <v>8</v>
-      </c>
-      <c r="F29" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
         <v>4.5</v>
       </c>
+      <c r="K29" t="n">
+        <v>2</v>
+      </c>
       <c r="L29" t="n">
         <v>7.5</v>
       </c>
       <c r="M29" t="n">
-        <v>7</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
@@ -2618,17 +2591,17 @@
       <c r="S29" t="n">
         <v>1</v>
       </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
       <c r="U29" t="n">
         <v>1</v>
       </c>
       <c r="V29" t="n">
         <v>1</v>
       </c>
-      <c r="Z29" t="n">
-        <v>1</v>
-      </c>
       <c r="AF29" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
@@ -2644,7 +2617,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Escala de pH</t>
+          <t>Ecuación química y su balanceo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2653,10 +2626,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="E30" t="n">
+        <v>8</v>
       </c>
       <c r="F30" t="n">
         <v>8</v>
@@ -2668,7 +2644,7 @@
         <v>7</v>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J30" t="n">
         <v>4.5</v>
@@ -2677,7 +2653,10 @@
         <v>7.5</v>
       </c>
       <c r="M30" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
@@ -2698,6 +2677,9 @@
         <v>1</v>
       </c>
       <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="n">
         <v>1</v>
       </c>
       <c r="AF30" t="n">
@@ -2717,7 +2699,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Estados de la materia</t>
+          <t>Escala de pH</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2726,40 +2708,31 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="M31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
@@ -2776,20 +2749,14 @@
       <c r="S31" t="n">
         <v>1</v>
       </c>
-      <c r="T31" t="n">
-        <v>1</v>
-      </c>
       <c r="U31" t="n">
         <v>1</v>
       </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
-      <c r="Z31" t="n">
-        <v>1</v>
-      </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
@@ -2805,7 +2772,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Estequiometría</t>
+          <t>Estados de la materia</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2814,22 +2781,40 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
       </c>
       <c r="F32" t="n">
         <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>8.5</v>
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>4</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
@@ -2837,14 +2822,29 @@
       <c r="P32" t="n">
         <v>1</v>
       </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
       <c r="R32" t="n">
         <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1</v>
+      </c>
       <c r="AF32" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Indicadores ácido-base</t>
+          <t>Estequiometría</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2869,25 +2869,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="D33" t="n">
+        <v>8</v>
       </c>
       <c r="F33" t="n">
         <v>8</v>
       </c>
       <c r="G33" t="n">
-        <v>6</v>
-      </c>
-      <c r="H33" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I33" t="n">
         <v>7</v>
       </c>
       <c r="J33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L33" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M33" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O33" t="n">
         <v>1</v>
@@ -2895,36 +2892,30 @@
       <c r="P33" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
       </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
       <c r="AF33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Materia y materiales</t>
+          <t>Indicadores ácido-base</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2933,41 +2924,26 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F34" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="M34" t="n">
         <v>2.5</v>
       </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
       <c r="O34" t="n">
         <v>1</v>
       </c>
@@ -2977,15 +2953,9 @@
       <c r="Q34" t="n">
         <v>1</v>
       </c>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
       <c r="S34" t="n">
         <v>1</v>
       </c>
-      <c r="T34" t="n">
-        <v>1</v>
-      </c>
       <c r="U34" t="n">
         <v>1</v>
       </c>
@@ -2993,23 +2963,23 @@
         <v>1</v>
       </c>
       <c r="AF34" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Minerales: composición y estructura cristalina</t>
+          <t>Materia y materiales</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3018,19 +2988,37 @@
         </is>
       </c>
       <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
         <v>8</v>
       </c>
-      <c r="D35" t="n">
-        <v>8</v>
-      </c>
-      <c r="E35" t="n">
-        <v>7</v>
-      </c>
-      <c r="F35" t="n">
-        <v>8</v>
-      </c>
-      <c r="H35" t="n">
-        <v>7</v>
+      <c r="J35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.5</v>
       </c>
       <c r="N35" t="n">
         <v>1</v>
@@ -3038,15 +3026,33 @@
       <c r="O35" t="n">
         <v>1</v>
       </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
       <c r="Q35" t="n">
         <v>1</v>
       </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
       <c r="AF35" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
@@ -3058,7 +3064,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Compuestos inorgánicos: funciones y nomenclatura</t>
+          <t>Minerales: composición y estructura cristalina</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3067,31 +3073,31 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7</v>
       </c>
       <c r="F36" t="n">
         <v>8</v>
       </c>
-      <c r="G36" t="n">
-        <v>6</v>
-      </c>
-      <c r="M36" t="n">
-        <v>7</v>
+      <c r="H36" t="n">
+        <v>7</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
       </c>
       <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="P36" t="n">
-        <v>1</v>
-      </c>
-      <c r="V36" t="n">
+      <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
@@ -3107,7 +3113,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Oxidación y corrosión de los metales</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3116,16 +3122,46 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4</v>
+      </c>
+      <c r="F37" t="n">
+        <v>8</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6</v>
       </c>
       <c r="H37" t="n">
+        <v>7</v>
+      </c>
+      <c r="I37" t="n">
         <v>3</v>
       </c>
-      <c r="I37" t="n">
-        <v>5</v>
+      <c r="J37" t="n">
+        <v>7</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4</v>
+      </c>
+      <c r="L37" t="n">
+        <v>7.5</v>
       </c>
       <c r="M37" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
@@ -3133,27 +3169,39 @@
       <c r="R37" t="n">
         <v>1</v>
       </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
       <c r="V37" t="n">
         <v>1</v>
       </c>
+      <c r="Z37" t="n">
+        <v>1</v>
+      </c>
       <c r="AF37" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Proceso de disolución y solvatación</t>
+          <t>Compuestos inorgánicos: funciones y nomenclatura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3162,31 +3210,31 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
-      </c>
-      <c r="H38" t="n">
-        <v>7</v>
-      </c>
-      <c r="K38" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>8</v>
+      </c>
+      <c r="G38" t="n">
         <v>6</v>
       </c>
       <c r="M38" t="n">
         <v>7</v>
       </c>
-      <c r="Q38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T38" t="n">
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" t="n">
         <v>1</v>
       </c>
       <c r="V38" t="n">
         <v>1</v>
       </c>
       <c r="AF38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
@@ -3202,7 +3250,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Propiedades físicas de los materiales</t>
+          <t>Oxidación y corrosión de los metales</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3211,86 +3259,44 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" t="n">
-        <v>2</v>
-      </c>
-      <c r="F39" t="n">
+        <v>11</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" t="n">
         <v>5</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" t="n">
-        <v>6</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K39" t="n">
-        <v>2</v>
-      </c>
-      <c r="L39" t="n">
-        <v>3</v>
       </c>
       <c r="M39" t="n">
         <v>2.5</v>
       </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1</v>
-      </c>
       <c r="Q39" t="n">
         <v>1</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
       </c>
-      <c r="S39" t="n">
-        <v>1</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1</v>
-      </c>
       <c r="V39" t="n">
         <v>1</v>
       </c>
-      <c r="Z39" t="n">
-        <v>1</v>
-      </c>
       <c r="AF39" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Propiedades físicas y químicas</t>
+          <t>Proceso de disolución y solvatación</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3299,71 +3305,35 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
-      </c>
-      <c r="E40" t="n">
-        <v>2</v>
-      </c>
-      <c r="F40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" t="n">
+        <v>7</v>
+      </c>
+      <c r="K40" t="n">
         <v>6</v>
       </c>
-      <c r="J40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K40" t="n">
-        <v>2</v>
-      </c>
-      <c r="L40" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M40" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" t="n">
-        <v>1</v>
-      </c>
-      <c r="S40" t="n">
-        <v>1</v>
-      </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
-      <c r="U40" t="n">
-        <v>1</v>
-      </c>
       <c r="V40" t="n">
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -3375,7 +3345,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sustancias puras: elementos y compuestos</t>
+          <t>Propiedades físicas de los materiales</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3384,34 +3354,34 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I41" t="n">
         <v>6</v>
       </c>
       <c r="J41" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K41" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L41" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
         <v>2.5</v>
@@ -3447,7 +3417,7 @@
         <v>1</v>
       </c>
       <c r="AF41" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
@@ -3456,14 +3426,14 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tipo de enlace y propiedades de las sustancias</t>
+          <t>Propiedades físicas y químicas</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3472,22 +3442,40 @@
         </is>
       </c>
       <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" t="n">
         <v>6</v>
       </c>
-      <c r="D42" t="n">
-        <v>6</v>
-      </c>
-      <c r="F42" t="n">
-        <v>8</v>
-      </c>
-      <c r="G42" t="n">
-        <v>6</v>
-      </c>
-      <c r="H42" t="n">
-        <v>7</v>
+      <c r="J42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>7.5</v>
       </c>
       <c r="M42" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
@@ -3498,15 +3486,27 @@
       <c r="Q42" t="n">
         <v>1</v>
       </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
+      </c>
       <c r="V42" t="n">
         <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
@@ -3518,7 +3518,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Clasificación de las reacciones químicas</t>
+          <t>Sustancias puras: elementos y compuestos</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3527,9 +3527,12 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D43" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" t="n">
         <v>6</v>
       </c>
       <c r="F43" t="n">
@@ -3544,9 +3547,21 @@
       <c r="I43" t="n">
         <v>6</v>
       </c>
+      <c r="J43" t="n">
+        <v>7</v>
+      </c>
+      <c r="K43" t="n">
+        <v>6</v>
+      </c>
       <c r="L43" t="n">
         <v>7.5</v>
       </c>
+      <c r="M43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
       <c r="O43" t="n">
         <v>1</v>
       </c>
@@ -3559,11 +3574,23 @@
       <c r="R43" t="n">
         <v>1</v>
       </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
       <c r="U43" t="n">
         <v>1</v>
       </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1</v>
+      </c>
       <c r="AF43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
@@ -3572,19 +3599,19 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cromatografía</t>
+          <t>Tipo de enlace y propiedades de las sustancias</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3593,63 +3620,60 @@
       <c r="D44" t="n">
         <v>6</v>
       </c>
+      <c r="F44" t="n">
+        <v>8</v>
+      </c>
       <c r="G44" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H44" t="n">
         <v>7</v>
       </c>
-      <c r="L44" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M44" t="n">
         <v>7</v>
       </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
-      <c r="U44" t="n">
-        <v>1</v>
-      </c>
       <c r="V44" t="n">
         <v>1</v>
       </c>
       <c r="AF44" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>Clasificación de las reacciones químicas</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F45" t="n">
         <v>8</v>
@@ -3661,23 +3685,11 @@
         <v>7</v>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" t="n">
-        <v>7</v>
-      </c>
-      <c r="K45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L45" t="n">
         <v>7.5</v>
       </c>
-      <c r="M45" t="n">
-        <v>7</v>
-      </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
       <c r="O45" t="n">
         <v>1</v>
       </c>
@@ -3690,19 +3702,7 @@
       <c r="R45" t="n">
         <v>1</v>
       </c>
-      <c r="S45" t="n">
-        <v>1</v>
-      </c>
-      <c r="T45" t="n">
-        <v>1</v>
-      </c>
       <c r="U45" t="n">
-        <v>1</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z45" t="n">
         <v>1</v>
       </c>
       <c r="AF45" t="n">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
@@ -3722,53 +3722,47 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Química de los ácidos nucleicos</t>
+          <t>Energía de enlace</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C46" t="n">
+        <v>11</v>
+      </c>
+      <c r="G46" t="n">
         <v>6</v>
       </c>
-      <c r="D46" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>10</v>
+      <c r="P46" t="n">
+        <v>1</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Semivida, series de desintegración y residuos radiactivos</t>
+          <t>Redes covalentes y alótropos del carbono</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
-      </c>
-      <c r="D47" t="n">
-        <v>5</v>
-      </c>
-      <c r="E47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F47" t="n">
         <v>8</v>
@@ -3776,8 +3770,8 @@
       <c r="G47" t="n">
         <v>8.5</v>
       </c>
-      <c r="N47" t="n">
-        <v>1</v>
+      <c r="M47" t="n">
+        <v>7</v>
       </c>
       <c r="O47" t="n">
         <v>1</v>
@@ -3785,98 +3779,107 @@
       <c r="P47" t="n">
         <v>1</v>
       </c>
-      <c r="AF47" t="n">
-        <v>11</v>
+      <c r="V47" t="n">
+        <v>1</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Energía de enlace</t>
+          <t>Agentes oxidantes y reductores</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>no_aplica</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>11</v>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>8</v>
       </c>
       <c r="G48" t="n">
         <v>6</v>
       </c>
+      <c r="H48" t="n">
+        <v>7</v>
+      </c>
+      <c r="I48" t="n">
+        <v>8</v>
+      </c>
+      <c r="M48" t="n">
+        <v>7</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
       <c r="P48" t="n">
         <v>1</v>
       </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>faltante</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Redes covalentes y alótropos del carbono</t>
+          <t>Aminoácidos y estructura de las proteínas</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C49" t="n">
+        <v>6</v>
+      </c>
+      <c r="D49" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF49" t="n">
         <v>10</v>
       </c>
-      <c r="F49" t="n">
-        <v>8</v>
-      </c>
-      <c r="G49" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M49" t="n">
-        <v>7</v>
-      </c>
-      <c r="O49" t="n">
-        <v>1</v>
-      </c>
-      <c r="P49" t="n">
-        <v>1</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1</v>
-      </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Agentes oxidantes y reductores</t>
+          <t>Autoionización del agua, Kw y cálculo de pH</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3884,51 +3887,39 @@
           <t>posterior</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>8</v>
+      <c r="C50" t="n">
+        <v>9</v>
       </c>
       <c r="G50" t="n">
-        <v>6</v>
-      </c>
-      <c r="H50" t="n">
-        <v>7</v>
-      </c>
-      <c r="I50" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="M50" t="n">
         <v>7</v>
       </c>
-      <c r="O50" t="n">
-        <v>1</v>
-      </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
-        <v>1</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1</v>
-      </c>
       <c r="V50" t="n">
         <v>1</v>
       </c>
+      <c r="AF50" t="n">
+        <v>9</v>
+      </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>faltante</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Aminoácidos y estructura de las proteínas</t>
+          <t>Celdas galvánicas</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3937,13 +3928,25 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="I51" t="n">
+        <v>5</v>
+      </c>
+      <c r="M51" t="n">
+        <v>7</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
       </c>
       <c r="AF51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
@@ -3959,7 +3962,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Autoionización del agua, Kw y cálculo de pH</t>
+          <t>Metales, cerámicas y materiales compuestos</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3968,22 +3971,43 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E52" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" t="n">
+        <v>8</v>
       </c>
       <c r="G52" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H52" t="n">
+        <v>7</v>
       </c>
       <c r="M52" t="n">
         <v>7</v>
       </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
       <c r="P52" t="n">
         <v>1</v>
       </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
       <c r="V52" t="n">
         <v>1</v>
       </c>
+      <c r="Z52" t="n">
+        <v>1</v>
+      </c>
       <c r="AF52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
@@ -3992,14 +4016,14 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Celdas galvánicas</t>
+          <t>Mezclas de gases, difusión y gases reales</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4008,25 +4032,25 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
-      </c>
-      <c r="I53" t="n">
-        <v>5</v>
-      </c>
-      <c r="M53" t="n">
-        <v>7</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
-      <c r="V53" t="n">
+        <v>8</v>
+      </c>
+      <c r="J53" t="n">
+        <v>7</v>
+      </c>
+      <c r="L53" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
         <v>1</v>
       </c>
       <c r="AF53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
@@ -4042,7 +4066,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Metales, cerámicas y materiales compuestos</t>
+          <t>Ecuación de los gases ideales y volumen molar</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4053,37 +4077,10 @@
       <c r="C54" t="n">
         <v>10</v>
       </c>
-      <c r="E54" t="n">
-        <v>3</v>
-      </c>
       <c r="F54" t="n">
         <v>8</v>
       </c>
-      <c r="G54" t="n">
-        <v>6</v>
-      </c>
-      <c r="H54" t="n">
-        <v>7</v>
-      </c>
-      <c r="M54" t="n">
-        <v>7</v>
-      </c>
-      <c r="N54" t="n">
-        <v>1</v>
-      </c>
       <c r="O54" t="n">
-        <v>1</v>
-      </c>
-      <c r="P54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>1</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z54" t="n">
         <v>1</v>
       </c>
       <c r="AF54" t="n">
@@ -4096,14 +4093,14 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mezclas de gases, difusión y gases reales</t>
+          <t>Ecuaciones y reacciones nucleares</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4112,29 +4109,20 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
-      </c>
-      <c r="D55" t="n">
-        <v>8</v>
-      </c>
-      <c r="J55" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L55" t="n">
         <v>7.5</v>
       </c>
-      <c r="S55" t="n">
-        <v>1</v>
-      </c>
       <c r="U55" t="n">
         <v>1</v>
       </c>
       <c r="AF55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH55" t="inlineStr">
@@ -4146,7 +4134,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ecuación de los gases ideales y volumen molar</t>
+          <t>El carbono y las moléculas orgánicas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4155,16 +4143,28 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F56" t="n">
         <v>8</v>
       </c>
+      <c r="G56" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M56" t="n">
+        <v>7</v>
+      </c>
       <c r="O56" t="n">
         <v>1</v>
       </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
       <c r="AF56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ecuaciones y reacciones nucleares</t>
+          <t>Electrólisis y celdas electrolíticas</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4191,10 +4191,28 @@
       <c r="C57" t="n">
         <v>11</v>
       </c>
-      <c r="L57" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="U57" t="n">
+      <c r="G57" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>7</v>
+      </c>
+      <c r="I57" t="n">
+        <v>8</v>
+      </c>
+      <c r="M57" t="n">
+        <v>7</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="V57" t="n">
         <v>1</v>
       </c>
       <c r="AF57" t="n">
@@ -4214,7 +4232,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>El carbono y las moléculas orgánicas</t>
+          <t>Electrolitos fuertes y débiles</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4223,7 +4241,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F58" t="n">
         <v>8</v>
@@ -4231,6 +4249,9 @@
       <c r="G58" t="n">
         <v>8.5</v>
       </c>
+      <c r="I58" t="n">
+        <v>8</v>
+      </c>
       <c r="M58" t="n">
         <v>7</v>
       </c>
@@ -4240,11 +4261,14 @@
       <c r="P58" t="n">
         <v>1</v>
       </c>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
       <c r="V58" t="n">
         <v>1</v>
       </c>
       <c r="AF58" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
@@ -4260,7 +4284,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Electrólisis y celdas electrolíticas</t>
+          <t>Energía de activación y perfil energético</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4269,38 +4293,23 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="D59" t="n">
+        <v>5</v>
       </c>
       <c r="G59" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H59" t="n">
-        <v>7</v>
-      </c>
-      <c r="I59" t="n">
-        <v>8</v>
-      </c>
-      <c r="M59" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P59" t="n">
         <v>1</v>
       </c>
-      <c r="Q59" t="n">
-        <v>1</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1</v>
-      </c>
       <c r="AF59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH59" t="inlineStr">
@@ -4312,7 +4321,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Electrolitos fuertes y débiles</t>
+          <t>Entalpía de reacción y ecuaciones termoquímicas</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4321,23 +4330,17 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>9</v>
-      </c>
-      <c r="F60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G60" t="n">
         <v>8.5</v>
       </c>
       <c r="I60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M60" t="n">
         <v>7</v>
       </c>
-      <c r="O60" t="n">
-        <v>1</v>
-      </c>
       <c r="P60" t="n">
         <v>1</v>
       </c>
@@ -4348,7 +4351,7 @@
         <v>1</v>
       </c>
       <c r="AF60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
@@ -4364,7 +4367,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Energía de activación y perfil energético</t>
+          <t>Equilibrio químico dinámico</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4373,19 +4376,25 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G61" t="n">
-        <v>6</v>
+        <v>8.5</v>
+      </c>
+      <c r="M61" t="n">
+        <v>7</v>
       </c>
       <c r="P61" t="n">
         <v>1</v>
       </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
       <c r="AF61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
@@ -4401,7 +4410,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Entalpía de reacción y ecuaciones termoquímicas</t>
+          <t>Equilibrio y rapidez en procesos industriales</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4410,28 +4419,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G62" t="n">
         <v>8.5</v>
       </c>
-      <c r="I62" t="n">
-        <v>7</v>
-      </c>
-      <c r="M62" t="n">
-        <v>7</v>
-      </c>
       <c r="P62" t="n">
         <v>1</v>
       </c>
-      <c r="R62" t="n">
-        <v>1</v>
-      </c>
-      <c r="V62" t="n">
-        <v>1</v>
-      </c>
       <c r="AF62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
@@ -4447,7 +4444,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Equilibrio químico dinámico</t>
+          <t>Espectros atómicos y modelo de Bohr</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4456,29 +4453,20 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
-      </c>
-      <c r="D63" t="n">
-        <v>6</v>
-      </c>
-      <c r="G63" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M63" t="n">
-        <v>7</v>
-      </c>
-      <c r="P63" t="n">
-        <v>1</v>
-      </c>
-      <c r="V63" t="n">
+        <v>10</v>
+      </c>
+      <c r="H63" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q63" t="n">
         <v>1</v>
       </c>
       <c r="AF63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH63" t="inlineStr">
@@ -4490,7 +4478,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Equilibrio y rapidez en procesos industriales</t>
+          <t>Estereoquímica y quiralidad</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4499,12 +4487,12 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>9</v>
-      </c>
-      <c r="G64" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P64" t="n">
+        <v>10</v>
+      </c>
+      <c r="M64" t="n">
+        <v>7</v>
+      </c>
+      <c r="V64" t="n">
         <v>1</v>
       </c>
       <c r="AF64" t="n">
@@ -4524,7 +4512,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Espectros atómicos y modelo de Bohr</t>
+          <t>Esterificación e hidrólisis</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4533,16 +4521,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>10</v>
-      </c>
-      <c r="H65" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q65" t="n">
+        <v>11</v>
+      </c>
+      <c r="M65" t="n">
+        <v>7</v>
+      </c>
+      <c r="V65" t="n">
         <v>1</v>
       </c>
       <c r="AF65" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
@@ -4558,7 +4546,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Estereoquímica y quiralidad</t>
+          <t>Estructura y propiedades de los polímeros</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4567,12 +4555,33 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F66" t="n">
+        <v>8</v>
+      </c>
+      <c r="G66" t="n">
+        <v>6</v>
+      </c>
+      <c r="H66" t="n">
+        <v>7</v>
       </c>
       <c r="M66" t="n">
         <v>7</v>
       </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1</v>
+      </c>
       <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z66" t="n">
         <v>1</v>
       </c>
       <c r="AF66" t="n">
@@ -4592,7 +4601,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Esterificación e hidrólisis</t>
+          <t>Fuerza de ácidos y bases: Ka y Kb</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4601,16 +4610,28 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="F67" t="n">
+        <v>8</v>
+      </c>
+      <c r="G67" t="n">
+        <v>8.5</v>
       </c>
       <c r="M67" t="n">
         <v>7</v>
       </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
       <c r="V67" t="n">
         <v>1</v>
       </c>
       <c r="AF67" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
@@ -4626,7 +4647,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Estructura y propiedades de los polímeros</t>
+          <t>Fundamentos de la reactividad orgánica</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4635,41 +4656,17 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>11</v>
-      </c>
-      <c r="F68" t="n">
-        <v>8</v>
-      </c>
-      <c r="G68" t="n">
-        <v>6</v>
-      </c>
-      <c r="H68" t="n">
-        <v>7</v>
-      </c>
-      <c r="M68" t="n">
-        <v>7</v>
-      </c>
-      <c r="O68" t="n">
-        <v>1</v>
-      </c>
-      <c r="P68" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>1</v>
-      </c>
-      <c r="V68" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D68" t="n">
+        <v>5</v>
       </c>
       <c r="AF68" t="n">
         <v>11</v>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH68" t="inlineStr">
@@ -4681,7 +4678,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Fuerza de ácidos y bases: Ka y Kb</t>
+          <t>Grupos funcionales</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4711,7 +4708,7 @@
         <v>1</v>
       </c>
       <c r="AF69" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
@@ -4727,7 +4724,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Fundamentos de la reactividad orgánica</t>
+          <t>Hidrocarburos: alcanos, alquenos y alquinos</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4736,17 +4733,35 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
-      </c>
-      <c r="D70" t="n">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="F70" t="n">
+        <v>8</v>
+      </c>
+      <c r="G70" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M70" t="n">
+        <v>7</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>1</v>
       </c>
       <c r="AF70" t="n">
         <v>11</v>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH70" t="inlineStr">
@@ -4758,7 +4773,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Grupos funcionales</t>
+          <t>Hidrocarburos aromáticos</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4767,24 +4782,12 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>9</v>
-      </c>
-      <c r="F71" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G71" t="n">
         <v>8.5</v>
       </c>
-      <c r="M71" t="n">
-        <v>7</v>
-      </c>
-      <c r="O71" t="n">
-        <v>1</v>
-      </c>
       <c r="P71" t="n">
-        <v>1</v>
-      </c>
-      <c r="V71" t="n">
         <v>1</v>
       </c>
       <c r="AF71" t="n">
@@ -4804,7 +4807,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Hidrocarburos: alcanos, alquenos y alquinos</t>
+          <t>Isomería estructural</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4818,22 +4821,13 @@
       <c r="F72" t="n">
         <v>8</v>
       </c>
-      <c r="G72" t="n">
-        <v>8.5</v>
-      </c>
       <c r="M72" t="n">
         <v>7</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
       </c>
-      <c r="P72" t="n">
-        <v>1</v>
-      </c>
       <c r="V72" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z72" t="n">
         <v>1</v>
       </c>
       <c r="AF72" t="n">
@@ -4853,7 +4847,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Hidrocarburos aromáticos</t>
+          <t>Ley de Hess y entalpías de formación</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4862,7 +4856,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G73" t="n">
         <v>8.5</v>
@@ -4871,7 +4865,7 @@
         <v>1</v>
       </c>
       <c r="AF73" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
@@ -4887,7 +4881,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Isomería estructural</t>
+          <t>Leyes de los gases</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4896,22 +4890,22 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>11</v>
-      </c>
-      <c r="F74" t="n">
-        <v>8</v>
-      </c>
-      <c r="M74" t="n">
-        <v>7</v>
-      </c>
-      <c r="O74" t="n">
-        <v>1</v>
-      </c>
-      <c r="V74" t="n">
+        <v>10</v>
+      </c>
+      <c r="I74" t="n">
+        <v>6</v>
+      </c>
+      <c r="J74" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" t="n">
         <v>1</v>
       </c>
       <c r="AF74" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
@@ -4927,7 +4921,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ley de Hess y entalpías de formación</t>
+          <t>Leyes ponderales y volumétricas</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4938,10 +4932,16 @@
       <c r="C75" t="n">
         <v>10</v>
       </c>
-      <c r="G75" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P75" t="n">
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>7</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
         <v>1</v>
       </c>
       <c r="AF75" t="n">
@@ -4961,7 +4961,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Leyes de los gases</t>
+          <t>Nomenclatura orgánica IUPAC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4970,26 +4970,29 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>10</v>
-      </c>
-      <c r="I76" t="n">
+        <v>7</v>
+      </c>
+      <c r="D76" t="n">
+        <v>7</v>
+      </c>
+      <c r="G76" t="n">
         <v>6</v>
       </c>
-      <c r="J76" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R76" t="n">
-        <v>1</v>
-      </c>
-      <c r="S76" t="n">
+      <c r="M76" t="n">
+        <v>7</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="V76" t="n">
         <v>1</v>
       </c>
       <c r="AF76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH76" t="inlineStr">
@@ -5001,7 +5004,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Leyes ponderales y volumétricas</t>
+          <t>Polimerización por adición y por condensación</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5010,22 +5013,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>10</v>
-      </c>
-      <c r="I77" t="n">
-        <v>7</v>
-      </c>
-      <c r="J77" t="n">
-        <v>7</v>
-      </c>
-      <c r="R77" t="n">
-        <v>1</v>
-      </c>
-      <c r="S77" t="n">
+        <v>11</v>
+      </c>
+      <c r="M77" t="n">
+        <v>7</v>
+      </c>
+      <c r="V77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z77" t="n">
         <v>1</v>
       </c>
       <c r="AF77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Nomenclatura orgánica IUPAC</t>
+          <t>Polímeros y ambiente</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5050,21 +5050,27 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>7</v>
-      </c>
-      <c r="D78" t="n">
-        <v>7</v>
-      </c>
-      <c r="G78" t="n">
-        <v>6</v>
-      </c>
-      <c r="M78" t="n">
-        <v>7</v>
-      </c>
-      <c r="P78" t="n">
-        <v>1</v>
-      </c>
-      <c r="V78" t="n">
+        <v>11</v>
+      </c>
+      <c r="F78" t="n">
+        <v>8</v>
+      </c>
+      <c r="H78" t="n">
+        <v>7</v>
+      </c>
+      <c r="K78" t="n">
+        <v>8</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z78" t="n">
         <v>1</v>
       </c>
       <c r="AF78" t="n">
@@ -5072,7 +5078,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH78" t="inlineStr">
@@ -5084,7 +5090,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Polimerización por adición y por condensación</t>
+          <t>Potenciales estándar de electrodo y de celda</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5095,13 +5101,16 @@
       <c r="C79" t="n">
         <v>11</v>
       </c>
-      <c r="M79" t="n">
-        <v>7</v>
-      </c>
-      <c r="V79" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z79" t="n">
+      <c r="F79" t="n">
+        <v>8</v>
+      </c>
+      <c r="G79" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" t="n">
         <v>1</v>
       </c>
       <c r="AF79" t="n">
@@ -5121,7 +5130,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Polímeros y ambiente</t>
+          <t>Principio de Le Chatelier</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5130,31 +5139,22 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>11</v>
-      </c>
-      <c r="F80" t="n">
-        <v>8</v>
-      </c>
-      <c r="H80" t="n">
-        <v>7</v>
-      </c>
-      <c r="K80" t="n">
-        <v>8</v>
-      </c>
-      <c r="O80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>1</v>
-      </c>
-      <c r="T80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z80" t="n">
+        <v>9</v>
+      </c>
+      <c r="G80" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M80" t="n">
+        <v>7</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="V80" t="n">
         <v>1</v>
       </c>
       <c r="AF80" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG80" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Potenciales estándar de electrodo y de celda</t>
+          <t>Procesos de la industria química</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5179,38 +5179,47 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>11</v>
-      </c>
-      <c r="F81" t="n">
+        <v>8</v>
+      </c>
+      <c r="D81" t="n">
         <v>8</v>
       </c>
       <c r="G81" t="n">
         <v>8.5</v>
       </c>
-      <c r="O81" t="n">
-        <v>1</v>
+      <c r="K81" t="n">
+        <v>4</v>
+      </c>
+      <c r="M81" t="n">
+        <v>7</v>
       </c>
       <c r="P81" t="n">
         <v>1</v>
       </c>
+      <c r="T81" t="n">
+        <v>1</v>
+      </c>
+      <c r="V81" t="n">
+        <v>1</v>
+      </c>
       <c r="AF81" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Principio de Le Chatelier</t>
+          <t>Química de los ácidos nucleicos</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5219,26 +5228,17 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>9</v>
-      </c>
-      <c r="G82" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M82" t="n">
-        <v>7</v>
-      </c>
-      <c r="P82" t="n">
-        <v>1</v>
-      </c>
-      <c r="V82" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="D82" t="n">
+        <v>6</v>
       </c>
       <c r="AF82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH82" t="inlineStr">
@@ -5250,7 +5250,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Procesos de la industria química</t>
+          <t>Química de los lípidos</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5259,31 +5259,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D83" t="n">
-        <v>8</v>
-      </c>
-      <c r="G83" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K83" t="n">
-        <v>4</v>
-      </c>
-      <c r="M83" t="n">
-        <v>7</v>
-      </c>
-      <c r="P83" t="n">
-        <v>1</v>
-      </c>
-      <c r="T83" t="n">
-        <v>1</v>
-      </c>
-      <c r="V83" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AF83" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG83" t="inlineStr">
         <is>
@@ -5292,14 +5274,14 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Química de los lípidos</t>
+          <t>Química verde y economía atómica</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5308,17 +5290,32 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>6</v>
-      </c>
-      <c r="D84" t="n">
-        <v>6</v>
+        <v>11</v>
+      </c>
+      <c r="G84" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H84" t="n">
+        <v>7</v>
+      </c>
+      <c r="K84" t="n">
+        <v>4</v>
+      </c>
+      <c r="P84" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
       </c>
       <c r="AF84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH84" t="inlineStr">
@@ -5330,7 +5327,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Química verde y economía atómica</t>
+          <t>Radiactividad y emisiones nucleares</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5339,28 +5336,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>11</v>
-      </c>
-      <c r="G85" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H85" t="n">
-        <v>7</v>
-      </c>
-      <c r="K85" t="n">
-        <v>4</v>
-      </c>
-      <c r="P85" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>1</v>
-      </c>
-      <c r="T85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="n">
+        <v>8</v>
+      </c>
+      <c r="N85" t="n">
         <v>1</v>
       </c>
       <c r="AF85" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
@@ -5376,7 +5361,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Radiactividad y emisiones nucleares</t>
+          <t>Factores que afectan la rapidez de reacción</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5385,20 +5370,44 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10</v>
-      </c>
-      <c r="E86" t="n">
+        <v>6</v>
+      </c>
+      <c r="D86" t="n">
+        <v>6</v>
+      </c>
+      <c r="F86" t="n">
         <v>8</v>
       </c>
-      <c r="N86" t="n">
+      <c r="G86" t="n">
+        <v>6</v>
+      </c>
+      <c r="H86" t="n">
+        <v>7</v>
+      </c>
+      <c r="M86" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1</v>
+      </c>
+      <c r="P86" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>1</v>
+      </c>
+      <c r="V86" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z86" t="n">
         <v>1</v>
       </c>
       <c r="AF86" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH86" t="inlineStr">
@@ -5410,7 +5419,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Factores que afectan la rapidez de reacción</t>
+          <t>Reacciones de precipitación e identificación de iones</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5419,44 +5428,32 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>6</v>
-      </c>
-      <c r="D87" t="n">
-        <v>6</v>
-      </c>
-      <c r="F87" t="n">
+        <v>11</v>
+      </c>
+      <c r="H87" t="n">
+        <v>7</v>
+      </c>
+      <c r="I87" t="n">
         <v>8</v>
       </c>
-      <c r="G87" t="n">
-        <v>6</v>
-      </c>
-      <c r="H87" t="n">
-        <v>7</v>
-      </c>
       <c r="M87" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O87" t="n">
-        <v>1</v>
-      </c>
-      <c r="P87" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q87" t="n">
         <v>1</v>
       </c>
+      <c r="R87" t="n">
+        <v>1</v>
+      </c>
       <c r="V87" t="n">
         <v>1</v>
       </c>
-      <c r="Z87" t="n">
-        <v>1</v>
-      </c>
       <c r="AF87" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
@@ -5468,7 +5465,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Reacciones de precipitación e identificación de iones</t>
+          <t>Reacciones orgánicas características</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5479,20 +5476,8 @@
       <c r="C88" t="n">
         <v>11</v>
       </c>
-      <c r="H88" t="n">
-        <v>7</v>
-      </c>
-      <c r="I88" t="n">
-        <v>8</v>
-      </c>
       <c r="M88" t="n">
         <v>7</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>1</v>
-      </c>
-      <c r="R88" t="n">
-        <v>1</v>
       </c>
       <c r="V88" t="n">
         <v>1</v>
@@ -5514,7 +5499,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Reacciones orgánicas características</t>
+          <t>Reactivo limitante y en exceso</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5523,16 +5508,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>11</v>
-      </c>
-      <c r="M89" t="n">
-        <v>7</v>
-      </c>
-      <c r="V89" t="n">
+        <v>10</v>
+      </c>
+      <c r="G89" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P89" t="n">
         <v>1</v>
       </c>
       <c r="AF89" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
@@ -5548,7 +5533,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Reactivo limitante y en exceso</t>
+          <t>Semivida, series de desintegración y residuos radiactivos</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5557,20 +5542,35 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="D90" t="n">
+        <v>5</v>
+      </c>
+      <c r="E90" t="n">
+        <v>8</v>
+      </c>
+      <c r="F90" t="n">
+        <v>8</v>
       </c>
       <c r="G90" t="n">
         <v>8.5</v>
       </c>
+      <c r="N90" t="n">
+        <v>1</v>
+      </c>
+      <c r="O90" t="n">
+        <v>1</v>
+      </c>
       <c r="P90" t="n">
         <v>1</v>
       </c>
       <c r="AF90" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH90" t="inlineStr">
